--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EGCO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DF3C5A-BC59-465A-A093-B7D2C258FDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC6BFC3-A3FD-4AF9-9422-EE5BCD57C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="189">
   <si>
     <t>Key</t>
   </si>
@@ -1648,18 +1648,6 @@
     <t>Ponto.Destino</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>"Uma mudança escalar"</t>
   </si>
   <si>
@@ -1723,33 +1711,9 @@
     <t xml:space="preserve">( Valor.Deslocar and Valor.Angular ) or ( Valor.X and Valor.Y and Valor.Z ) </t>
   </si>
   <si>
-    <t>Valor Deslocar</t>
-  </si>
-  <si>
-    <t>Valor Angular</t>
-  </si>
-  <si>
-    <t>Valor Escalar</t>
-  </si>
-  <si>
-    <t>Ponto Base</t>
-  </si>
-  <si>
-    <t>Ponto Destino</t>
-  </si>
-  <si>
     <t>Translación</t>
   </si>
   <si>
-    <t>Valor de X</t>
-  </si>
-  <si>
-    <t>Valor de Y</t>
-  </si>
-  <si>
-    <t>Valor de Z</t>
-  </si>
-  <si>
     <t>PB1</t>
   </si>
   <si>
@@ -1769,6 +1733,102 @@
   </si>
   <si>
     <t>"Um valor do deslocamento"</t>
+  </si>
+  <si>
+    <t>plano.da.transfornação</t>
+  </si>
+  <si>
+    <t>"XY"</t>
+  </si>
+  <si>
+    <t>é.ponto.base</t>
+  </si>
+  <si>
+    <t>PBP</t>
+  </si>
+  <si>
+    <t>"O Ponto Base do Projeto"</t>
+  </si>
+  <si>
+    <t>"A Translação principal dos módulos estruturais horizontais"</t>
+  </si>
+  <si>
+    <t>TRA_Hor</t>
+  </si>
+  <si>
+    <t>TRA_Ver</t>
+  </si>
+  <si>
+    <t>"A Translação principal dos módulos estruturais verticais"</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>é.transformação.geométrica</t>
+  </si>
+  <si>
+    <t>Ponto.Eixo1 and Ponto.Eixo2</t>
+  </si>
+  <si>
+    <t>Ponto.Eixo1</t>
+  </si>
+  <si>
+    <t>Ponto.Eixo2</t>
+  </si>
+  <si>
+    <t>Ponto 1 que define um eixo de simetria</t>
+  </si>
+  <si>
+    <t>Ponto 2 que define um eixo de simetria</t>
+  </si>
+  <si>
+    <t>Ponto Base que pode servir como primeiro ponto base de um vetor de translação ou para referenciar um projeto</t>
+  </si>
+  <si>
+    <t>Ponto final de um vetor de translação</t>
+  </si>
+  <si>
+    <t>Valor Escalar de uma transformação de mudança de escala</t>
+  </si>
+  <si>
+    <t>Valor Angular de uma transformação de Giro ou rotação</t>
+  </si>
+  <si>
+    <t>Valor Deslocar. Valor de distância de uma translação</t>
+  </si>
+  <si>
+    <t>Valor de Y. Coordenada Y.</t>
+  </si>
+  <si>
+    <t>Valor de X. Coordenada X.</t>
+  </si>
+  <si>
+    <t>Valor de Z. Coordenada Z.</t>
+  </si>
+  <si>
+    <t>Giro. A transformação que transforma a posição de um ponto com um deslocamento circular. Precisa Ponto Base e ângulo.</t>
+  </si>
+  <si>
+    <t>Escalar. Ampliação ou redução de uma forma em relação a um centro de homotetia.  Precisa Ponto Base e fator escalar.</t>
+  </si>
+  <si>
+    <t>Translação. A transformação que transforma o ponto por um deslocamento linear. Precisa Ponto Base e Ponto Destino.</t>
+  </si>
+  <si>
+    <t>Reflexão. Transformação de uma ponto em relação a um eixo de simetria. Precisa Ponto Eixo1 e Ponto Eixo2.</t>
+  </si>
+  <si>
+    <t>Bases.Geométricas</t>
   </si>
 </sst>
 </file>
@@ -1952,7 +2012,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1986,12 +2046,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2063,18 +2117,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6C6AD"/>
-        <bgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6E896"/>
-        <bgColor rgb="FFD9F2D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
@@ -2083,6 +2125,18 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
   </fills>
@@ -2137,7 +2191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2156,10 +2210,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2171,13 +2225,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2189,28 +2243,28 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2225,113 +2279,125 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="0"/>
@@ -2339,46 +2405,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2460,20 +2486,12 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCFF"/>
       <color rgb="FFFF99FF"/>
-      <color rgb="FFFFCCFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2789,7 +2807,7 @@
   <cols>
     <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
     <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="54" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
@@ -2800,7 +2818,7 @@
       <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="47" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2811,7 +2829,7 @@
       <c r="B2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2822,7 +2840,7 @@
       <c r="B3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2833,7 +2851,7 @@
       <c r="B4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2845,7 +2863,7 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2857,7 +2875,7 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2868,7 +2886,7 @@
       <c r="B7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2879,7 +2897,7 @@
       <c r="B8" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2890,7 +2908,7 @@
       <c r="B9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2901,7 +2919,7 @@
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2912,7 +2930,7 @@
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2923,7 +2941,7 @@
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2934,7 +2952,7 @@
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2945,7 +2963,7 @@
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2956,7 +2974,7 @@
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2967,7 +2985,7 @@
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2978,7 +2996,7 @@
       <c r="B17" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2988,44 +3006,44 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46126.520989814817</v>
-      </c>
-      <c r="C18" s="59" t="s">
+        <v>46142.515520833331</v>
+      </c>
+      <c r="C18" s="53" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="45" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="53" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="45" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="61" t="str">
+      <c r="B20" s="55" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="53" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="45" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B21" s="61" t="str">
+      <c r="B21" s="55" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="53" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3036,7 +3054,7 @@
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3047,7 +3065,7 @@
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3058,7 +3076,7 @@
       <c r="B24" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3069,7 +3087,7 @@
       <c r="B25" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="53" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3081,7 +3099,7 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of Genetically Constructed Structures</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="53" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3092,13 +3110,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" customWidth="1"/>
     <col min="2" max="2" width="4.5703125" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="6" width="6.85546875" customWidth="1"/>
     <col min="7" max="10" width="7.42578125" customWidth="1"/>
@@ -3107,8 +3125,8 @@
     <col min="13" max="13" width="3.140625" customWidth="1"/>
     <col min="14" max="14" width="10.7109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="10.28515625" customWidth="1"/>
-    <col min="17" max="17" width="8.42578125" customWidth="1"/>
+    <col min="16" max="16" width="62.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.140625" customWidth="1"/>
     <col min="20" max="20" width="5.7109375" customWidth="1"/>
@@ -3116,7 +3134,7 @@
     <col min="22" max="22" width="6.85546875" customWidth="1"/>
     <col min="23" max="23" width="7" customWidth="1"/>
     <col min="24" max="26" width="6.42578125" customWidth="1"/>
-    <col min="27" max="27" width="8.7109375" customWidth="1"/>
+    <col min="27" max="27" width="53.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3171,7 +3189,7 @@
       <c r="Q1" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="49" t="s">
+      <c r="R1" s="44" t="s">
         <v>88</v>
       </c>
       <c r="S1" s="23" t="s">
@@ -3198,7 +3216,7 @@
       <c r="Z1" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="AA1" s="57" t="s">
+      <c r="AA1" s="51" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3218,8 +3236,8 @@
       <c r="E2" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F2" s="62" t="s">
-        <v>147</v>
+      <c r="F2" s="56" t="s">
+        <v>143</v>
       </c>
       <c r="G2" s="30" t="s">
         <v>1</v>
@@ -3236,63 +3254,63 @@
       <c r="K2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="31" t="str">
-        <f t="shared" ref="L2:L12" si="0">_xlfn.CONCAT(C2)</f>
+      <c r="L2" s="64" t="str">
+        <f t="shared" ref="L2:L14" si="0">_xlfn.CONCAT(C2)</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M2" s="31" t="str">
+      <c r="M2" s="64" t="str">
         <f t="shared" ref="M2" si="1">_xlfn.CONCAT("", D2)</f>
         <v>TGB</v>
       </c>
-      <c r="N2" s="31" t="str">
+      <c r="N2" s="64" t="str">
         <f t="shared" ref="N2" si="2">_xlfn.CONCAT("", E2)</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O2" s="31" t="str">
-        <f t="shared" ref="O2" si="3">_xlfn.CONCAT("", F2)</f>
+      <c r="O2" s="64" t="str">
+        <f t="shared" ref="O2:O15" si="3">_xlfn.CONCAT("", F2)</f>
         <v>Valor.X</v>
       </c>
-      <c r="P2" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q2" s="31" t="str">
-        <f t="shared" ref="Q2:Q13" si="4">_xlfn.TRANSLATE(P2,"pt","es")</f>
-        <v>Valor X</v>
-      </c>
-      <c r="R2" s="50" t="s">
+      <c r="P2" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q2" s="64" t="str">
+        <f t="shared" ref="Q2:Q15" si="4">_xlfn.TRANSLATE(P2,"pt","es")</f>
+        <v>Valor de X. Coordenada X.</v>
+      </c>
+      <c r="R2" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S2" s="33" t="str">
+      <c r="S2" s="66" t="str">
         <f t="shared" ref="S2" si="5">SUBSTITUTE(C2, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T2" s="33" t="str">
+      <c r="T2" s="66" t="str">
         <f t="shared" ref="T2" si="6">SUBSTITUTE(D2, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U2" s="32" t="str">
+      <c r="U2" s="67" t="str">
         <f t="shared" ref="U2" si="7">SUBSTITUTE(E2, "_", " ")</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V2" s="34" t="s">
+      <c r="V2" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W2" s="35" t="str">
+      <c r="W2" s="68" t="str">
         <f>CONCATENATE("Key.EGC",".",A2)</f>
         <v>Key.EGC.2</v>
       </c>
-      <c r="X2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="58" t="str">
-        <f t="shared" ref="AA2:AA13" si="8">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>X Value</v>
+      <c r="X2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="52" t="str">
+        <f t="shared" ref="AA2:AA15" si="8">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Value of X. Coordinate X.</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3311,8 +3329,8 @@
       <c r="E3" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="62" t="s">
-        <v>148</v>
+      <c r="F3" s="56" t="s">
+        <v>144</v>
       </c>
       <c r="G3" s="30" t="s">
         <v>1</v>
@@ -3329,63 +3347,63 @@
       <c r="K3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="31" t="str">
+      <c r="L3" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M3" s="31" t="str">
-        <f t="shared" ref="M3:O3" si="9">_xlfn.CONCAT("", D3)</f>
+      <c r="M3" s="64" t="str">
+        <f t="shared" ref="M3:N3" si="9">_xlfn.CONCAT("", D3)</f>
         <v>TGB</v>
       </c>
-      <c r="N3" s="31" t="str">
+      <c r="N3" s="64" t="str">
         <f t="shared" si="9"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O3" s="31" t="str">
-        <f t="shared" si="9"/>
+      <c r="O3" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Valor.Y</v>
       </c>
-      <c r="P3" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q3" s="31" t="str">
+      <c r="P3" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q3" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Valor Y</v>
-      </c>
-      <c r="R3" s="50" t="s">
+        <v>Valor de Y. Coordenada Y.</v>
+      </c>
+      <c r="R3" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="33" t="str">
+      <c r="S3" s="66" t="str">
         <f t="shared" ref="S3:U3" si="10">SUBSTITUTE(C3, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T3" s="33" t="str">
+      <c r="T3" s="66" t="str">
         <f t="shared" si="10"/>
         <v>TGB</v>
       </c>
-      <c r="U3" s="32" t="str">
+      <c r="U3" s="67" t="str">
         <f t="shared" si="10"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V3" s="34" t="s">
+      <c r="V3" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W3" s="35" t="str">
-        <f t="shared" ref="W3:W13" si="11">CONCATENATE("Key.EGC",".",A3)</f>
+      <c r="W3" s="68" t="str">
+        <f t="shared" ref="W3:W15" si="11">CONCATENATE("Key.EGC",".",A3)</f>
         <v>Key.EGC.3</v>
       </c>
-      <c r="X3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="58" t="str">
+      <c r="X3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Y Value</v>
+        <v>Value of Y. Y-coordinate.</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3404,8 +3422,8 @@
       <c r="E4" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F4" s="62" t="s">
-        <v>149</v>
+      <c r="F4" s="56" t="s">
+        <v>145</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>1</v>
@@ -3422,63 +3440,63 @@
       <c r="K4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="31" t="str">
+      <c r="L4" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M4" s="31" t="str">
-        <f t="shared" ref="M4:M9" si="12">_xlfn.CONCAT("", D4)</f>
+      <c r="M4" s="64" t="str">
+        <f t="shared" ref="M4:M11" si="12">_xlfn.CONCAT("", D4)</f>
         <v>TGB</v>
       </c>
-      <c r="N4" s="31" t="str">
-        <f t="shared" ref="N4:N9" si="13">_xlfn.CONCAT("", E4)</f>
+      <c r="N4" s="64" t="str">
+        <f t="shared" ref="N4:N11" si="13">_xlfn.CONCAT("", E4)</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O4" s="31" t="str">
-        <f t="shared" ref="O4:O9" si="14">_xlfn.CONCAT("", F4)</f>
+      <c r="O4" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Valor.Z</v>
       </c>
-      <c r="P4" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q4" s="31" t="str">
+      <c r="P4" s="64" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q4" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Valor Z</v>
-      </c>
-      <c r="R4" s="50" t="s">
+        <v>Valor Z. Coordenada Z.</v>
+      </c>
+      <c r="R4" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S4" s="33" t="str">
-        <f t="shared" ref="S4:S9" si="15">SUBSTITUTE(C4, "_", " ")</f>
+      <c r="S4" s="66" t="str">
+        <f t="shared" ref="S4:S11" si="14">SUBSTITUTE(C4, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T4" s="33" t="str">
-        <f t="shared" ref="T4:T9" si="16">SUBSTITUTE(D4, "_", " ")</f>
+      <c r="T4" s="66" t="str">
+        <f t="shared" ref="T4:T11" si="15">SUBSTITUTE(D4, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U4" s="32" t="str">
-        <f t="shared" ref="U4:U9" si="17">SUBSTITUTE(E4, "_", " ")</f>
+      <c r="U4" s="67" t="str">
+        <f t="shared" ref="U4:U11" si="16">SUBSTITUTE(E4, "_", " ")</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V4" s="34" t="s">
+      <c r="V4" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W4" s="35" t="str">
+      <c r="W4" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.4</v>
       </c>
-      <c r="X4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="58" t="str">
+      <c r="X4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Z value</v>
+        <v>Z Value. Z Coordinate.</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3497,8 +3515,8 @@
       <c r="E5" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="62" t="s">
-        <v>151</v>
+      <c r="F5" s="56" t="s">
+        <v>147</v>
       </c>
       <c r="G5" s="30" t="s">
         <v>1</v>
@@ -3515,63 +3533,63 @@
       <c r="K5" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L5" s="31" t="str">
+      <c r="L5" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M5" s="31" t="str">
+      <c r="M5" s="64" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N5" s="31" t="str">
+      <c r="N5" s="64" t="str">
         <f t="shared" si="13"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O5" s="31" t="str">
+      <c r="O5" s="64" t="str">
+        <f t="shared" si="3"/>
+        <v>Valor.Deslocar</v>
+      </c>
+      <c r="P5" s="64" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q5" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Valor desplazado. Valor de distancia de una traslación</v>
+      </c>
+      <c r="R5" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="S5" s="66" t="str">
         <f t="shared" si="14"/>
-        <v>Valor.Deslocar</v>
-      </c>
-      <c r="P5" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q5" s="31" t="str">
-        <f t="shared" si="4"/>
-        <v>Valor desplazado</v>
-      </c>
-      <c r="R5" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="S5" s="33" t="str">
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="T5" s="66" t="str">
         <f t="shared" si="15"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T5" s="33" t="str">
+        <v>TGB</v>
+      </c>
+      <c r="U5" s="67" t="str">
         <f t="shared" si="16"/>
-        <v>TGB</v>
-      </c>
-      <c r="U5" s="32" t="str">
-        <f t="shared" si="17"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V5" s="34" t="s">
+      <c r="V5" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W5" s="35" t="str">
+      <c r="W5" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.5</v>
       </c>
-      <c r="X5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="58" t="str">
+      <c r="X5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Displace Value</v>
+        <v>Displace Value. Distance Value of a Translation</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3590,8 +3608,8 @@
       <c r="E6" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F6" s="62" t="s">
-        <v>146</v>
+      <c r="F6" s="56" t="s">
+        <v>142</v>
       </c>
       <c r="G6" s="30" t="s">
         <v>1</v>
@@ -3608,63 +3626,63 @@
       <c r="K6" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L6" s="31" t="str">
+      <c r="L6" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M6" s="31" t="str">
-        <f t="shared" ref="M6" si="18">_xlfn.CONCAT("", D6)</f>
+      <c r="M6" s="64" t="str">
+        <f t="shared" ref="M6" si="17">_xlfn.CONCAT("", D6)</f>
         <v>TGB</v>
       </c>
-      <c r="N6" s="31" t="str">
-        <f t="shared" ref="N6" si="19">_xlfn.CONCAT("", E6)</f>
+      <c r="N6" s="64" t="str">
+        <f t="shared" ref="N6" si="18">_xlfn.CONCAT("", E6)</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O6" s="31" t="str">
-        <f t="shared" ref="O6" si="20">_xlfn.CONCAT("", F6)</f>
+      <c r="O6" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Valor.Angular</v>
       </c>
-      <c r="P6" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q6" s="31" t="str">
+      <c r="P6" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q6" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Valor angular</v>
-      </c>
-      <c r="R6" s="50" t="s">
+        <v>Valor angular de una transformada de espín o rotación</v>
+      </c>
+      <c r="R6" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S6" s="33" t="str">
-        <f t="shared" ref="S6" si="21">SUBSTITUTE(C6, "_", " ")</f>
+      <c r="S6" s="66" t="str">
+        <f t="shared" ref="S6" si="19">SUBSTITUTE(C6, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T6" s="33" t="str">
-        <f t="shared" ref="T6" si="22">SUBSTITUTE(D6, "_", " ")</f>
+      <c r="T6" s="66" t="str">
+        <f t="shared" ref="T6" si="20">SUBSTITUTE(D6, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U6" s="32" t="str">
-        <f t="shared" ref="U6" si="23">SUBSTITUTE(E6, "_", " ")</f>
+      <c r="U6" s="67" t="str">
+        <f t="shared" ref="U6" si="21">SUBSTITUTE(E6, "_", " ")</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V6" s="34" t="s">
+      <c r="V6" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W6" s="35" t="str">
+      <c r="W6" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.6</v>
       </c>
-      <c r="X6" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="58" t="str">
+      <c r="X6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Angular Value</v>
+        <v>Angular Value of a Spin or Rotation Transform</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3683,8 +3701,8 @@
       <c r="E7" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F7" s="62" t="s">
-        <v>150</v>
+      <c r="F7" s="56" t="s">
+        <v>146</v>
       </c>
       <c r="G7" s="30" t="s">
         <v>1</v>
@@ -3701,63 +3719,63 @@
       <c r="K7" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L7" s="31" t="str">
+      <c r="L7" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M7" s="31" t="str">
+      <c r="M7" s="64" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N7" s="31" t="str">
+      <c r="N7" s="64" t="str">
         <f t="shared" si="13"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O7" s="31" t="str">
+      <c r="O7" s="64" t="str">
+        <f t="shared" si="3"/>
+        <v>Valor.Escalar</v>
+      </c>
+      <c r="P7" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q7" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Valor escalar de una transformación que cambia la escala</v>
+      </c>
+      <c r="R7" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="S7" s="66" t="str">
         <f t="shared" si="14"/>
-        <v>Valor.Escalar</v>
-      </c>
-      <c r="P7" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q7" s="31" t="str">
-        <f t="shared" si="4"/>
-        <v>Valor escalar</v>
-      </c>
-      <c r="R7" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="S7" s="33" t="str">
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="T7" s="66" t="str">
         <f t="shared" si="15"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T7" s="33" t="str">
+        <v>TGB</v>
+      </c>
+      <c r="U7" s="67" t="str">
         <f t="shared" si="16"/>
-        <v>TGB</v>
-      </c>
-      <c r="U7" s="32" t="str">
-        <f t="shared" si="17"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V7" s="34" t="s">
+      <c r="V7" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W7" s="35" t="str">
+      <c r="W7" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.7</v>
       </c>
-      <c r="X7" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="58" t="str">
+      <c r="X7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Scalar Value</v>
+        <v>Scalar Value of a Scale-Changing Transformation</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3774,10 +3792,10 @@
         <v>118</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F8" s="62" t="s">
-        <v>126</v>
+        <v>188</v>
+      </c>
+      <c r="F8" s="56" t="s">
+        <v>172</v>
       </c>
       <c r="G8" s="30" t="s">
         <v>1</v>
@@ -3794,68 +3812,68 @@
       <c r="K8" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="31" t="str">
+      <c r="L8" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M8" s="31" t="str">
+      <c r="M8" s="64" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N8" s="31" t="str">
+      <c r="N8" s="64" t="str">
         <f t="shared" si="13"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O8" s="31" t="str">
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O8" s="64" t="str">
+        <f t="shared" si="3"/>
+        <v>Ponto.Eixo1</v>
+      </c>
+      <c r="P8" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q8" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Punto 1 que define un eje de simetría</v>
+      </c>
+      <c r="R8" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="S8" s="66" t="str">
         <f t="shared" si="14"/>
-        <v>Ponto.Base</v>
-      </c>
-      <c r="P8" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q8" s="31" t="str">
-        <f t="shared" si="4"/>
-        <v>Punto base</v>
-      </c>
-      <c r="R8" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="S8" s="33" t="str">
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="T8" s="66" t="str">
         <f t="shared" si="15"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T8" s="33" t="str">
+        <v>TGB</v>
+      </c>
+      <c r="U8" s="67" t="str">
         <f t="shared" si="16"/>
-        <v>TGB</v>
-      </c>
-      <c r="U8" s="32" t="str">
-        <f t="shared" si="17"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V8" s="34" t="s">
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V8" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W8" s="35" t="str">
+      <c r="W8" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.8</v>
       </c>
-      <c r="X8" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="58" t="str">
+      <c r="X8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Base Point</v>
+        <v>Point 1 that defines a symmetry axis</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>94</v>
@@ -3867,10 +3885,10 @@
         <v>118</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>127</v>
+        <v>188</v>
+      </c>
+      <c r="F9" s="56" t="s">
+        <v>173</v>
       </c>
       <c r="G9" s="30" t="s">
         <v>1</v>
@@ -3887,460 +3905,642 @@
       <c r="K9" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="31" t="str">
+      <c r="L9" s="64" t="str">
+        <f t="shared" ref="L9" si="22">_xlfn.CONCAT(C9)</f>
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="M9" s="64" t="str">
+        <f t="shared" ref="M9" si="23">_xlfn.CONCAT("", D9)</f>
+        <v>TGB</v>
+      </c>
+      <c r="N9" s="64" t="str">
+        <f t="shared" ref="N9" si="24">_xlfn.CONCAT("", E9)</f>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O9" s="64" t="str">
+        <f t="shared" si="3"/>
+        <v>Ponto.Eixo2</v>
+      </c>
+      <c r="P9" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q9" s="64" t="str">
+        <f t="shared" ref="Q9" si="25">_xlfn.TRANSLATE(P9,"pt","es")</f>
+        <v>Punto 2 que define un eje de simetría</v>
+      </c>
+      <c r="R9" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="S9" s="66" t="str">
+        <f t="shared" ref="S9" si="26">SUBSTITUTE(C9, "_", " ")</f>
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="T9" s="66" t="str">
+        <f t="shared" ref="T9" si="27">SUBSTITUTE(D9, "_", " ")</f>
+        <v>TGB</v>
+      </c>
+      <c r="U9" s="67" t="str">
+        <f t="shared" ref="U9" si="28">SUBSTITUTE(E9, "_", " ")</f>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V9" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="W9" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key.EGC.8</v>
+      </c>
+      <c r="X9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="52" t="str">
+        <f t="shared" ref="AA9" si="29">_xlfn.TRANSLATE(P9,"pt","en")</f>
+        <v>Point 2 that defines a symmetry axis</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>8</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M9" s="31" t="str">
+      <c r="M10" s="64" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N9" s="31" t="str">
+      <c r="N10" s="64" t="str">
         <f t="shared" si="13"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O9" s="31" t="str">
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O10" s="64" t="str">
+        <f t="shared" si="3"/>
+        <v>Ponto.Base</v>
+      </c>
+      <c r="P10" s="64" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q10" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
+      </c>
+      <c r="R10" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="S10" s="66" t="str">
         <f t="shared" si="14"/>
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="T10" s="66" t="str">
+        <f t="shared" si="15"/>
+        <v>TGB</v>
+      </c>
+      <c r="U10" s="67" t="str">
+        <f t="shared" si="16"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V10" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="W10" s="68" t="str">
+        <f t="shared" si="11"/>
+        <v>Key.EGC.8</v>
+      </c>
+      <c r="X10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Base point that can serve as the first base point of a translation vector or to reference a project</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>9</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="64" t="str">
+        <f t="shared" si="0"/>
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="M11" s="64" t="str">
+        <f t="shared" si="12"/>
+        <v>TGB</v>
+      </c>
+      <c r="N11" s="64" t="str">
+        <f t="shared" si="13"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O11" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Ponto.Destino</v>
       </c>
-      <c r="P9" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q9" s="31" t="str">
+      <c r="P11" s="64" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q11" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Punto de destino</v>
-      </c>
-      <c r="R9" s="50" t="s">
+        <v>Punto final de un vector de traslación</v>
+      </c>
+      <c r="R11" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S9" s="33" t="str">
+      <c r="S11" s="66" t="str">
+        <f t="shared" si="14"/>
+        <v>Estrutura.Geométrica</v>
+      </c>
+      <c r="T11" s="66" t="str">
         <f t="shared" si="15"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T9" s="33" t="str">
+        <v>TGB</v>
+      </c>
+      <c r="U11" s="67" t="str">
         <f t="shared" si="16"/>
-        <v>TGB</v>
-      </c>
-      <c r="U9" s="32" t="str">
-        <f t="shared" si="17"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V9" s="34" t="s">
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V11" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W9" s="35" t="str">
+      <c r="W11" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.9</v>
       </c>
-      <c r="X9" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="58" t="str">
+      <c r="X11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Destination Point</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+        <v>Endpoint of a Translation Vector</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
         <v>10</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B12" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C12" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D12" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E12" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="62" t="s">
+      <c r="F12" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="G10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="L10" s="31" t="str">
+      <c r="G12" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="L12" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M10" s="31" t="str">
-        <f t="shared" ref="M10:M13" si="24">_xlfn.CONCAT("", D10)</f>
+      <c r="M12" s="64" t="str">
+        <f t="shared" ref="M12:M15" si="30">_xlfn.CONCAT("", D12)</f>
         <v>TGB</v>
       </c>
-      <c r="N10" s="31" t="str">
-        <f t="shared" ref="N10:N13" si="25">_xlfn.CONCAT("", E10)</f>
+      <c r="N12" s="64" t="str">
+        <f t="shared" ref="N12:N15" si="31">_xlfn.CONCAT("", E12)</f>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O10" s="31" t="str">
-        <f t="shared" ref="O10:O13" si="26">_xlfn.CONCAT("", F10)</f>
+      <c r="O12" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Translação</v>
       </c>
-      <c r="P10" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q10" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="R10" s="50" t="s">
+      <c r="P12" s="64" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q12" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="R12" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S10" s="33" t="str">
-        <f t="shared" ref="S10:S13" si="27">SUBSTITUTE(C10, "_", " ")</f>
+      <c r="S12" s="66" t="str">
+        <f t="shared" ref="S12:S15" si="32">SUBSTITUTE(C12, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T10" s="33" t="str">
-        <f t="shared" ref="T10:T13" si="28">SUBSTITUTE(D10, "_", " ")</f>
+      <c r="T12" s="66" t="str">
+        <f t="shared" ref="T12:T15" si="33">SUBSTITUTE(D12, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U10" s="32" t="str">
-        <f t="shared" ref="U10:U13" si="29">SUBSTITUTE(E10, "_", " ")</f>
+      <c r="U12" s="67" t="str">
+        <f t="shared" ref="U12:U15" si="34">SUBSTITUTE(E12, "_", " ")</f>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="V10" s="34" t="s">
+      <c r="V12" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W10" s="35" t="str">
+      <c r="W12" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.10</v>
       </c>
-      <c r="X10" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="58" t="str">
+      <c r="X12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Translation</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+        <v>Translation. The transformation that transforms the point by a linear displacement. Need Base Point and Target Point.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
         <v>11</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B13" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C13" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D13" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E13" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F13" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="L11" s="31" t="str">
+      <c r="G13" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="L13" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M11" s="31" t="str">
-        <f t="shared" si="24"/>
+      <c r="M13" s="64" t="str">
+        <f t="shared" si="30"/>
         <v>TGB</v>
       </c>
-      <c r="N11" s="31" t="str">
-        <f t="shared" si="25"/>
+      <c r="N13" s="64" t="str">
+        <f t="shared" si="31"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O11" s="31" t="str">
-        <f t="shared" si="26"/>
+      <c r="O13" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Giro</v>
       </c>
-      <c r="P11" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q11" s="31" t="str">
+      <c r="P13" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q13" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Giro</v>
-      </c>
-      <c r="R11" s="50" t="s">
+        <v>Giro. La transformación que transforma la posición de un punto con un desplazamiento circular. Punto base y ángulo precisos.</v>
+      </c>
+      <c r="R13" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S11" s="33" t="str">
-        <f t="shared" si="27"/>
+      <c r="S13" s="66" t="str">
+        <f t="shared" si="32"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T11" s="33" t="str">
-        <f t="shared" si="28"/>
+      <c r="T13" s="66" t="str">
+        <f t="shared" si="33"/>
         <v>TGB</v>
       </c>
-      <c r="U11" s="32" t="str">
-        <f t="shared" si="29"/>
+      <c r="U13" s="67" t="str">
+        <f t="shared" si="34"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="V11" s="34" t="s">
+      <c r="V13" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W11" s="35" t="str">
+      <c r="W13" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.11</v>
       </c>
-      <c r="X11" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="58" t="str">
+      <c r="X13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Giro</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
+        <v>Giro. The transformation that transforms the position of a point with a circular displacement. Precise Base Point and Angle.</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26">
         <v>12</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B14" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C14" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D14" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E14" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F14" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="L12" s="31" t="str">
+      <c r="G14" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M12" s="31" t="str">
-        <f t="shared" si="24"/>
+      <c r="M14" s="64" t="str">
+        <f t="shared" si="30"/>
         <v>TGB</v>
       </c>
-      <c r="N12" s="31" t="str">
-        <f t="shared" si="25"/>
+      <c r="N14" s="64" t="str">
+        <f t="shared" si="31"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O12" s="31" t="str">
-        <f t="shared" si="26"/>
+      <c r="O14" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Escalar</v>
       </c>
-      <c r="P12" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q12" s="31" t="str">
+      <c r="P14" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q14" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Escala</v>
-      </c>
-      <c r="R12" s="50" t="s">
+        <v>Escala. Agrandamiento o reducción de una forma en relación con un centro homotético.  Necesito punto base y factor escalar.</v>
+      </c>
+      <c r="R14" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S12" s="33" t="str">
-        <f t="shared" si="27"/>
+      <c r="S14" s="66" t="str">
+        <f t="shared" si="32"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T12" s="33" t="str">
-        <f t="shared" si="28"/>
+      <c r="T14" s="66" t="str">
+        <f t="shared" si="33"/>
         <v>TGB</v>
       </c>
-      <c r="U12" s="32" t="str">
-        <f t="shared" si="29"/>
+      <c r="U14" s="67" t="str">
+        <f t="shared" si="34"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="V12" s="34" t="s">
+      <c r="V14" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W12" s="35" t="str">
+      <c r="W14" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.12</v>
       </c>
-      <c r="X12" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="58" t="str">
+      <c r="X14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Scale</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+        <v>Scale. Enlargement or reduction of a shape in relation to a homothetic center.  Need Base Point and Scalar Factor.</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26">
         <v>13</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B15" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C15" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D15" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E15" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F15" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="G13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="31" t="str">
-        <f t="shared" ref="L13" si="30">_xlfn.CONCAT(C13)</f>
+      <c r="G15" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" s="64" t="str">
+        <f t="shared" ref="L15" si="35">_xlfn.CONCAT(C15)</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M13" s="31" t="str">
-        <f t="shared" si="24"/>
+      <c r="M15" s="64" t="str">
+        <f t="shared" si="30"/>
         <v>TGB</v>
       </c>
-      <c r="N13" s="31" t="str">
-        <f t="shared" si="25"/>
+      <c r="N15" s="64" t="str">
+        <f t="shared" si="31"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O13" s="31" t="str">
-        <f t="shared" si="26"/>
+      <c r="O15" s="64" t="str">
+        <f t="shared" si="3"/>
         <v>Reflexão</v>
       </c>
-      <c r="P13" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q13" s="31" t="str">
+      <c r="P15" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q15" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Reflexión</v>
-      </c>
-      <c r="R13" s="50" t="s">
+        <v>Reflexión. Transformación de un punto respecto a un eje de simetría. Eje de puntos preciso 1 y eje de puntos2.</v>
+      </c>
+      <c r="R15" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="S13" s="33" t="str">
-        <f t="shared" si="27"/>
+      <c r="S15" s="66" t="str">
+        <f t="shared" si="32"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T13" s="33" t="str">
-        <f t="shared" si="28"/>
+      <c r="T15" s="66" t="str">
+        <f t="shared" si="33"/>
         <v>TGB</v>
       </c>
-      <c r="U13" s="32" t="str">
-        <f t="shared" si="29"/>
+      <c r="U15" s="67" t="str">
+        <f t="shared" si="34"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="V13" s="34" t="s">
+      <c r="V15" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W13" s="35" t="str">
+      <c r="W15" s="68" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.13</v>
       </c>
-      <c r="X13" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="58" t="str">
+      <c r="X15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Reflection</v>
+        <v>Reflection. Transformation of a point with respect to an axis of symmetry. Precise Point Axis1 and Point Axis2.</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:Z1 AA1:AA13 A2:C2 A3:A13">
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:Z1 AA1:AA15">
+    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10:E13">
-    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E9 F2:Z13 B3:C9">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:Z15">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F7">
-    <cfRule type="duplicateValues" dxfId="11" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F13">
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+  <conditionalFormatting sqref="F8:F15">
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+  <conditionalFormatting sqref="F16:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4359,72 +4559,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="N1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="44" t="s">
+      <c r="O1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="44" t="s">
+      <c r="P1" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="44" t="s">
+      <c r="Q1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="44" t="s">
+      <c r="R1" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="44" t="s">
+      <c r="S1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="44" t="s">
+      <c r="U1" s="39" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="43">
+      <c r="A2" s="38">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -4489,7 +4689,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="43">
+      <c r="A3" s="38">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -4556,7 +4756,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4576,13 +4776,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40">
-        <v>1</v>
-      </c>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="35">
+        <v>1</v>
+      </c>
+      <c r="B1" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="36" t="s">
         <v>96</v>
       </c>
     </row>
@@ -4590,16 +4790,16 @@
       <c r="A2" s="19">
         <v>2</v>
       </c>
-      <c r="B2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="42" t="s">
+      <c r="B2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4609,668 +4809,951 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
-    <col min="4" max="11" width="2.7109375" style="51" customWidth="1"/>
+    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" customWidth="1"/>
+    <col min="4" max="11" width="3.42578125" style="45" customWidth="1"/>
     <col min="12" max="12" width="5" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="45" customWidth="1"/>
-    <col min="15" max="15" width="3.5703125" style="64" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" style="45" customWidth="1"/>
-    <col min="17" max="17" width="3.42578125" style="46" customWidth="1"/>
-    <col min="18" max="18" width="6.85546875" style="46" customWidth="1"/>
-    <col min="19" max="23" width="3.42578125" style="46" customWidth="1"/>
+    <col min="13" max="13" width="27.140625" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="40" customWidth="1"/>
+    <col min="15" max="15" width="4.28515625" style="58" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" style="40" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="41" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" style="41" customWidth="1"/>
+    <col min="19" max="19" width="3.42578125" style="41" customWidth="1"/>
+    <col min="20" max="20" width="6.5703125" style="41" customWidth="1"/>
+    <col min="21" max="21" width="3.42578125" style="41" customWidth="1"/>
+    <col min="22" max="22" width="7.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="41" customWidth="1"/>
+    <col min="24" max="24" width="12" style="41" customWidth="1"/>
+    <col min="25" max="25" width="4.42578125" style="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="J1" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="K1" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="54" t="s">
+      <c r="O1" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="V1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="37" t="s">
+      <c r="W1" s="32" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36">
+      <c r="X1" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" s="48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31">
         <v>2</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="N2" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="O2" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="P2" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q2" s="57">
+        <v>1.05</v>
+      </c>
+      <c r="R2" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="S2" s="57">
+        <v>1.05</v>
+      </c>
+      <c r="T2" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="U2" s="57">
+        <v>1.05</v>
+      </c>
+      <c r="V2" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W2" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X2" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y2" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31">
+        <v>3</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M3" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="P3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W3" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X3" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y3" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="31">
+        <v>4</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M4" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="N4" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="O4" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="P4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W4" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X4" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y4" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31">
+        <v>5</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M5" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="N5" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="O5" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="P5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W5" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X5" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y5" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="31">
+        <v>6</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="N6" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q6" s="57">
+        <v>1.05</v>
+      </c>
+      <c r="R6" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="S6" s="57">
+        <v>1.05</v>
+      </c>
+      <c r="T6" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="U6" s="57">
+        <v>1.05</v>
+      </c>
+      <c r="V6" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W6" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X6" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y6" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="31">
+        <v>7</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M7" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="N7" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="O7" s="57">
+        <v>10.5</v>
+      </c>
+      <c r="P7" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W7" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X7" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y7" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31">
+        <v>8</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="N8" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="O8" s="57">
+        <v>35</v>
+      </c>
+      <c r="P8" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W8" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X8" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y8" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31">
+        <v>9</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="O9" s="57">
+        <v>20.2</v>
+      </c>
+      <c r="P9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W9" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="X9" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y9" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="31">
+        <v>10</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="N10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q10" s="57">
+        <v>15.05</v>
+      </c>
+      <c r="R10" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="S10" s="57">
+        <v>23.05</v>
+      </c>
+      <c r="T10" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="U10" s="57">
+        <v>0.05</v>
+      </c>
+      <c r="V10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31">
+        <v>11</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="47" t="s">
+      <c r="D11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="N2" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="O2" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="P2" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q2" s="63">
-        <v>1.05</v>
-      </c>
-      <c r="R2" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="S2" s="63">
-        <v>1.05</v>
-      </c>
-      <c r="T2" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="U2" s="63">
-        <v>1.05</v>
-      </c>
-      <c r="V2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="52" t="str">
-        <f>IF(OR(V2="rgb",V2="cmy",V2="rgba",V2="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O2,".",Q2,".",S2,".",U2,""""), ".null",""), V2)</f>
-        <v>null</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36">
-        <v>3</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="62" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="47" t="s">
+      <c r="M11" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="N11" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="O11" s="57">
+        <v>0</v>
+      </c>
+      <c r="P11" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W11" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="X11" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y11" s="63" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="31">
+        <v>12</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="M3" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="O3" s="63" t="s">
-        <v>136</v>
-      </c>
-      <c r="P3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W3" s="52" t="str">
-        <f t="shared" ref="W3" si="0">IF(OR(V3="rgb",V3="cmy",V3="rgba",V3="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O3,".",Q3,".",S3,".",U3,""""), ".null",""), V3)</f>
-        <v>null</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36">
-        <v>4</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="M4" s="52" t="s">
-        <v>132</v>
-      </c>
-      <c r="N4" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="O4" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="52" t="str">
-        <f>IF(OR(V4="rgb",V4="cmy",V4="rgba",V4="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O4,".",Q4,".",S4,".",U4,""""), ".null",""), V4)</f>
-        <v>null</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36">
-        <v>5</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="62" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="M5" s="52" t="s">
-        <v>133</v>
-      </c>
-      <c r="N5" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="O5" s="63" t="s">
-        <v>138</v>
-      </c>
-      <c r="P5" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="52" t="str">
-        <f t="shared" ref="W5:W6" si="1">IF(OR(V5="rgb",V5="cmy",V5="rgba",V5="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O5,".",Q5,".",S5,".",U5,""""), ".null",""), V5)</f>
-        <v>null</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36">
-        <v>7</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="M6" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="N6" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="O6" s="63">
-        <v>1.05</v>
-      </c>
-      <c r="P6" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q6" s="63">
-        <v>1.05</v>
-      </c>
-      <c r="R6" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="S6" s="63">
-        <v>1.05</v>
-      </c>
-      <c r="T6" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="U6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="52" t="str">
-        <f t="shared" si="1"/>
-        <v>null</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36">
-        <v>6</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="M7" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="N7" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="O7" s="63">
-        <v>10.5</v>
-      </c>
-      <c r="P7" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="52" t="str">
-        <f t="shared" ref="W7" si="2">IF(OR(V7="rgb",V7="cmy",V7="rgba",V7="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O7,".",Q7,".",S7,".",U7,""""), ".null",""), V7)</f>
-        <v>null</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36">
-        <v>8</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="M8" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="N8" s="48" t="s">
+      <c r="M12" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="N12" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="O12" s="57">
+        <v>90</v>
+      </c>
+      <c r="P12" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U12" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="W12" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="X12" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y12" s="63" t="s">
         <v>166</v>
-      </c>
-      <c r="O8" s="63">
-        <v>35</v>
-      </c>
-      <c r="P8" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="52" t="str">
-        <f t="shared" ref="W8" si="3">IF(OR(V8="rgb",V8="cmy",V8="rgba",V8="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O8,".",Q8,".",S8,".",U8,""""), ".null",""), V8)</f>
-        <v>null</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" s="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36">
-        <v>9</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="C9" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="N9" s="48" t="s">
-        <v>166</v>
-      </c>
-      <c r="O9" s="63">
-        <v>20.2</v>
-      </c>
-      <c r="P9" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="52" t="str">
-        <f t="shared" ref="W9" si="4">IF(OR(V9="rgb",V9="cmy",V9="rgba",V9="cmyb"),  SUBSTITUTE(_xlfn.CONCAT("""",O9,".",Q9,".",S9,".",U9,""""), ".null",""), V9)</f>
-        <v>null</v>
       </c>
     </row>
   </sheetData>
@@ -5278,28 +5761,16 @@
     <sortCondition ref="C1:C2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:XFD1 A2:B9 A10:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="equal">
+  <conditionalFormatting sqref="A1:B1048576">
+    <cfRule type="cellIs" dxfId="2" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
-    <cfRule type="duplicateValues" dxfId="4" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:XFD9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="D1:M1048576 Z1:XFD1048576">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC6BFC3-A3FD-4AF9-9422-EE5BCD57C3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629B8F87-4E92-4D87-AD41-7889374FF91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="185">
   <si>
     <t>Key</t>
   </si>
@@ -1726,19 +1726,7 @@
     <t>Va2</t>
   </si>
   <si>
-    <t>valor.angular</t>
-  </si>
-  <si>
-    <t>valor.transladar</t>
-  </si>
-  <si>
     <t>"Um valor do deslocamento"</t>
-  </si>
-  <si>
-    <t>plano.da.transfornação</t>
-  </si>
-  <si>
-    <t>"XY"</t>
   </si>
   <si>
     <t>é.ponto.base</t>
@@ -2191,7 +2179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2366,12 +2354,6 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2391,21 +2373,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3006,7 +2983,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46142.515520833331</v>
+        <v>46142.531605902775</v>
       </c>
       <c r="C18" s="53" t="s">
         <v>105</v>
@@ -3254,48 +3231,48 @@
       <c r="K2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="64" t="str">
+      <c r="L2" s="62" t="str">
         <f t="shared" ref="L2:L14" si="0">_xlfn.CONCAT(C2)</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M2" s="64" t="str">
+      <c r="M2" s="62" t="str">
         <f t="shared" ref="M2" si="1">_xlfn.CONCAT("", D2)</f>
         <v>TGB</v>
       </c>
-      <c r="N2" s="64" t="str">
+      <c r="N2" s="62" t="str">
         <f t="shared" ref="N2" si="2">_xlfn.CONCAT("", E2)</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O2" s="64" t="str">
+      <c r="O2" s="62" t="str">
         <f t="shared" ref="O2:O15" si="3">_xlfn.CONCAT("", F2)</f>
         <v>Valor.X</v>
       </c>
-      <c r="P2" s="64" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q2" s="64" t="str">
+      <c r="P2" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q2" s="62" t="str">
         <f t="shared" ref="Q2:Q15" si="4">_xlfn.TRANSLATE(P2,"pt","es")</f>
         <v>Valor de X. Coordenada X.</v>
       </c>
-      <c r="R2" s="65" t="s">
+      <c r="R2" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S2" s="66" t="str">
+      <c r="S2" s="64" t="str">
         <f t="shared" ref="S2" si="5">SUBSTITUTE(C2, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T2" s="66" t="str">
+      <c r="T2" s="64" t="str">
         <f t="shared" ref="T2" si="6">SUBSTITUTE(D2, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U2" s="67" t="str">
+      <c r="U2" s="65" t="str">
         <f t="shared" ref="U2" si="7">SUBSTITUTE(E2, "_", " ")</f>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V2" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W2" s="68" t="str">
+      <c r="W2" s="66" t="str">
         <f>CONCATENATE("Key.EGC",".",A2)</f>
         <v>Key.EGC.2</v>
       </c>
@@ -3347,48 +3324,48 @@
       <c r="K3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="64" t="str">
+      <c r="L3" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M3" s="64" t="str">
+      <c r="M3" s="62" t="str">
         <f t="shared" ref="M3:N3" si="9">_xlfn.CONCAT("", D3)</f>
         <v>TGB</v>
       </c>
-      <c r="N3" s="64" t="str">
+      <c r="N3" s="62" t="str">
         <f t="shared" si="9"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O3" s="64" t="str">
+      <c r="O3" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Valor.Y</v>
       </c>
-      <c r="P3" s="64" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q3" s="64" t="str">
+      <c r="P3" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q3" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Valor de Y. Coordenada Y.</v>
       </c>
-      <c r="R3" s="65" t="s">
+      <c r="R3" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="66" t="str">
+      <c r="S3" s="64" t="str">
         <f t="shared" ref="S3:U3" si="10">SUBSTITUTE(C3, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T3" s="66" t="str">
+      <c r="T3" s="64" t="str">
         <f t="shared" si="10"/>
         <v>TGB</v>
       </c>
-      <c r="U3" s="67" t="str">
+      <c r="U3" s="65" t="str">
         <f t="shared" si="10"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V3" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W3" s="68" t="str">
+      <c r="W3" s="66" t="str">
         <f t="shared" ref="W3:W15" si="11">CONCATENATE("Key.EGC",".",A3)</f>
         <v>Key.EGC.3</v>
       </c>
@@ -3440,48 +3417,48 @@
       <c r="K4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="64" t="str">
+      <c r="L4" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M4" s="64" t="str">
+      <c r="M4" s="62" t="str">
         <f t="shared" ref="M4:M11" si="12">_xlfn.CONCAT("", D4)</f>
         <v>TGB</v>
       </c>
-      <c r="N4" s="64" t="str">
+      <c r="N4" s="62" t="str">
         <f t="shared" ref="N4:N11" si="13">_xlfn.CONCAT("", E4)</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O4" s="64" t="str">
+      <c r="O4" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Valor.Z</v>
       </c>
-      <c r="P4" s="64" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q4" s="64" t="str">
+      <c r="P4" s="62" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q4" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Valor Z. Coordenada Z.</v>
       </c>
-      <c r="R4" s="65" t="s">
+      <c r="R4" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S4" s="66" t="str">
+      <c r="S4" s="64" t="str">
         <f t="shared" ref="S4:S11" si="14">SUBSTITUTE(C4, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T4" s="66" t="str">
+      <c r="T4" s="64" t="str">
         <f t="shared" ref="T4:T11" si="15">SUBSTITUTE(D4, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U4" s="67" t="str">
+      <c r="U4" s="65" t="str">
         <f t="shared" ref="U4:U11" si="16">SUBSTITUTE(E4, "_", " ")</f>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V4" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W4" s="68" t="str">
+      <c r="W4" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.4</v>
       </c>
@@ -3533,48 +3510,48 @@
       <c r="K5" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L5" s="64" t="str">
+      <c r="L5" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M5" s="64" t="str">
+      <c r="M5" s="62" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N5" s="64" t="str">
+      <c r="N5" s="62" t="str">
         <f t="shared" si="13"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O5" s="64" t="str">
+      <c r="O5" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Valor.Deslocar</v>
       </c>
-      <c r="P5" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q5" s="64" t="str">
+      <c r="P5" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q5" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Valor desplazado. Valor de distancia de una traslación</v>
       </c>
-      <c r="R5" s="65" t="s">
+      <c r="R5" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S5" s="66" t="str">
+      <c r="S5" s="64" t="str">
         <f t="shared" si="14"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T5" s="66" t="str">
+      <c r="T5" s="64" t="str">
         <f t="shared" si="15"/>
         <v>TGB</v>
       </c>
-      <c r="U5" s="67" t="str">
+      <c r="U5" s="65" t="str">
         <f t="shared" si="16"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V5" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W5" s="68" t="str">
+      <c r="W5" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.5</v>
       </c>
@@ -3626,48 +3603,48 @@
       <c r="K6" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L6" s="64" t="str">
+      <c r="L6" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M6" s="64" t="str">
+      <c r="M6" s="62" t="str">
         <f t="shared" ref="M6" si="17">_xlfn.CONCAT("", D6)</f>
         <v>TGB</v>
       </c>
-      <c r="N6" s="64" t="str">
+      <c r="N6" s="62" t="str">
         <f t="shared" ref="N6" si="18">_xlfn.CONCAT("", E6)</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O6" s="64" t="str">
+      <c r="O6" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Valor.Angular</v>
       </c>
-      <c r="P6" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q6" s="64" t="str">
+      <c r="P6" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q6" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Valor angular de una transformada de espín o rotación</v>
       </c>
-      <c r="R6" s="65" t="s">
+      <c r="R6" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S6" s="66" t="str">
+      <c r="S6" s="64" t="str">
         <f t="shared" ref="S6" si="19">SUBSTITUTE(C6, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T6" s="66" t="str">
+      <c r="T6" s="64" t="str">
         <f t="shared" ref="T6" si="20">SUBSTITUTE(D6, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U6" s="67" t="str">
+      <c r="U6" s="65" t="str">
         <f t="shared" ref="U6" si="21">SUBSTITUTE(E6, "_", " ")</f>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V6" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W6" s="68" t="str">
+      <c r="W6" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.6</v>
       </c>
@@ -3719,48 +3696,48 @@
       <c r="K7" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L7" s="64" t="str">
+      <c r="L7" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M7" s="64" t="str">
+      <c r="M7" s="62" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N7" s="64" t="str">
+      <c r="N7" s="62" t="str">
         <f t="shared" si="13"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O7" s="64" t="str">
+      <c r="O7" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Valor.Escalar</v>
       </c>
-      <c r="P7" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q7" s="64" t="str">
+      <c r="P7" s="62" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q7" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Valor escalar de una transformación que cambia la escala</v>
       </c>
-      <c r="R7" s="65" t="s">
+      <c r="R7" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S7" s="66" t="str">
+      <c r="S7" s="64" t="str">
         <f t="shared" si="14"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T7" s="66" t="str">
+      <c r="T7" s="64" t="str">
         <f t="shared" si="15"/>
         <v>TGB</v>
       </c>
-      <c r="U7" s="67" t="str">
+      <c r="U7" s="65" t="str">
         <f t="shared" si="16"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V7" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W7" s="68" t="str">
+      <c r="W7" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.7</v>
       </c>
@@ -3792,10 +3769,10 @@
         <v>118</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G8" s="30" t="s">
         <v>1</v>
@@ -3812,48 +3789,48 @@
       <c r="K8" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="64" t="str">
+      <c r="L8" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M8" s="64" t="str">
+      <c r="M8" s="62" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N8" s="64" t="str">
+      <c r="N8" s="62" t="str">
         <f t="shared" si="13"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="O8" s="64" t="str">
+      <c r="O8" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Ponto.Eixo1</v>
       </c>
-      <c r="P8" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q8" s="64" t="str">
+      <c r="P8" s="62" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q8" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Punto 1 que define un eje de simetría</v>
       </c>
-      <c r="R8" s="65" t="s">
+      <c r="R8" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S8" s="66" t="str">
+      <c r="S8" s="64" t="str">
         <f t="shared" si="14"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T8" s="66" t="str">
+      <c r="T8" s="64" t="str">
         <f t="shared" si="15"/>
         <v>TGB</v>
       </c>
-      <c r="U8" s="67" t="str">
+      <c r="U8" s="65" t="str">
         <f t="shared" si="16"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V8" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W8" s="68" t="str">
+      <c r="W8" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.8</v>
       </c>
@@ -3885,10 +3862,10 @@
         <v>118</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G9" s="30" t="s">
         <v>1</v>
@@ -3905,48 +3882,48 @@
       <c r="K9" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="64" t="str">
+      <c r="L9" s="62" t="str">
         <f t="shared" ref="L9" si="22">_xlfn.CONCAT(C9)</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M9" s="64" t="str">
+      <c r="M9" s="62" t="str">
         <f t="shared" ref="M9" si="23">_xlfn.CONCAT("", D9)</f>
         <v>TGB</v>
       </c>
-      <c r="N9" s="64" t="str">
+      <c r="N9" s="62" t="str">
         <f t="shared" ref="N9" si="24">_xlfn.CONCAT("", E9)</f>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="O9" s="64" t="str">
+      <c r="O9" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Ponto.Eixo2</v>
       </c>
-      <c r="P9" s="64" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q9" s="64" t="str">
+      <c r="P9" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q9" s="62" t="str">
         <f t="shared" ref="Q9" si="25">_xlfn.TRANSLATE(P9,"pt","es")</f>
         <v>Punto 2 que define un eje de simetría</v>
       </c>
-      <c r="R9" s="65" t="s">
+      <c r="R9" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S9" s="66" t="str">
+      <c r="S9" s="64" t="str">
         <f t="shared" ref="S9" si="26">SUBSTITUTE(C9, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T9" s="66" t="str">
+      <c r="T9" s="64" t="str">
         <f t="shared" ref="T9" si="27">SUBSTITUTE(D9, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U9" s="67" t="str">
+      <c r="U9" s="65" t="str">
         <f t="shared" ref="U9" si="28">SUBSTITUTE(E9, "_", " ")</f>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V9" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W9" s="68" t="str">
+      <c r="W9" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.8</v>
       </c>
@@ -3978,7 +3955,7 @@
         <v>118</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F10" s="56" t="s">
         <v>126</v>
@@ -3998,48 +3975,48 @@
       <c r="K10" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L10" s="64" t="str">
+      <c r="L10" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M10" s="64" t="str">
+      <c r="M10" s="62" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N10" s="64" t="str">
+      <c r="N10" s="62" t="str">
         <f t="shared" si="13"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="O10" s="64" t="str">
+      <c r="O10" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Ponto.Base</v>
       </c>
-      <c r="P10" s="64" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q10" s="64" t="str">
+      <c r="P10" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q10" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
       </c>
-      <c r="R10" s="65" t="s">
+      <c r="R10" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S10" s="66" t="str">
+      <c r="S10" s="64" t="str">
         <f t="shared" si="14"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T10" s="66" t="str">
+      <c r="T10" s="64" t="str">
         <f t="shared" si="15"/>
         <v>TGB</v>
       </c>
-      <c r="U10" s="67" t="str">
+      <c r="U10" s="65" t="str">
         <f t="shared" si="16"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V10" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W10" s="68" t="str">
+      <c r="W10" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.8</v>
       </c>
@@ -4071,7 +4048,7 @@
         <v>118</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F11" s="56" t="s">
         <v>127</v>
@@ -4091,48 +4068,48 @@
       <c r="K11" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="64" t="str">
+      <c r="L11" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M11" s="64" t="str">
+      <c r="M11" s="62" t="str">
         <f t="shared" si="12"/>
         <v>TGB</v>
       </c>
-      <c r="N11" s="64" t="str">
+      <c r="N11" s="62" t="str">
         <f t="shared" si="13"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="O11" s="64" t="str">
+      <c r="O11" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Ponto.Destino</v>
       </c>
-      <c r="P11" s="64" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q11" s="64" t="str">
+      <c r="P11" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q11" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Punto final de un vector de traslación</v>
       </c>
-      <c r="R11" s="65" t="s">
+      <c r="R11" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S11" s="66" t="str">
+      <c r="S11" s="64" t="str">
         <f t="shared" si="14"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T11" s="66" t="str">
+      <c r="T11" s="64" t="str">
         <f t="shared" si="15"/>
         <v>TGB</v>
       </c>
-      <c r="U11" s="67" t="str">
+      <c r="U11" s="65" t="str">
         <f t="shared" si="16"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V11" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W11" s="68" t="str">
+      <c r="W11" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.9</v>
       </c>
@@ -4184,47 +4161,47 @@
       <c r="K12" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="L12" s="64" t="str">
+      <c r="L12" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M12" s="64" t="str">
+      <c r="M12" s="62" t="str">
         <f t="shared" ref="M12:M15" si="30">_xlfn.CONCAT("", D12)</f>
         <v>TGB</v>
       </c>
-      <c r="N12" s="64" t="str">
+      <c r="N12" s="62" t="str">
         <f t="shared" ref="N12:N15" si="31">_xlfn.CONCAT("", E12)</f>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O12" s="64" t="str">
+      <c r="O12" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Translação</v>
       </c>
-      <c r="P12" s="64" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q12" s="64" t="s">
+      <c r="P12" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q12" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="R12" s="65" t="s">
+      <c r="R12" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S12" s="66" t="str">
+      <c r="S12" s="64" t="str">
         <f t="shared" ref="S12:S15" si="32">SUBSTITUTE(C12, "_", " ")</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T12" s="66" t="str">
+      <c r="T12" s="64" t="str">
         <f t="shared" ref="T12:T15" si="33">SUBSTITUTE(D12, "_", " ")</f>
         <v>TGB</v>
       </c>
-      <c r="U12" s="67" t="str">
+      <c r="U12" s="65" t="str">
         <f t="shared" ref="U12:U15" si="34">SUBSTITUTE(E12, "_", " ")</f>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V12" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W12" s="68" t="str">
+      <c r="W12" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.10</v>
       </c>
@@ -4276,48 +4253,48 @@
       <c r="K13" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="L13" s="64" t="str">
+      <c r="L13" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M13" s="64" t="str">
+      <c r="M13" s="62" t="str">
         <f t="shared" si="30"/>
         <v>TGB</v>
       </c>
-      <c r="N13" s="64" t="str">
+      <c r="N13" s="62" t="str">
         <f t="shared" si="31"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O13" s="64" t="str">
+      <c r="O13" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Giro</v>
       </c>
-      <c r="P13" s="64" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q13" s="64" t="str">
+      <c r="P13" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q13" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Giro. La transformación que transforma la posición de un punto con un desplazamiento circular. Punto base y ángulo precisos.</v>
       </c>
-      <c r="R13" s="65" t="s">
+      <c r="R13" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S13" s="66" t="str">
+      <c r="S13" s="64" t="str">
         <f t="shared" si="32"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T13" s="66" t="str">
+      <c r="T13" s="64" t="str">
         <f t="shared" si="33"/>
         <v>TGB</v>
       </c>
-      <c r="U13" s="67" t="str">
+      <c r="U13" s="65" t="str">
         <f t="shared" si="34"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V13" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W13" s="68" t="str">
+      <c r="W13" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.11</v>
       </c>
@@ -4369,48 +4346,48 @@
       <c r="K14" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="L14" s="64" t="str">
+      <c r="L14" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M14" s="64" t="str">
+      <c r="M14" s="62" t="str">
         <f t="shared" si="30"/>
         <v>TGB</v>
       </c>
-      <c r="N14" s="64" t="str">
+      <c r="N14" s="62" t="str">
         <f t="shared" si="31"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O14" s="64" t="str">
+      <c r="O14" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Escalar</v>
       </c>
-      <c r="P14" s="64" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q14" s="64" t="str">
+      <c r="P14" s="62" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q14" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Escala. Agrandamiento o reducción de una forma en relación con un centro homotético.  Necesito punto base y factor escalar.</v>
       </c>
-      <c r="R14" s="65" t="s">
+      <c r="R14" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S14" s="66" t="str">
+      <c r="S14" s="64" t="str">
         <f t="shared" si="32"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T14" s="66" t="str">
+      <c r="T14" s="64" t="str">
         <f t="shared" si="33"/>
         <v>TGB</v>
       </c>
-      <c r="U14" s="67" t="str">
+      <c r="U14" s="65" t="str">
         <f t="shared" si="34"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V14" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W14" s="68" t="str">
+      <c r="W14" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.12</v>
       </c>
@@ -4460,50 +4437,50 @@
         <v>1</v>
       </c>
       <c r="K15" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="L15" s="64" t="str">
+        <v>167</v>
+      </c>
+      <c r="L15" s="62" t="str">
         <f t="shared" ref="L15" si="35">_xlfn.CONCAT(C15)</f>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="M15" s="64" t="str">
+      <c r="M15" s="62" t="str">
         <f t="shared" si="30"/>
         <v>TGB</v>
       </c>
-      <c r="N15" s="64" t="str">
+      <c r="N15" s="62" t="str">
         <f t="shared" si="31"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O15" s="64" t="str">
+      <c r="O15" s="62" t="str">
         <f t="shared" si="3"/>
         <v>Reflexão</v>
       </c>
-      <c r="P15" s="64" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q15" s="64" t="str">
+      <c r="P15" s="62" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q15" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Reflexión. Transformación de un punto respecto a un eje de simetría. Eje de puntos preciso 1 y eje de puntos2.</v>
       </c>
-      <c r="R15" s="65" t="s">
+      <c r="R15" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="S15" s="66" t="str">
+      <c r="S15" s="64" t="str">
         <f t="shared" si="32"/>
         <v>Estrutura.Geométrica</v>
       </c>
-      <c r="T15" s="66" t="str">
+      <c r="T15" s="64" t="str">
         <f t="shared" si="33"/>
         <v>TGB</v>
       </c>
-      <c r="U15" s="67" t="str">
+      <c r="U15" s="65" t="str">
         <f t="shared" si="34"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V15" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="W15" s="68" t="str">
+      <c r="W15" s="66" t="str">
         <f t="shared" si="11"/>
         <v>Key.EGC.13</v>
       </c>
@@ -4524,23 +4501,23 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:Z1 AA1:AA15">
-    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:Z15">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F7">
-    <cfRule type="duplicateValues" dxfId="7" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F15">
-    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4756,7 +4733,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4799,7 +4776,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4809,7 +4786,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4818,21 +4795,23 @@
     <col min="4" max="11" width="3.42578125" style="45" customWidth="1"/>
     <col min="12" max="12" width="5" customWidth="1"/>
     <col min="13" max="13" width="27.140625" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="40" customWidth="1"/>
-    <col min="15" max="15" width="4.28515625" style="58" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" style="40" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="40" customWidth="1"/>
+    <col min="15" max="15" width="3.42578125" style="41" customWidth="1"/>
+    <col min="16" max="16" width="6.85546875" style="41" customWidth="1"/>
     <col min="17" max="17" width="3.42578125" style="41" customWidth="1"/>
-    <col min="18" max="18" width="6.85546875" style="41" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" style="41" customWidth="1"/>
     <col min="19" max="19" width="3.42578125" style="41" customWidth="1"/>
-    <col min="20" max="20" width="6.5703125" style="41" customWidth="1"/>
-    <col min="21" max="21" width="3.42578125" style="41" customWidth="1"/>
-    <col min="22" max="22" width="7.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="41" customWidth="1"/>
-    <col min="24" max="24" width="12" style="41" customWidth="1"/>
-    <col min="25" max="25" width="4.42578125" style="58" customWidth="1"/>
+    <col min="20" max="20" width="12" style="41" customWidth="1"/>
+    <col min="21" max="21" width="4.42578125" style="58" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" style="40" customWidth="1"/>
+    <col min="23" max="23" width="4.28515625" style="58" customWidth="1"/>
+    <col min="24" max="24" width="7.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12" style="41" customWidth="1"/>
+    <col min="27" max="27" width="4.42578125" style="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>92</v>
       </c>
@@ -4875,10 +4854,10 @@
       <c r="N1" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="O1" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="32" t="s">
         <v>48</v>
       </c>
       <c r="Q1" s="32" t="s">
@@ -4893,13 +4872,13 @@
       <c r="T1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="32" t="s">
+      <c r="U1" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="V1" s="32" t="s">
+      <c r="V1" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="32" t="s">
+      <c r="W1" s="48" t="s">
         <v>93</v>
       </c>
       <c r="X1" s="32" t="s">
@@ -4908,13 +4887,19 @@
       <c r="Y1" s="48" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z1" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" s="48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31">
         <v>2</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C2" s="56" t="s">
         <v>121</v>
@@ -4950,48 +4935,54 @@
         <v>116</v>
       </c>
       <c r="N2" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="O2" s="57" t="s">
-        <v>131</v>
+        <v>136</v>
+      </c>
+      <c r="O2" s="57">
+        <v>1.05</v>
       </c>
       <c r="P2" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q2" s="57">
         <v>1.05</v>
       </c>
       <c r="R2" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S2" s="57">
         <v>1.05</v>
       </c>
       <c r="T2" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="U2" s="57">
-        <v>1.05</v>
-      </c>
-      <c r="V2" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="W2" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="X2" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y2" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="X2" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y2" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>122</v>
@@ -5027,48 +5018,54 @@
         <v>117</v>
       </c>
       <c r="N3" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="O3" s="57">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P3" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q3" s="57">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="R3" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="S3" s="57">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="T3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="O3" s="57" t="s">
+      <c r="W3" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="P3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W3" s="60" t="s">
+      <c r="X3" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y3" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="X3" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y3" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>123</v>
@@ -5104,48 +5101,54 @@
         <v>128</v>
       </c>
       <c r="N4" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="O4" s="57">
+        <v>3.05</v>
+      </c>
+      <c r="P4" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q4" s="57">
+        <v>3.05</v>
+      </c>
+      <c r="R4" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="S4" s="57">
+        <v>3.05</v>
+      </c>
+      <c r="T4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="O4" s="57" t="s">
+      <c r="W4" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="P4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W4" s="60" t="s">
+      <c r="X4" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y4" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="X4" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y4" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>124</v>
@@ -5181,45 +5184,51 @@
         <v>129</v>
       </c>
       <c r="N5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="W5" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="P5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W5" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="X5" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y5" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>150</v>
@@ -5264,45 +5273,51 @@
         <v>1</v>
       </c>
       <c r="P6" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q6" s="57">
-        <v>1.05</v>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="R6" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="S6" s="57">
-        <v>1.05</v>
+        <v>1</v>
+      </c>
+      <c r="S6" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="T6" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="U6" s="57">
-        <v>1.05</v>
-      </c>
-      <c r="V6" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W6" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="X6" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y6" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>1</v>
@@ -5332,13 +5347,13 @@
         <v>97</v>
       </c>
       <c r="M7" s="46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="O7" s="57">
-        <v>10.5</v>
+        <v>1</v>
+      </c>
+      <c r="O7" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="P7" s="43" t="s">
         <v>1</v>
@@ -5355,31 +5370,37 @@
       <c r="T7" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="U7" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="59" t="s">
+      <c r="U7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31">
+        <v>2</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="W7" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="X7" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y7" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
-        <v>8</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>152</v>
-      </c>
       <c r="C8" s="56" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>1</v>
@@ -5409,13 +5430,13 @@
         <v>97</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="O8" s="57">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="O8" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="P8" s="43" t="s">
         <v>1</v>
@@ -5432,31 +5453,37 @@
       <c r="T8" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="U8" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W8" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="X8" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y8" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y8" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z8" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA8" s="61" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="D9" s="49" t="s">
         <v>1</v>
@@ -5486,13 +5513,13 @@
         <v>97</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="O9" s="57">
-        <v>20.2</v>
+        <v>1</v>
+      </c>
+      <c r="O9" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="P9" s="43" t="s">
         <v>1</v>
@@ -5509,31 +5536,37 @@
       <c r="T9" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="U9" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W9" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="X9" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y9" s="57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y9" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z9" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA9" s="61" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>1</v>
@@ -5563,7 +5596,7 @@
         <v>97</v>
       </c>
       <c r="M10" s="46" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N10" s="43" t="s">
         <v>1</v>
@@ -5572,45 +5605,51 @@
         <v>1</v>
       </c>
       <c r="P10" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q10" s="57">
-        <v>15.05</v>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="R10" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="S10" s="57">
-        <v>23.05</v>
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="T10" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="U10" s="57">
-        <v>0.05</v>
-      </c>
-      <c r="V10" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="57" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>1</v>
@@ -5640,13 +5679,13 @@
         <v>97</v>
       </c>
       <c r="M11" s="46" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="N11" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="O11" s="57">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O11" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="P11" s="43" t="s">
         <v>1</v>
@@ -5663,31 +5702,37 @@
       <c r="T11" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="U11" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V11" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W11" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="X11" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y11" s="63" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="67" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>1</v>
@@ -5717,13 +5762,13 @@
         <v>97</v>
       </c>
       <c r="M12" s="46" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="O12" s="57">
-        <v>90</v>
+        <v>1</v>
+      </c>
+      <c r="O12" s="46" t="s">
+        <v>1</v>
       </c>
       <c r="P12" s="43" t="s">
         <v>1</v>
@@ -5740,39 +5785,40 @@
       <c r="T12" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="U12" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V12" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="W12" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="X12" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y12" s="63" t="s">
-        <v>166</v>
+      <c r="U12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="67" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U2">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="cellIs" dxfId="2" priority="30" operator="equal">
+  <conditionalFormatting sqref="D1:M1048576 AB1:XFD1048576 A1:B1048576">
+    <cfRule type="cellIs" dxfId="1" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:M1048576 Z1:XFD1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629B8F87-4E92-4D87-AD41-7889374FF91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFDBE71-8676-44F2-8270-BB7655332AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
     <sheet name="Classes" sheetId="31" r:id="rId2"/>
     <sheet name="Disjunt" sheetId="3" r:id="rId3"/>
     <sheet name="Interop" sheetId="27" r:id="rId4"/>
-    <sheet name="FatosIn" sheetId="30" r:id="rId5"/>
+    <sheet name="FatosIn" sheetId="32" r:id="rId5"/>
     <sheet name="ExemplosDL" sheetId="24" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="223">
   <si>
     <t>Key</t>
   </si>
@@ -1534,9 +1534,6 @@
     <t>Especie</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>Interdisciplinar</t>
   </si>
   <si>
@@ -1618,12 +1615,6 @@
     <t>"Uma rotação"</t>
   </si>
   <si>
-    <t>TGB</t>
-  </si>
-  <si>
-    <t>Estrutura.Geométrica</t>
-  </si>
-  <si>
     <t>Movimento.Geométrico</t>
   </si>
   <si>
@@ -1711,9 +1702,6 @@
     <t xml:space="preserve">( Valor.Deslocar and Valor.Angular ) or ( Valor.X and Valor.Y and Valor.Z ) </t>
   </si>
   <si>
-    <t>Translación</t>
-  </si>
-  <si>
     <t>PB1</t>
   </si>
   <si>
@@ -1817,6 +1805,132 @@
   </si>
   <si>
     <t>Bases.Geométricas</t>
+  </si>
+  <si>
+    <t>Gestão</t>
+  </si>
+  <si>
+    <t>Contêiner</t>
+  </si>
+  <si>
+    <t>Informação</t>
+  </si>
+  <si>
+    <t>Definida</t>
+  </si>
+  <si>
+    <t>No.Projeto</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
+  </si>
+  <si>
+    <t>Requerida</t>
+  </si>
+  <si>
+    <t>Requisito.Espacial</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Mobiliário</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Equipamento</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Sistemas</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Formal</t>
+  </si>
+  <si>
+    <t>Elementos.TGB</t>
+  </si>
+  <si>
+    <t>Punto final de un vector de traslación</t>
+  </si>
+  <si>
+    <t>La transformación que modifica la posición de un punto mediante un desplazamiento lineal. Necesita punto base y punto objetivo.</t>
+  </si>
+  <si>
+    <t>Transformación de un punto respecto a un eje de simetría. Define el eje de simetría por 2 puntos.</t>
+  </si>
+  <si>
+    <t>Aumento o reducción de una forma en relación con un centro homotético. Necesita punto base y factor escalar.</t>
+  </si>
+  <si>
+    <t>La transformación que modifica la posición de un punto mediante un desplazamiento circular. Necesita punto base y ángulo de rotación.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Value of X. Coordinate X.</t>
+  </si>
+  <si>
+    <t>Value of Y. Y-coordinate.</t>
+  </si>
+  <si>
+    <t>Z Value. Z Coordinate.</t>
+  </si>
+  <si>
+    <t>Displace Value. Distance Value of a Translation</t>
+  </si>
+  <si>
+    <t>Angular Value of a Spin or Rotation Transform</t>
+  </si>
+  <si>
+    <t>Scalar Value of a Scale-Changing Transformation</t>
+  </si>
+  <si>
+    <t>Point 1 that defines a symmetry axis</t>
+  </si>
+  <si>
+    <t>Point 2 that defines a symmetry axis</t>
+  </si>
+  <si>
+    <t>Base point that can serve as the first base point of a translation vector or to reference a project</t>
+  </si>
+  <si>
+    <t>Endpoint of a translational vector</t>
+  </si>
+  <si>
+    <t>The transformation that modifies the position of a point by means of a linear displacement. You need base point and target point.</t>
+  </si>
+  <si>
+    <t>The transformation that modifies the position of a point by means of a circular displacement. Needs base point and rotation angle.</t>
+  </si>
+  <si>
+    <t>Increase or decrease of a shape in relation to a homothetic center. You need base point and scalar factor.</t>
+  </si>
+  <si>
+    <t>Transformation of a point with respect to an axis of symmetry. Define the axis of symmetry by 2 points.</t>
   </si>
 </sst>
 </file>
@@ -2000,7 +2114,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2035,12 +2149,6 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -2179,7 +2287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2198,10 +2306,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2213,13 +2321,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2231,29 +2339,23 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2264,28 +2366,25 @@
     <xf numFmtId="0" fontId="23" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2297,40 +2396,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2345,10 +2438,7 @@
     <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2357,32 +2447,118 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2415,6 +2591,62 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2784,7 +3016,7 @@
   <cols>
     <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
     <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
@@ -2795,8 +3027,8 @@
       <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="47" t="s">
-        <v>104</v>
+      <c r="C1" s="42" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2806,8 +3038,8 @@
       <c r="B2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="53" t="s">
-        <v>105</v>
+      <c r="C2" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2815,10 +3047,10 @@
         <v>61</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>105</v>
+        <v>111</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2828,8 +3060,8 @@
       <c r="B4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="53" t="s">
-        <v>105</v>
+      <c r="C4" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2840,8 +3072,8 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="53" t="s">
-        <v>105</v>
+      <c r="C5" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2852,8 +3084,8 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="53" t="s">
-        <v>105</v>
+      <c r="C6" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2863,8 +3095,8 @@
       <c r="B7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>105</v>
+      <c r="C7" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2872,10 +3104,10 @@
         <v>56</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2885,8 +3117,8 @@
       <c r="B9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="53" t="s">
-        <v>105</v>
+      <c r="C9" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2896,8 +3128,8 @@
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="53" t="s">
-        <v>105</v>
+      <c r="C10" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2907,8 +3139,8 @@
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="53" t="s">
-        <v>105</v>
+      <c r="C11" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2918,8 +3150,8 @@
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="53" t="s">
-        <v>105</v>
+      <c r="C12" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2929,8 +3161,8 @@
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="53" t="s">
-        <v>105</v>
+      <c r="C13" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2940,8 +3172,8 @@
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="53" t="s">
-        <v>105</v>
+      <c r="C14" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2951,8 +3183,8 @@
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="53" t="s">
-        <v>105</v>
+      <c r="C15" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2962,8 +3194,8 @@
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="53" t="s">
-        <v>105</v>
+      <c r="C16" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2971,10 +3203,10 @@
         <v>59</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="53" t="s">
-        <v>105</v>
+        <v>112</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2983,45 +3215,45 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46142.531605902775</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46142.684945023146</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="55" t="str">
+        <v>107</v>
+      </c>
+      <c r="B20" s="50" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="53" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="40" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="48" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" s="55" t="str">
+        <v>108</v>
+      </c>
+      <c r="B21" s="50" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
-      <c r="C21" s="53" t="s">
-        <v>107</v>
+      <c r="C21" s="48" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3031,8 +3263,8 @@
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="53" t="s">
-        <v>105</v>
+      <c r="C22" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3042,8 +3274,8 @@
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="53" t="s">
-        <v>105</v>
+      <c r="C23" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3051,10 +3283,10 @@
         <v>74</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>105</v>
+        <v>113</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3062,22 +3294,22 @@
         <v>75</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>106</v>
+        <v>114</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of Genetically Constructed Structures</v>
       </c>
-      <c r="C26" s="53" t="s">
-        <v>107</v>
+      <c r="C26" s="48" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3087,30 +3319,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" customWidth="1"/>
     <col min="2" max="2" width="4.5703125" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="10" width="7.42578125" customWidth="1"/>
-    <col min="11" max="11" width="31.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="3.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="10" width="7.42578125" style="68" customWidth="1"/>
+    <col min="11" max="11" width="31.28515625" style="68" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="62.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="50.5703125" customWidth="1"/>
+    <col min="17" max="17" width="55" customWidth="1"/>
     <col min="18" max="18" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="10.7109375" customWidth="1"/>
-    <col min="22" max="22" width="6.85546875" customWidth="1"/>
+    <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7" customWidth="1"/>
-    <col min="24" max="26" width="6.42578125" customWidth="1"/>
+    <col min="24" max="25" width="6.42578125" customWidth="1"/>
+    <col min="26" max="26" width="5.140625" style="68" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="53.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3133,1391 +3366,1828 @@
       <c r="F1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="Q1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="44" t="s">
+      <c r="R1" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="S1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="T1" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="U1" s="25" t="s">
+      <c r="U1" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="V1" s="23" t="s">
+      <c r="V1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="W1" s="24" t="s">
+      <c r="W1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="23" t="s">
+      <c r="X1" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y1" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="Y1" s="23" t="s">
+      <c r="Z1" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="Z1" s="23" t="s">
+      <c r="AA1" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="AA1" s="51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+    </row>
+    <row r="2" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="61">
         <v>2</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="62" t="str">
-        <f t="shared" ref="L2:L14" si="0">_xlfn.CONCAT(C2)</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M2" s="62" t="str">
-        <f t="shared" ref="M2" si="1">_xlfn.CONCAT("", D2)</f>
-        <v>TGB</v>
-      </c>
-      <c r="N2" s="62" t="str">
-        <f t="shared" ref="N2" si="2">_xlfn.CONCAT("", E2)</f>
+      <c r="B2" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="63" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="G2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="58" t="str">
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="M2" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N2" s="58" t="str">
+        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Definida</v>
+      </c>
+      <c r="O2" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>No Projeto</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="R2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="57" t="str">
+        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="T2" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U2" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Definida</v>
+      </c>
+      <c r="V2" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W2" s="59" t="str">
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.EGC",".",A2)</f>
+        <v>Key.EGC.2</v>
+      </c>
+      <c r="X2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="61">
+        <v>3</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="G3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M3" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N3" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O3" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Espacial</v>
+      </c>
+      <c r="P3" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q3" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="R3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T3" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U3" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V3" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key.EGC.3</v>
+      </c>
+      <c r="X3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="47" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="61">
+        <v>4</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="G4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M4" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N4" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O4" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Mobiliário</v>
+      </c>
+      <c r="P4" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q4" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="R4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T4" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U4" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V4" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W4" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key.EGC.4</v>
+      </c>
+      <c r="X4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="47" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="61">
+        <v>5</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M5" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N5" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O5" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Equipamento</v>
+      </c>
+      <c r="P5" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q5" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="R5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T5" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U5" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V5" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W5" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key.EGC.5</v>
+      </c>
+      <c r="X5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="47" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="61">
+        <v>6</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M6" s="58" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N6" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O6" s="58" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Sistemas</v>
+      </c>
+      <c r="P6" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q6" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="R6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T6" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U6" s="57" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V6" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W6" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key.EGC.6</v>
+      </c>
+      <c r="X6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="47" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="61">
+        <v>7</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="56" t="str">
+        <f t="shared" ref="L7:L19" si="4">_xlfn.CONCAT(C7)</f>
+        <v>Formal</v>
+      </c>
+      <c r="M7" s="56" t="str">
+        <f t="shared" ref="M7" si="5">_xlfn.CONCAT("", D7)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N7" s="56" t="str">
+        <f t="shared" ref="N7" si="6">_xlfn.CONCAT("", E7)</f>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O2" s="62" t="str">
-        <f t="shared" ref="O2:O15" si="3">_xlfn.CONCAT("", F2)</f>
+      <c r="O7" s="56" t="str">
+        <f t="shared" ref="O7:O20" si="7">_xlfn.CONCAT("", F7)</f>
         <v>Valor.X</v>
       </c>
-      <c r="P2" s="62" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q2" s="62" t="str">
-        <f t="shared" ref="Q2:Q15" si="4">_xlfn.TRANSLATE(P2,"pt","es")</f>
+      <c r="P7" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q7" s="56" t="str">
+        <f t="shared" ref="Q7:Q20" si="8">_xlfn.TRANSLATE(P7,"pt","es")</f>
         <v>Valor de X. Coordenada X.</v>
       </c>
-      <c r="R2" s="63" t="s">
+      <c r="R7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="57" t="str">
+        <f t="shared" ref="S7" si="9">SUBSTITUTE(C7, "_", " ")</f>
+        <v>Formal</v>
+      </c>
+      <c r="T7" s="57" t="str">
+        <f t="shared" ref="T7" si="10">SUBSTITUTE(D7, "_", " ")</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U7" s="58" t="str">
+        <f t="shared" ref="U7" si="11">SUBSTITUTE(E7, "_", " ")</f>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V7" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="S2" s="64" t="str">
-        <f t="shared" ref="S2" si="5">SUBSTITUTE(C2, "_", " ")</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T2" s="64" t="str">
-        <f t="shared" ref="T2" si="6">SUBSTITUTE(D2, "_", " ")</f>
-        <v>TGB</v>
-      </c>
-      <c r="U2" s="65" t="str">
-        <f t="shared" ref="U2" si="7">SUBSTITUTE(E2, "_", " ")</f>
+      <c r="W7" s="59" t="str">
+        <f>CONCATENATE("Key.EGC",".",A7)</f>
+        <v>Key.EGC.7</v>
+      </c>
+      <c r="X7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="47" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="61">
+        <v>8</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="56" t="str">
+        <f t="shared" si="4"/>
+        <v>Formal</v>
+      </c>
+      <c r="M8" s="56" t="str">
+        <f t="shared" ref="M8:N8" si="12">_xlfn.CONCAT("", D8)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N8" s="56" t="str">
+        <f t="shared" si="12"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V2" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W2" s="66" t="str">
-        <f>CONCATENATE("Key.EGC",".",A2)</f>
-        <v>Key.EGC.2</v>
-      </c>
-      <c r="X2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="52" t="str">
-        <f t="shared" ref="AA2:AA15" si="8">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Value of X. Coordinate X.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
-        <v>3</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F3" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M3" s="62" t="str">
-        <f t="shared" ref="M3:N3" si="9">_xlfn.CONCAT("", D3)</f>
-        <v>TGB</v>
-      </c>
-      <c r="N3" s="62" t="str">
-        <f t="shared" si="9"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O3" s="62" t="str">
-        <f t="shared" si="3"/>
+      <c r="O8" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>Valor.Y</v>
       </c>
-      <c r="P3" s="62" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q3" s="62" t="str">
-        <f t="shared" si="4"/>
+      <c r="P8" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q8" s="56" t="str">
+        <f t="shared" si="8"/>
         <v>Valor de Y. Coordenada Y.</v>
       </c>
-      <c r="R3" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S3" s="64" t="str">
-        <f t="shared" ref="S3:U3" si="10">SUBSTITUTE(C3, "_", " ")</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T3" s="64" t="str">
-        <f t="shared" si="10"/>
-        <v>TGB</v>
-      </c>
-      <c r="U3" s="65" t="str">
-        <f t="shared" si="10"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V3" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W3" s="66" t="str">
-        <f t="shared" ref="W3:W15" si="11">CONCATENATE("Key.EGC",".",A3)</f>
-        <v>Key.EGC.3</v>
-      </c>
-      <c r="X3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Value of Y. Y-coordinate.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26">
-        <v>4</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F4" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M4" s="62" t="str">
-        <f t="shared" ref="M4:M11" si="12">_xlfn.CONCAT("", D4)</f>
-        <v>TGB</v>
-      </c>
-      <c r="N4" s="62" t="str">
-        <f t="shared" ref="N4:N11" si="13">_xlfn.CONCAT("", E4)</f>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O4" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Valor.Z</v>
-      </c>
-      <c r="P4" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q4" s="62" t="str">
-        <f t="shared" si="4"/>
-        <v>Valor Z. Coordenada Z.</v>
-      </c>
-      <c r="R4" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S4" s="64" t="str">
-        <f t="shared" ref="S4:S11" si="14">SUBSTITUTE(C4, "_", " ")</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T4" s="64" t="str">
-        <f t="shared" ref="T4:T11" si="15">SUBSTITUTE(D4, "_", " ")</f>
-        <v>TGB</v>
-      </c>
-      <c r="U4" s="65" t="str">
-        <f t="shared" ref="U4:U11" si="16">SUBSTITUTE(E4, "_", " ")</f>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V4" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W4" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.4</v>
-      </c>
-      <c r="X4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Z Value. Z Coordinate.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
-        <v>5</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M5" s="62" t="str">
-        <f t="shared" si="12"/>
-        <v>TGB</v>
-      </c>
-      <c r="N5" s="62" t="str">
+      <c r="R8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="57" t="str">
+        <f t="shared" ref="S8:U8" si="13">SUBSTITUTE(C8, "_", " ")</f>
+        <v>Formal</v>
+      </c>
+      <c r="T8" s="57" t="str">
+        <f t="shared" si="13"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U8" s="58" t="str">
         <f t="shared" si="13"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O5" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Valor.Deslocar</v>
-      </c>
-      <c r="P5" s="62" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q5" s="62" t="str">
+      <c r="V8" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W8" s="59" t="str">
+        <f t="shared" ref="W8:W20" si="14">CONCATENATE("Key.EGC",".",A8)</f>
+        <v>Key.EGC.8</v>
+      </c>
+      <c r="X8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="61">
+        <v>9</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="56" t="str">
         <f t="shared" si="4"/>
-        <v>Valor desplazado. Valor de distancia de una traslación</v>
-      </c>
-      <c r="R5" s="63" t="s">
+        <v>Formal</v>
+      </c>
+      <c r="M9" s="56" t="str">
+        <f t="shared" ref="M9:M16" si="15">_xlfn.CONCAT("", D9)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N9" s="56" t="str">
+        <f t="shared" ref="N9:N16" si="16">_xlfn.CONCAT("", E9)</f>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O9" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor.Z</v>
+      </c>
+      <c r="P9" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q9" s="56" t="str">
+        <f t="shared" si="8"/>
+        <v>Valor Z. Coordenada Z.</v>
+      </c>
+      <c r="R9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="57" t="str">
+        <f t="shared" ref="S9:S16" si="17">SUBSTITUTE(C9, "_", " ")</f>
+        <v>Formal</v>
+      </c>
+      <c r="T9" s="57" t="str">
+        <f t="shared" ref="T9:T16" si="18">SUBSTITUTE(D9, "_", " ")</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U9" s="58" t="str">
+        <f t="shared" ref="U9:U16" si="19">SUBSTITUTE(E9, "_", " ")</f>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V9" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="S5" s="64" t="str">
+      <c r="W9" s="59" t="str">
         <f t="shared" si="14"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T5" s="64" t="str">
+        <v>Key.EGC.9</v>
+      </c>
+      <c r="X9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="47" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="61">
+        <v>10</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="56" t="str">
+        <f t="shared" si="4"/>
+        <v>Formal</v>
+      </c>
+      <c r="M10" s="56" t="str">
         <f t="shared" si="15"/>
-        <v>TGB</v>
-      </c>
-      <c r="U5" s="65" t="str">
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N10" s="56" t="str">
         <f t="shared" si="16"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V5" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W5" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.5</v>
-      </c>
-      <c r="X5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="52" t="str">
+      <c r="O10" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor.Deslocar</v>
+      </c>
+      <c r="P10" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q10" s="56" t="str">
         <f t="shared" si="8"/>
-        <v>Displace Value. Distance Value of a Translation</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
-        <v>6</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M6" s="62" t="str">
-        <f t="shared" ref="M6" si="17">_xlfn.CONCAT("", D6)</f>
-        <v>TGB</v>
-      </c>
-      <c r="N6" s="62" t="str">
-        <f t="shared" ref="N6" si="18">_xlfn.CONCAT("", E6)</f>
+        <v>Valor desplazado. Valor de distancia de una traslación</v>
+      </c>
+      <c r="R10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="57" t="str">
+        <f t="shared" si="17"/>
+        <v>Formal</v>
+      </c>
+      <c r="T10" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U10" s="58" t="str">
+        <f t="shared" si="19"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="O6" s="62" t="str">
-        <f t="shared" si="3"/>
+      <c r="V10" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W10" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.10</v>
+      </c>
+      <c r="X10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="47" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="61">
+        <v>11</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="56" t="str">
+        <f t="shared" si="4"/>
+        <v>Formal</v>
+      </c>
+      <c r="M11" s="56" t="str">
+        <f t="shared" ref="M11" si="20">_xlfn.CONCAT("", D11)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N11" s="56" t="str">
+        <f t="shared" ref="N11" si="21">_xlfn.CONCAT("", E11)</f>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O11" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>Valor.Angular</v>
       </c>
-      <c r="P6" s="62" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q6" s="62" t="str">
+      <c r="P11" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q11" s="56" t="str">
+        <f t="shared" si="8"/>
+        <v>Valor angular de una transformada de espín o rotación</v>
+      </c>
+      <c r="R11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="57" t="str">
+        <f t="shared" ref="S11" si="22">SUBSTITUTE(C11, "_", " ")</f>
+        <v>Formal</v>
+      </c>
+      <c r="T11" s="57" t="str">
+        <f t="shared" ref="T11" si="23">SUBSTITUTE(D11, "_", " ")</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U11" s="58" t="str">
+        <f t="shared" ref="U11" si="24">SUBSTITUTE(E11, "_", " ")</f>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V11" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W11" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.11</v>
+      </c>
+      <c r="X11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="61">
+        <v>12</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="56" t="str">
         <f t="shared" si="4"/>
-        <v>Valor angular de una transformada de espín o rotación</v>
-      </c>
-      <c r="R6" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S6" s="64" t="str">
-        <f t="shared" ref="S6" si="19">SUBSTITUTE(C6, "_", " ")</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T6" s="64" t="str">
-        <f t="shared" ref="T6" si="20">SUBSTITUTE(D6, "_", " ")</f>
-        <v>TGB</v>
-      </c>
-      <c r="U6" s="65" t="str">
-        <f t="shared" ref="U6" si="21">SUBSTITUTE(E6, "_", " ")</f>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V6" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W6" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.6</v>
-      </c>
-      <c r="X6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Angular Value of a Spin or Rotation Transform</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
-        <v>7</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F7" s="56" t="s">
-        <v>146</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M7" s="62" t="str">
-        <f t="shared" si="12"/>
-        <v>TGB</v>
-      </c>
-      <c r="N7" s="62" t="str">
-        <f t="shared" si="13"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O7" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Valor.Escalar</v>
-      </c>
-      <c r="P7" s="62" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q7" s="62" t="str">
-        <f t="shared" si="4"/>
-        <v>Valor escalar de una transformación que cambia la escala</v>
-      </c>
-      <c r="R7" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S7" s="64" t="str">
-        <f t="shared" si="14"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T7" s="64" t="str">
+        <v>Formal</v>
+      </c>
+      <c r="M12" s="56" t="str">
         <f t="shared" si="15"/>
-        <v>TGB</v>
-      </c>
-      <c r="U7" s="65" t="str">
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N12" s="56" t="str">
         <f t="shared" si="16"/>
         <v>Parâmetro.Geométrico</v>
       </c>
-      <c r="V7" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W7" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.7</v>
-      </c>
-      <c r="X7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="52" t="str">
+      <c r="O12" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor.Escalar</v>
+      </c>
+      <c r="P12" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q12" s="56" t="str">
         <f t="shared" si="8"/>
-        <v>Scalar Value of a Scale-Changing Transformation</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>8</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="F8" s="56" t="s">
-        <v>168</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M8" s="62" t="str">
-        <f t="shared" si="12"/>
-        <v>TGB</v>
-      </c>
-      <c r="N8" s="62" t="str">
-        <f t="shared" si="13"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="O8" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Ponto.Eixo1</v>
-      </c>
-      <c r="P8" s="62" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q8" s="62" t="str">
+        <v>Valor escalar de una transformación que cambia la escala</v>
+      </c>
+      <c r="R12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="57" t="str">
+        <f t="shared" si="17"/>
+        <v>Formal</v>
+      </c>
+      <c r="T12" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U12" s="58" t="str">
+        <f t="shared" si="19"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V12" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W12" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.12</v>
+      </c>
+      <c r="X12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="47" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="61">
+        <v>13</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="56" t="str">
         <f t="shared" si="4"/>
-        <v>Punto 1 que define un eje de simetría</v>
-      </c>
-      <c r="R8" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S8" s="64" t="str">
-        <f t="shared" si="14"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T8" s="64" t="str">
+        <v>Formal</v>
+      </c>
+      <c r="M13" s="56" t="str">
         <f t="shared" si="15"/>
-        <v>TGB</v>
-      </c>
-      <c r="U8" s="65" t="str">
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N13" s="56" t="str">
         <f t="shared" si="16"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="V8" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W8" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.8</v>
-      </c>
-      <c r="X8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="52" t="str">
+      <c r="O13" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Ponto.Eixo1</v>
+      </c>
+      <c r="P13" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q13" s="56" t="str">
         <f t="shared" si="8"/>
-        <v>Point 1 that defines a symmetry axis</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
-        <v>8</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="F9" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="62" t="str">
-        <f t="shared" ref="L9" si="22">_xlfn.CONCAT(C9)</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M9" s="62" t="str">
-        <f t="shared" ref="M9" si="23">_xlfn.CONCAT("", D9)</f>
-        <v>TGB</v>
-      </c>
-      <c r="N9" s="62" t="str">
-        <f t="shared" ref="N9" si="24">_xlfn.CONCAT("", E9)</f>
+        <v>Punto 1 que define un eje de simetría</v>
+      </c>
+      <c r="R13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="57" t="str">
+        <f t="shared" si="17"/>
+        <v>Formal</v>
+      </c>
+      <c r="T13" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U13" s="58" t="str">
+        <f t="shared" si="19"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="O9" s="62" t="str">
-        <f t="shared" si="3"/>
+      <c r="V13" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W13" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.13</v>
+      </c>
+      <c r="X13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="47" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="61">
+        <v>14</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="F14" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="56" t="str">
+        <f t="shared" ref="L14" si="25">_xlfn.CONCAT(C14)</f>
+        <v>Formal</v>
+      </c>
+      <c r="M14" s="56" t="str">
+        <f t="shared" ref="M14" si="26">_xlfn.CONCAT("", D14)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N14" s="56" t="str">
+        <f t="shared" ref="N14" si="27">_xlfn.CONCAT("", E14)</f>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O14" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>Ponto.Eixo2</v>
       </c>
-      <c r="P9" s="62" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q9" s="62" t="str">
-        <f t="shared" ref="Q9" si="25">_xlfn.TRANSLATE(P9,"pt","es")</f>
+      <c r="P14" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q14" s="56" t="str">
+        <f t="shared" ref="Q14" si="28">_xlfn.TRANSLATE(P14,"pt","es")</f>
         <v>Punto 2 que define un eje de simetría</v>
       </c>
-      <c r="R9" s="63" t="s">
+      <c r="R14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="57" t="str">
+        <f t="shared" ref="S14" si="29">SUBSTITUTE(C14, "_", " ")</f>
+        <v>Formal</v>
+      </c>
+      <c r="T14" s="57" t="str">
+        <f t="shared" ref="T14" si="30">SUBSTITUTE(D14, "_", " ")</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U14" s="58" t="str">
+        <f t="shared" ref="U14" si="31">SUBSTITUTE(E14, "_", " ")</f>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V14" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="S9" s="64" t="str">
-        <f t="shared" ref="S9" si="26">SUBSTITUTE(C9, "_", " ")</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T9" s="64" t="str">
-        <f t="shared" ref="T9" si="27">SUBSTITUTE(D9, "_", " ")</f>
-        <v>TGB</v>
-      </c>
-      <c r="U9" s="65" t="str">
-        <f t="shared" ref="U9" si="28">SUBSTITUTE(E9, "_", " ")</f>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V9" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W9" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.8</v>
-      </c>
-      <c r="X9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="52" t="str">
-        <f t="shared" ref="AA9" si="29">_xlfn.TRANSLATE(P9,"pt","en")</f>
-        <v>Point 2 that defines a symmetry axis</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
-        <v>8</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="F10" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M10" s="62" t="str">
-        <f t="shared" si="12"/>
-        <v>TGB</v>
-      </c>
-      <c r="N10" s="62" t="str">
-        <f t="shared" si="13"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="O10" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Ponto.Base</v>
-      </c>
-      <c r="P10" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q10" s="62" t="str">
+      <c r="W14" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.14</v>
+      </c>
+      <c r="X14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="61">
+        <v>15</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="56" t="str">
         <f t="shared" si="4"/>
-        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
-      </c>
-      <c r="R10" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S10" s="64" t="str">
-        <f t="shared" si="14"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T10" s="64" t="str">
+        <v>Formal</v>
+      </c>
+      <c r="M15" s="56" t="str">
         <f t="shared" si="15"/>
-        <v>TGB</v>
-      </c>
-      <c r="U10" s="65" t="str">
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N15" s="56" t="str">
         <f t="shared" si="16"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="V10" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W10" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.8</v>
-      </c>
-      <c r="X10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="52" t="str">
+      <c r="O15" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Ponto.Base</v>
+      </c>
+      <c r="P15" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q15" s="56" t="str">
         <f t="shared" si="8"/>
-        <v>Base point that can serve as the first base point of a translation vector or to reference a project</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
-        <v>9</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="F11" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M11" s="62" t="str">
-        <f t="shared" si="12"/>
-        <v>TGB</v>
-      </c>
-      <c r="N11" s="62" t="str">
-        <f t="shared" si="13"/>
+        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
+      </c>
+      <c r="R15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="57" t="str">
+        <f t="shared" si="17"/>
+        <v>Formal</v>
+      </c>
+      <c r="T15" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U15" s="58" t="str">
+        <f t="shared" si="19"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="O11" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Ponto.Destino</v>
-      </c>
-      <c r="P11" s="62" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q11" s="62" t="str">
+      <c r="V15" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W15" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.15</v>
+      </c>
+      <c r="X15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="47" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="61">
+        <v>16</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="56" t="str">
         <f t="shared" si="4"/>
-        <v>Punto final de un vector de traslación</v>
-      </c>
-      <c r="R11" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S11" s="64" t="str">
-        <f t="shared" si="14"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T11" s="64" t="str">
+        <v>Formal</v>
+      </c>
+      <c r="M16" s="56" t="str">
         <f t="shared" si="15"/>
-        <v>TGB</v>
-      </c>
-      <c r="U11" s="65" t="str">
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N16" s="56" t="str">
         <f t="shared" si="16"/>
         <v>Bases.Geométricas</v>
       </c>
-      <c r="V11" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W11" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.9</v>
-      </c>
-      <c r="X11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Endpoint of a Translation Vector</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
-        <v>10</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="28" t="s">
+      <c r="O16" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Ponto.Destino</v>
+      </c>
+      <c r="P16" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q16" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="R16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="57" t="str">
+        <f t="shared" si="17"/>
+        <v>Formal</v>
+      </c>
+      <c r="T16" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U16" s="58" t="str">
+        <f t="shared" si="19"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V16" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W16" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.16</v>
+      </c>
+      <c r="X16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="47" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="61">
+        <v>17</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="L17" s="56" t="str">
+        <f t="shared" si="4"/>
+        <v>Formal</v>
+      </c>
+      <c r="M17" s="56" t="str">
+        <f t="shared" ref="M17:M20" si="32">_xlfn.CONCAT("", D17)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N17" s="56" t="str">
+        <f t="shared" ref="N17:N20" si="33">_xlfn.CONCAT("", E17)</f>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O17" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Translação</v>
+      </c>
+      <c r="P17" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q17" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="R17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="57" t="str">
+        <f t="shared" ref="S17:S20" si="34">SUBSTITUTE(C17, "_", " ")</f>
+        <v>Formal</v>
+      </c>
+      <c r="T17" s="57" t="str">
+        <f t="shared" ref="T17:T20" si="35">SUBSTITUTE(D17, "_", " ")</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U17" s="58" t="str">
+        <f t="shared" ref="U17:U20" si="36">SUBSTITUTE(E17, "_", " ")</f>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V17" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W17" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.17</v>
+      </c>
+      <c r="X17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="47" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="61">
+        <v>18</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="29" t="s">
+      <c r="G18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="67" t="s">
+        <v>138</v>
+      </c>
+      <c r="L18" s="56" t="str">
+        <f t="shared" si="4"/>
+        <v>Formal</v>
+      </c>
+      <c r="M18" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N18" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O18" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Giro</v>
+      </c>
+      <c r="P18" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q18" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="R18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v>Formal</v>
+      </c>
+      <c r="T18" s="57" t="str">
+        <f t="shared" si="35"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U18" s="58" t="str">
+        <f t="shared" si="36"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V18" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W18" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.18</v>
+      </c>
+      <c r="X18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="47" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="61">
+        <v>19</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="F12" s="56" t="s">
+      <c r="G19" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="56" t="str">
+        <f t="shared" si="4"/>
+        <v>Formal</v>
+      </c>
+      <c r="M19" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N19" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O19" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Escalar</v>
+      </c>
+      <c r="P19" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q19" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="R19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v>Formal</v>
+      </c>
+      <c r="T19" s="57" t="str">
+        <f t="shared" si="35"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U19" s="58" t="str">
+        <f t="shared" si="36"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V19" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W19" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.19</v>
+      </c>
+      <c r="X19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="47" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="61">
+        <v>20</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="G12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="L12" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M12" s="62" t="str">
-        <f t="shared" ref="M12:M15" si="30">_xlfn.CONCAT("", D12)</f>
-        <v>TGB</v>
-      </c>
-      <c r="N12" s="62" t="str">
-        <f t="shared" ref="N12:N15" si="31">_xlfn.CONCAT("", E12)</f>
+      <c r="G20" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="56" t="str">
+        <f t="shared" ref="L20" si="37">_xlfn.CONCAT(C20)</f>
+        <v>Formal</v>
+      </c>
+      <c r="M20" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N20" s="56" t="str">
+        <f t="shared" si="33"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O12" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Translação</v>
-      </c>
-      <c r="P12" s="62" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q12" s="62" t="s">
-        <v>149</v>
-      </c>
-      <c r="R12" s="63" t="s">
+      <c r="O20" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>Reflexão</v>
+      </c>
+      <c r="P20" s="56" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q20" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="R20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v>Formal</v>
+      </c>
+      <c r="T20" s="57" t="str">
+        <f t="shared" si="35"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U20" s="58" t="str">
+        <f t="shared" si="36"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V20" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="S12" s="64" t="str">
-        <f t="shared" ref="S12:S15" si="32">SUBSTITUTE(C12, "_", " ")</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T12" s="64" t="str">
-        <f t="shared" ref="T12:T15" si="33">SUBSTITUTE(D12, "_", " ")</f>
-        <v>TGB</v>
-      </c>
-      <c r="U12" s="65" t="str">
-        <f t="shared" ref="U12:U15" si="34">SUBSTITUTE(E12, "_", " ")</f>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V12" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W12" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.10</v>
-      </c>
-      <c r="X12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Translation. The transformation that transforms the point by a linear displacement. Need Base Point and Target Point.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
-        <v>11</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="F13" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="L13" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M13" s="62" t="str">
-        <f t="shared" si="30"/>
-        <v>TGB</v>
-      </c>
-      <c r="N13" s="62" t="str">
-        <f t="shared" si="31"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O13" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Giro</v>
-      </c>
-      <c r="P13" s="62" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q13" s="62" t="str">
-        <f t="shared" si="4"/>
-        <v>Giro. La transformación que transforma la posición de un punto con un desplazamiento circular. Punto base y ángulo precisos.</v>
-      </c>
-      <c r="R13" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S13" s="64" t="str">
-        <f t="shared" si="32"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T13" s="64" t="str">
-        <f t="shared" si="33"/>
-        <v>TGB</v>
-      </c>
-      <c r="U13" s="65" t="str">
-        <f t="shared" si="34"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V13" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W13" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.11</v>
-      </c>
-      <c r="X13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Giro. The transformation that transforms the position of a point with a circular displacement. Precise Base Point and Angle.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
-        <v>12</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="F14" s="56" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="L14" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M14" s="62" t="str">
-        <f t="shared" si="30"/>
-        <v>TGB</v>
-      </c>
-      <c r="N14" s="62" t="str">
-        <f t="shared" si="31"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O14" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Escalar</v>
-      </c>
-      <c r="P14" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q14" s="62" t="str">
-        <f t="shared" si="4"/>
-        <v>Escala. Agrandamiento o reducción de una forma en relación con un centro homotético.  Necesito punto base y factor escalar.</v>
-      </c>
-      <c r="R14" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S14" s="64" t="str">
-        <f t="shared" si="32"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T14" s="64" t="str">
-        <f t="shared" si="33"/>
-        <v>TGB</v>
-      </c>
-      <c r="U14" s="65" t="str">
-        <f t="shared" si="34"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V14" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W14" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.12</v>
-      </c>
-      <c r="X14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Scale. Enlargement or reduction of a shape in relation to a homothetic center.  Need Base Point and Scalar Factor.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
-        <v>13</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="L15" s="62" t="str">
-        <f t="shared" ref="L15" si="35">_xlfn.CONCAT(C15)</f>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="M15" s="62" t="str">
-        <f t="shared" si="30"/>
-        <v>TGB</v>
-      </c>
-      <c r="N15" s="62" t="str">
-        <f t="shared" si="31"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O15" s="62" t="str">
-        <f t="shared" si="3"/>
-        <v>Reflexão</v>
-      </c>
-      <c r="P15" s="62" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q15" s="62" t="str">
-        <f t="shared" si="4"/>
-        <v>Reflexión. Transformación de un punto respecto a un eje de simetría. Eje de puntos preciso 1 y eje de puntos2.</v>
-      </c>
-      <c r="R15" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="S15" s="64" t="str">
-        <f t="shared" si="32"/>
-        <v>Estrutura.Geométrica</v>
-      </c>
-      <c r="T15" s="64" t="str">
-        <f t="shared" si="33"/>
-        <v>TGB</v>
-      </c>
-      <c r="U15" s="65" t="str">
-        <f t="shared" si="34"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V15" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W15" s="66" t="str">
-        <f t="shared" si="11"/>
-        <v>Key.EGC.13</v>
-      </c>
-      <c r="X15" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Reflection. Transformation of a point with respect to an axis of symmetry. Precise Point Axis1 and Point Axis2.</v>
+      <c r="W20" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v>Key.EGC.20</v>
+      </c>
+      <c r="X20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="47" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:Z1 AA1:AA15">
-    <cfRule type="cellIs" dxfId="8" priority="18" operator="equal">
+  <conditionalFormatting sqref="F1 F7:F1048576">
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A20">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:Z15">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
-    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F15">
-    <cfRule type="duplicateValues" dxfId="5" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4536,72 +5206,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="39" t="s">
+      <c r="Q1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="S1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="39" t="s">
+      <c r="T1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="39" t="s">
+      <c r="U1" s="36" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="38">
+      <c r="A2" s="35">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -4666,7 +5336,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="38">
+      <c r="A3" s="35">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -4733,7 +5403,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4753,30 +5423,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35">
-        <v>1</v>
-      </c>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="32">
+        <v>1</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="33" t="s">
         <v>95</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="37" t="s">
+      <c r="B2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="34" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4785,1043 +5455,1045 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <dimension ref="A1:AA12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" customWidth="1"/>
-    <col min="4" max="11" width="3.42578125" style="45" customWidth="1"/>
-    <col min="12" max="12" width="5" customWidth="1"/>
-    <col min="13" max="13" width="27.140625" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" style="40" customWidth="1"/>
-    <col min="15" max="15" width="3.42578125" style="41" customWidth="1"/>
-    <col min="16" max="16" width="6.85546875" style="41" customWidth="1"/>
-    <col min="17" max="17" width="3.42578125" style="41" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" style="41" customWidth="1"/>
-    <col min="19" max="19" width="3.42578125" style="41" customWidth="1"/>
-    <col min="20" max="20" width="12" style="41" customWidth="1"/>
-    <col min="21" max="21" width="4.42578125" style="58" customWidth="1"/>
-    <col min="22" max="22" width="9.7109375" style="40" customWidth="1"/>
-    <col min="23" max="23" width="4.28515625" style="58" customWidth="1"/>
-    <col min="24" max="24" width="7.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.42578125" style="58" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12" style="41" customWidth="1"/>
-    <col min="27" max="27" width="4.42578125" style="58" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="48" t="s">
+      <c r="F1" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="48" t="s">
+      <c r="G1" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="H1" s="48" t="s">
+      <c r="I1" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="J1" s="48" t="s">
+      <c r="K1" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="32" t="s">
+      <c r="M1" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="N1" s="34" t="s">
+      <c r="O1" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="P1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="P1" s="32" t="s">
+      <c r="Q1" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="R1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="R1" s="32" t="s">
+      <c r="S1" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="T1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="T1" s="32" t="s">
+      <c r="U1" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="V1" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="V1" s="34" t="s">
+      <c r="W1" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="X1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="X1" s="32" t="s">
+      <c r="Y1" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="Y1" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z1" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA1" s="48" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
+      <c r="AA1" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28">
         <v>2</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="N2" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="52">
+        <v>1.05</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q2" s="52">
+        <v>1.05</v>
+      </c>
+      <c r="R2" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="S2" s="52">
+        <v>1.05</v>
+      </c>
+      <c r="T2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="W2" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="X2" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y2" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28">
+        <v>3</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="N3" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="O3" s="52">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P3" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q3" s="52">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="R3" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="S3" s="52">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="T3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="W3" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="X3" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y3" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="28">
+        <v>4</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M4" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="N4" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="O4" s="52">
+        <v>3.05</v>
+      </c>
+      <c r="P4" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q4" s="52">
+        <v>3.05</v>
+      </c>
+      <c r="R4" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="S4" s="52">
+        <v>3.05</v>
+      </c>
+      <c r="T4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="W4" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="X4" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y4" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="28">
+        <v>5</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="W5" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="X5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28">
+        <v>6</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M6" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28">
+        <v>7</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="N7" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>8</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="N8" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y8" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z8" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M2" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="N2" s="43" t="s">
+      <c r="AA8" s="55" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>9</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="N9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y9" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z9" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA9" s="55" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>10</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="N10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>11</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="O2" s="57">
-        <v>1.05</v>
-      </c>
-      <c r="P2" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q2" s="57">
-        <v>1.05</v>
-      </c>
-      <c r="R2" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="S2" s="57">
-        <v>1.05</v>
-      </c>
-      <c r="T2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="W2" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="X2" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y2" s="61" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z2" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31">
-        <v>2</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M3" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="43" t="s">
+      <c r="N11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>12</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="O3" s="57">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="P3" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q3" s="57">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="R3" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="S3" s="57">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="T3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="W3" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="X3" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y3" s="61" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31">
-        <v>2</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M4" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="N4" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="O4" s="57">
-        <v>3.05</v>
-      </c>
-      <c r="P4" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q4" s="57">
-        <v>3.05</v>
-      </c>
-      <c r="R4" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="S4" s="57">
-        <v>3.05</v>
-      </c>
-      <c r="T4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="W4" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="X4" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y4" s="61" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31">
-        <v>2</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M5" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="N5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="W5" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="X5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
-        <v>2</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M6" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="N6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31">
-        <v>2</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M7" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="N7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
-        <v>2</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M8" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="N8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X8" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y8" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z8" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA8" s="61" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31">
-        <v>2</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="N9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X9" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y9" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z9" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA9" s="61" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
-        <v>2</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M10" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="N10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31">
-        <v>2</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M11" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="N11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31">
-        <v>2</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="M12" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="N12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="U12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="V12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="67" t="s">
+      <c r="N12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="60" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S2">
-    <sortCondition ref="C1:C2"/>
-  </sortState>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D1:M1048576 AB1:XFD1048576 A1:B1048576">
-    <cfRule type="cellIs" dxfId="1" priority="30" operator="equal">
+  <conditionalFormatting sqref="D1:M12 A1:B12">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  <conditionalFormatting sqref="B1:B12">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFDBE71-8676-44F2-8270-BB7655332AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8560B5-8266-4B86-A9AA-64E64FDBB332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
-    <sheet name="Classes" sheetId="31" r:id="rId2"/>
+    <sheet name="Classes" sheetId="33" r:id="rId2"/>
     <sheet name="Disjunt" sheetId="3" r:id="rId3"/>
     <sheet name="Interop" sheetId="27" r:id="rId4"/>
     <sheet name="FatosIn" sheetId="32" r:id="rId5"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="223">
   <si>
     <t>Key</t>
   </si>
@@ -2287,7 +2287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2486,15 +2486,33 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2508,7 +2526,15 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -2568,124 +2594,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3215,7 +3123,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46142.684945023146</v>
+        <v>46142.699317245373</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>104</v>
@@ -3318,36 +3226,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <dimension ref="A1:AA20"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" customWidth="1"/>
-    <col min="7" max="10" width="7.42578125" style="68" customWidth="1"/>
-    <col min="11" max="11" width="31.28515625" style="68" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
-    <col min="16" max="16" width="50.5703125" customWidth="1"/>
-    <col min="17" max="17" width="55" customWidth="1"/>
-    <col min="18" max="18" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="65.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7" customWidth="1"/>
-    <col min="24" max="25" width="6.42578125" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="68" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="53.140625" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="69.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3423,14 +3331,14 @@
       <c r="Y1" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="Z1" s="69" t="s">
+      <c r="Z1" s="68" t="s">
         <v>99</v>
       </c>
       <c r="AA1" s="46" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="61">
         <v>2</v>
       </c>
@@ -3521,7 +3429,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="61">
         <v>3</v>
       </c>
@@ -3612,7 +3520,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61">
         <v>4</v>
       </c>
@@ -3703,7 +3611,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="61">
         <v>5</v>
       </c>
@@ -3794,7 +3702,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="61">
         <v>6</v>
       </c>
@@ -3885,7 +3793,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="61">
         <v>7</v>
       </c>
@@ -3920,41 +3828,41 @@
         <v>1</v>
       </c>
       <c r="L7" s="56" t="str">
-        <f t="shared" ref="L7:L19" si="4">_xlfn.CONCAT(C7)</f>
+        <f t="shared" ref="L7:L20" si="4">_xlfn.CONCAT(C7)</f>
         <v>Formal</v>
       </c>
       <c r="M7" s="56" t="str">
-        <f t="shared" ref="M7" si="5">_xlfn.CONCAT("", D7)</f>
+        <f t="shared" ref="M7:O20" si="5">_xlfn.CONCAT("", D7)</f>
         <v>Elementos.TGB</v>
       </c>
       <c r="N7" s="56" t="str">
-        <f t="shared" ref="N7" si="6">_xlfn.CONCAT("", E7)</f>
+        <f t="shared" si="5"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="O7" s="56" t="str">
-        <f t="shared" ref="O7:O20" si="7">_xlfn.CONCAT("", F7)</f>
+        <f t="shared" si="5"/>
         <v>Valor.X</v>
       </c>
       <c r="P7" s="56" t="s">
         <v>174</v>
       </c>
       <c r="Q7" s="56" t="str">
-        <f t="shared" ref="Q7:Q20" si="8">_xlfn.TRANSLATE(P7,"pt","es")</f>
+        <f t="shared" ref="Q7:Q15" si="6">_xlfn.TRANSLATE(P7,"pt","es")</f>
         <v>Valor de X. Coordenada X.</v>
       </c>
       <c r="R7" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S7" s="57" t="str">
-        <f t="shared" ref="S7" si="9">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U20" si="7">SUBSTITUTE(C7, "_", " ")</f>
         <v>Formal</v>
       </c>
       <c r="T7" s="57" t="str">
-        <f t="shared" ref="T7" si="10">SUBSTITUTE(D7, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U7" s="58" t="str">
-        <f t="shared" ref="U7" si="11">SUBSTITUTE(E7, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V7" s="47" t="s">
@@ -3977,7 +3885,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="61">
         <v>8</v>
       </c>
@@ -4016,44 +3924,44 @@
         <v>Formal</v>
       </c>
       <c r="M8" s="56" t="str">
-        <f t="shared" ref="M8:N8" si="12">_xlfn.CONCAT("", D8)</f>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N8" s="56" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="O8" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Valor.Y</v>
       </c>
       <c r="P8" s="56" t="s">
         <v>173</v>
       </c>
       <c r="Q8" s="56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Valor de Y. Coordenada Y.</v>
       </c>
       <c r="R8" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="57" t="str">
-        <f t="shared" ref="S8:U8" si="13">SUBSTITUTE(C8, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T8" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U8" s="58" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V8" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W8" s="59" t="str">
-        <f t="shared" ref="W8:W20" si="14">CONCATENATE("Key.EGC",".",A8)</f>
+        <f t="shared" ref="W8:W20" si="8">CONCATENATE("Key.EGC",".",A8)</f>
         <v>Key.EGC.8</v>
       </c>
       <c r="X8" s="47" t="s">
@@ -4069,7 +3977,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="61">
         <v>9</v>
       </c>
@@ -4108,44 +4016,44 @@
         <v>Formal</v>
       </c>
       <c r="M9" s="56" t="str">
-        <f t="shared" ref="M9:M16" si="15">_xlfn.CONCAT("", D9)</f>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N9" s="56" t="str">
-        <f t="shared" ref="N9:N16" si="16">_xlfn.CONCAT("", E9)</f>
+        <f t="shared" si="5"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="O9" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Valor.Z</v>
       </c>
       <c r="P9" s="56" t="s">
         <v>175</v>
       </c>
       <c r="Q9" s="56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Valor Z. Coordenada Z.</v>
       </c>
       <c r="R9" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="57" t="str">
-        <f t="shared" ref="S9:S16" si="17">SUBSTITUTE(C9, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T9" s="57" t="str">
-        <f t="shared" ref="T9:T16" si="18">SUBSTITUTE(D9, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U9" s="58" t="str">
-        <f t="shared" ref="U9:U16" si="19">SUBSTITUTE(E9, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V9" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W9" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.9</v>
       </c>
       <c r="X9" s="47" t="s">
@@ -4161,7 +4069,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="61">
         <v>10</v>
       </c>
@@ -4200,44 +4108,44 @@
         <v>Formal</v>
       </c>
       <c r="M10" s="56" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N10" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="O10" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Valor.Deslocar</v>
       </c>
       <c r="P10" s="56" t="s">
         <v>172</v>
       </c>
       <c r="Q10" s="56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Valor desplazado. Valor de distancia de una traslación</v>
       </c>
       <c r="R10" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T10" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U10" s="58" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V10" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W10" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.10</v>
       </c>
       <c r="X10" s="47" t="s">
@@ -4253,7 +4161,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="61">
         <v>11</v>
       </c>
@@ -4292,44 +4200,44 @@
         <v>Formal</v>
       </c>
       <c r="M11" s="56" t="str">
-        <f t="shared" ref="M11" si="20">_xlfn.CONCAT("", D11)</f>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N11" s="56" t="str">
-        <f t="shared" ref="N11" si="21">_xlfn.CONCAT("", E11)</f>
+        <f t="shared" si="5"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="O11" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Valor.Angular</v>
       </c>
       <c r="P11" s="56" t="s">
         <v>171</v>
       </c>
       <c r="Q11" s="56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Valor angular de una transformada de espín o rotación</v>
       </c>
       <c r="R11" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="57" t="str">
-        <f t="shared" ref="S11" si="22">SUBSTITUTE(C11, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T11" s="57" t="str">
-        <f t="shared" ref="T11" si="23">SUBSTITUTE(D11, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U11" s="58" t="str">
-        <f t="shared" ref="U11" si="24">SUBSTITUTE(E11, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V11" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W11" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.11</v>
       </c>
       <c r="X11" s="47" t="s">
@@ -4345,7 +4253,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="61">
         <v>12</v>
       </c>
@@ -4384,44 +4292,44 @@
         <v>Formal</v>
       </c>
       <c r="M12" s="56" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N12" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="O12" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Valor.Escalar</v>
       </c>
       <c r="P12" s="56" t="s">
         <v>170</v>
       </c>
       <c r="Q12" s="56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Valor escalar de una transformación que cambia la escala</v>
       </c>
       <c r="R12" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S12" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T12" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U12" s="58" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V12" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W12" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.12</v>
       </c>
       <c r="X12" s="47" t="s">
@@ -4437,7 +4345,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="61">
         <v>13</v>
       </c>
@@ -4476,44 +4384,44 @@
         <v>Formal</v>
       </c>
       <c r="M13" s="56" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N13" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="O13" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Ponto.Eixo1</v>
       </c>
       <c r="P13" s="56" t="s">
         <v>166</v>
       </c>
       <c r="Q13" s="56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Punto 1 que define un eje de simetría</v>
       </c>
       <c r="R13" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S13" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T13" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U13" s="58" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V13" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W13" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.13</v>
       </c>
       <c r="X13" s="47" t="s">
@@ -4529,7 +4437,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="61">
         <v>14</v>
       </c>
@@ -4564,48 +4472,48 @@
         <v>1</v>
       </c>
       <c r="L14" s="56" t="str">
-        <f t="shared" ref="L14" si="25">_xlfn.CONCAT(C14)</f>
+        <f t="shared" si="4"/>
         <v>Formal</v>
       </c>
       <c r="M14" s="56" t="str">
-        <f t="shared" ref="M14" si="26">_xlfn.CONCAT("", D14)</f>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N14" s="56" t="str">
-        <f t="shared" ref="N14" si="27">_xlfn.CONCAT("", E14)</f>
+        <f t="shared" si="5"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="O14" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Ponto.Eixo2</v>
       </c>
       <c r="P14" s="56" t="s">
         <v>167</v>
       </c>
       <c r="Q14" s="56" t="str">
-        <f t="shared" ref="Q14" si="28">_xlfn.TRANSLATE(P14,"pt","es")</f>
+        <f t="shared" si="6"/>
         <v>Punto 2 que define un eje de simetría</v>
       </c>
       <c r="R14" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S14" s="57" t="str">
-        <f t="shared" ref="S14" si="29">SUBSTITUTE(C14, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T14" s="57" t="str">
-        <f t="shared" ref="T14" si="30">SUBSTITUTE(D14, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U14" s="58" t="str">
-        <f t="shared" ref="U14" si="31">SUBSTITUTE(E14, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V14" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W14" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.14</v>
       </c>
       <c r="X14" s="47" t="s">
@@ -4621,7 +4529,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="61">
         <v>15</v>
       </c>
@@ -4660,44 +4568,44 @@
         <v>Formal</v>
       </c>
       <c r="M15" s="56" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N15" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="O15" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Ponto.Base</v>
       </c>
       <c r="P15" s="56" t="s">
         <v>168</v>
       </c>
       <c r="Q15" s="56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
       </c>
       <c r="R15" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T15" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U15" s="58" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V15" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W15" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.15</v>
       </c>
       <c r="X15" s="47" t="s">
@@ -4713,7 +4621,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="61">
         <v>16</v>
       </c>
@@ -4752,15 +4660,15 @@
         <v>Formal</v>
       </c>
       <c r="M16" s="56" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N16" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="O16" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Ponto.Destino</v>
       </c>
       <c r="P16" s="56" t="s">
@@ -4773,22 +4681,22 @@
         <v>1</v>
       </c>
       <c r="S16" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T16" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U16" s="58" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>Bases.Geométricas</v>
       </c>
       <c r="V16" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W16" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.16</v>
       </c>
       <c r="X16" s="47" t="s">
@@ -4804,7 +4712,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="61">
         <v>17</v>
       </c>
@@ -4843,15 +4751,15 @@
         <v>Formal</v>
       </c>
       <c r="M17" s="56" t="str">
-        <f t="shared" ref="M17:M20" si="32">_xlfn.CONCAT("", D17)</f>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N17" s="56" t="str">
-        <f t="shared" ref="N17:N20" si="33">_xlfn.CONCAT("", E17)</f>
+        <f t="shared" si="5"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="O17" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Translação</v>
       </c>
       <c r="P17" s="56" t="s">
@@ -4864,22 +4772,22 @@
         <v>1</v>
       </c>
       <c r="S17" s="57" t="str">
-        <f t="shared" ref="S17:S20" si="34">SUBSTITUTE(C17, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T17" s="57" t="str">
-        <f t="shared" ref="T17:T20" si="35">SUBSTITUTE(D17, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U17" s="58" t="str">
-        <f t="shared" ref="U17:U20" si="36">SUBSTITUTE(E17, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V17" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W17" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.17</v>
       </c>
       <c r="X17" s="47" t="s">
@@ -4895,7 +4803,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="61">
         <v>18</v>
       </c>
@@ -4934,15 +4842,15 @@
         <v>Formal</v>
       </c>
       <c r="M18" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N18" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="5"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="O18" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Giro</v>
       </c>
       <c r="P18" s="56" t="s">
@@ -4955,22 +4863,22 @@
         <v>1</v>
       </c>
       <c r="S18" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T18" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U18" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V18" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W18" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.18</v>
       </c>
       <c r="X18" s="47" t="s">
@@ -4986,7 +4894,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="61">
         <v>19</v>
       </c>
@@ -5025,15 +4933,15 @@
         <v>Formal</v>
       </c>
       <c r="M19" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N19" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="5"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="O19" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Escalar</v>
       </c>
       <c r="P19" s="56" t="s">
@@ -5046,22 +4954,22 @@
         <v>1</v>
       </c>
       <c r="S19" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T19" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U19" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V19" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W19" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.19</v>
       </c>
       <c r="X19" s="47" t="s">
@@ -5077,7 +4985,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="61">
         <v>20</v>
       </c>
@@ -5112,19 +5020,19 @@
         <v>163</v>
       </c>
       <c r="L20" s="56" t="str">
-        <f t="shared" ref="L20" si="37">_xlfn.CONCAT(C20)</f>
+        <f t="shared" si="4"/>
         <v>Formal</v>
       </c>
       <c r="M20" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="5"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N20" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="5"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="O20" s="56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>Reflexão</v>
       </c>
       <c r="P20" s="56" t="s">
@@ -5137,22 +5045,22 @@
         <v>1</v>
       </c>
       <c r="S20" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="7"/>
         <v>Formal</v>
       </c>
       <c r="T20" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="7"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U20" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V20" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W20" s="59" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>Key.EGC.20</v>
       </c>
       <c r="X20" s="47" t="s">
@@ -5169,28 +5077,26 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F7:F1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A20">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F7:F20">
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5403,7 +5309,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5446,7 +5352,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5456,39 +5362,33 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
-  <dimension ref="A1:AA12"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U12"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" customWidth="1"/>
+    <col min="13" max="13" width="28.140625" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" customWidth="1"/>
+    <col min="17" max="17" width="3.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" customWidth="1"/>
+    <col min="19" max="19" width="4.5703125" style="71" customWidth="1"/>
+    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -5498,13 +5398,13 @@
       <c r="C1" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="29" t="s">
         <v>48</v>
       </c>
       <c r="E1" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="29" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="43" t="s">
@@ -5531,47 +5431,29 @@
       <c r="N1" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="O1" s="69" t="s">
         <v>92</v>
       </c>
       <c r="P1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="Q1" s="69" t="s">
         <v>92</v>
       </c>
       <c r="R1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="T1" s="31" t="s">
         <v>48</v>
       </c>
       <c r="U1" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="V1" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="W1" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="X1" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y1" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z1" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA1" s="43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28">
         <v>2</v>
       </c>
@@ -5581,16 +5463,16 @@
       <c r="C2" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="45" t="s">
+      <c r="D2" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
@@ -5614,47 +5496,29 @@
       <c r="N2" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="O2" s="52">
+      <c r="O2" s="70">
         <v>1.05</v>
       </c>
       <c r="P2" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="Q2" s="52">
+      <c r="Q2" s="70">
         <v>1.05</v>
       </c>
       <c r="R2" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="S2" s="52">
+      <c r="S2" s="70">
         <v>1.05</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="U2" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="W2" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="X2" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y2" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>3</v>
       </c>
@@ -5664,16 +5528,16 @@
       <c r="C3" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="45" t="s">
+      <c r="D3" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="44" t="s">
@@ -5697,47 +5561,29 @@
       <c r="N3" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="P3" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="Q3" s="52">
+      <c r="Q3" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="R3" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="S3" s="52">
+      <c r="S3" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="T3" s="39" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="U3" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="W3" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="X3" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y3" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z3" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>4</v>
       </c>
@@ -5747,16 +5593,16 @@
       <c r="C4" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="45" t="s">
+      <c r="D4" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="44" t="s">
@@ -5780,47 +5626,29 @@
       <c r="N4" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4" s="70">
         <v>3.05</v>
       </c>
       <c r="P4" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="Q4" s="52">
+      <c r="Q4" s="70">
         <v>3.05</v>
       </c>
       <c r="R4" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="S4" s="52">
+      <c r="S4" s="70">
         <v>3.05</v>
       </c>
       <c r="T4" s="39" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="U4" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="W4" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="X4" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y4" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>5</v>
       </c>
@@ -5830,16 +5658,16 @@
       <c r="C5" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="45" t="s">
+      <c r="D5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H5" s="44" t="s">
@@ -5863,47 +5691,29 @@
       <c r="N5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O5" s="41" t="s">
+      <c r="O5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q5" s="41" t="s">
+      <c r="Q5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S5" s="41" t="s">
+      <c r="S5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="U5" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="W5" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="X5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
         <v>6</v>
       </c>
@@ -5913,16 +5723,16 @@
       <c r="C6" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="45" t="s">
+      <c r="D6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="44" t="s">
@@ -5946,19 +5756,19 @@
       <c r="N6" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="41" t="s">
+      <c r="O6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P6" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="41" t="s">
+      <c r="Q6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R6" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S6" s="41" t="s">
+      <c r="S6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="39" t="s">
@@ -5967,26 +5777,8 @@
       <c r="U6" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="V6" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28">
         <v>7</v>
       </c>
@@ -5996,16 +5788,16 @@
       <c r="C7" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="45" t="s">
+      <c r="D7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H7" s="44" t="s">
@@ -6029,19 +5821,19 @@
       <c r="N7" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O7" s="41" t="s">
+      <c r="O7" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P7" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="41" t="s">
+      <c r="Q7" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R7" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S7" s="41" t="s">
+      <c r="S7" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T7" s="39" t="s">
@@ -6050,26 +5842,8 @@
       <c r="U7" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="V7" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28">
         <v>8</v>
       </c>
@@ -6079,17 +5853,17 @@
       <c r="C8" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>1</v>
+      <c r="D8" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>158</v>
       </c>
       <c r="H8" s="44" t="s">
         <v>1</v>
@@ -6112,19 +5886,19 @@
       <c r="N8" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O8" s="41" t="s">
+      <c r="O8" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P8" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q8" s="41" t="s">
+      <c r="Q8" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R8" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S8" s="41" t="s">
+      <c r="S8" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T8" s="39" t="s">
@@ -6133,26 +5907,8 @@
       <c r="U8" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="V8" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X8" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y8" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z8" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA8" s="55" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>9</v>
       </c>
@@ -6162,17 +5918,17 @@
       <c r="C9" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="45" t="s">
-        <v>1</v>
+      <c r="D9" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>158</v>
       </c>
       <c r="H9" s="44" t="s">
         <v>1</v>
@@ -6195,19 +5951,19 @@
       <c r="N9" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P9" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q9" s="41" t="s">
+      <c r="Q9" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R9" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S9" s="41" t="s">
+      <c r="S9" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T9" s="39" t="s">
@@ -6216,26 +5972,8 @@
       <c r="U9" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="V9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X9" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y9" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z9" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA9" s="55" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>10</v>
       </c>
@@ -6245,16 +5983,16 @@
       <c r="C10" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="45" t="s">
+      <c r="D10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H10" s="44" t="s">
@@ -6278,19 +6016,19 @@
       <c r="N10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O10" s="41" t="s">
+      <c r="O10" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q10" s="41" t="s">
+      <c r="Q10" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S10" s="41" t="s">
+      <c r="S10" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="39" t="s">
@@ -6299,26 +6037,8 @@
       <c r="U10" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="V10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>11</v>
       </c>
@@ -6328,16 +6048,16 @@
       <c r="C11" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="45" t="s">
+      <c r="D11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H11" s="44" t="s">
@@ -6361,19 +6081,19 @@
       <c r="N11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="41" t="s">
+      <c r="O11" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q11" s="41" t="s">
+      <c r="Q11" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S11" s="41" t="s">
+      <c r="S11" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T11" s="39" t="s">
@@ -6382,26 +6102,8 @@
       <c r="U11" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="V11" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
         <v>12</v>
       </c>
@@ -6411,16 +6113,16 @@
       <c r="C12" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="45" t="s">
+      <c r="D12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="60" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="44" t="s">
@@ -6444,19 +6146,19 @@
       <c r="N12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O12" s="41" t="s">
+      <c r="O12" s="70" t="s">
         <v>1</v>
       </c>
       <c r="P12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q12" s="41" t="s">
+      <c r="Q12" s="70" t="s">
         <v>1</v>
       </c>
       <c r="R12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="S12" s="41" t="s">
+      <c r="S12" s="70" t="s">
         <v>1</v>
       </c>
       <c r="T12" s="39" t="s">
@@ -6465,33 +6167,15 @@
       <c r="U12" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="V12" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="60" t="s">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:M12 A1:B12">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+  <conditionalFormatting sqref="A1:B12 H1:M12">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B12">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8560B5-8266-4B86-A9AA-64E64FDBB332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4437DF90-3F2D-4BD7-A476-7D4FAB9825AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="228">
   <si>
     <t>Key</t>
   </si>
@@ -1618,9 +1618,6 @@
     <t>Movimento.Geométrico</t>
   </si>
   <si>
-    <t>Translação</t>
-  </si>
-  <si>
     <t>Giro</t>
   </si>
   <si>
@@ -1696,12 +1693,6 @@
     <t>Valor.Escalar</t>
   </si>
   <si>
-    <t>Valor.Deslocar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">( Valor.Deslocar and Valor.Angular ) or ( Valor.X and Valor.Y and Valor.Z ) </t>
-  </si>
-  <si>
     <t>PB1</t>
   </si>
   <si>
@@ -1714,9 +1705,6 @@
     <t>Va2</t>
   </si>
   <si>
-    <t>"Um valor do deslocamento"</t>
-  </si>
-  <si>
     <t>é.ponto.base</t>
   </si>
   <si>
@@ -1798,9 +1786,6 @@
     <t>Escalar. Ampliação ou redução de uma forma em relação a um centro de homotetia.  Precisa Ponto Base e fator escalar.</t>
   </si>
   <si>
-    <t>Translação. A transformação que transforma o ponto por um deslocamento linear. Precisa Ponto Base e Ponto Destino.</t>
-  </si>
-  <si>
     <t>Reflexão. Transformação de uma ponto em relação a um eixo de simetria. Precisa Ponto Eixo1 e Ponto Eixo2.</t>
   </si>
   <si>
@@ -1864,9 +1849,6 @@
     <t>Punto final de un vector de traslación</t>
   </si>
   <si>
-    <t>La transformación que modifica la posición de un punto mediante un desplazamiento lineal. Necesita punto base y punto objetivo.</t>
-  </si>
-  <si>
     <t>Transformación de un punto respecto a un eje de simetría. Define el eje de simetría por 2 puntos.</t>
   </si>
   <si>
@@ -1921,9 +1903,6 @@
     <t>Endpoint of a translational vector</t>
   </si>
   <si>
-    <t>The transformation that modifies the position of a point by means of a linear displacement. You need base point and target point.</t>
-  </si>
-  <si>
     <t>The transformation that modifies the position of a point by means of a circular displacement. Needs base point and rotation angle.</t>
   </si>
   <si>
@@ -1931,6 +1910,42 @@
   </si>
   <si>
     <t>Transformation of a point with respect to an axis of symmetry. Define the axis of symmetry by 2 points.</t>
+  </si>
+  <si>
+    <t>Translação.Polar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor.X and Valor.Y and Valor.Z </t>
+  </si>
+  <si>
+    <t>Valor.Distância</t>
+  </si>
+  <si>
+    <t>Valor.Distância and Valor.Angular</t>
+  </si>
+  <si>
+    <t>"Um valor de distância de deslocamento"</t>
+  </si>
+  <si>
+    <t>Translação.XYZ</t>
+  </si>
+  <si>
+    <t>Translação Polar. A transformação que transforma o ponto por um deslocamento linear. Precisa Ponto Base e Ponto Destino.</t>
+  </si>
+  <si>
+    <t>Translação XYZ. A transformação que transforma o ponto por um deslocamento linear. Precisa dos componentes XYZ do vetor de translação.</t>
+  </si>
+  <si>
+    <t>Translación Polar. La transformación que modifica la posición de un punto mediante un desplazamiento lineal. Necesita punto base y punto objetivo.</t>
+  </si>
+  <si>
+    <t>Translación XYZ. La transformación que modifica la posición de un punto mediante un desplazamiento lineal. Necesita los componentes XYZ del vector de translación.</t>
+  </si>
+  <si>
+    <t>XYZ translation. The transformation that modifies the position of a point by means of a linear displacement. You need the XYZ components of the translation vector.</t>
+  </si>
+  <si>
+    <t>Polar translation. The transformation that modifies the position of a point by means of a linear displacement. You need base point and target point.</t>
   </si>
 </sst>
 </file>
@@ -2505,6 +2520,14 @@
   <dxfs count="11">
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2594,14 +2617,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2919,6 +2934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
+  <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3123,7 +3139,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46142.699317245373</v>
+        <v>46142.721239814811</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>104</v>
@@ -3227,7 +3243,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
-  <dimension ref="A1:AA20"/>
+  <sheetPr codeName="Planilha2"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
@@ -3343,19 +3360,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E2" s="63" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G2" s="66" t="s">
         <v>1</v>
@@ -3389,10 +3406,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="47" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q2" s="47" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="R2" s="62" t="s">
         <v>1</v>
@@ -3426,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="AA2" s="47" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3434,19 +3451,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D3" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="E3" s="63" t="s">
-        <v>188</v>
-      </c>
       <c r="F3" s="64" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G3" s="66" t="s">
         <v>1</v>
@@ -3480,10 +3497,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="47" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Q3" s="47" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>1</v>
@@ -3517,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="AA3" s="47" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3525,19 +3542,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D4" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="63" t="s">
-        <v>188</v>
-      </c>
       <c r="F4" s="64" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G4" s="66" t="s">
         <v>1</v>
@@ -3571,10 +3588,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="47" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q4" s="47" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>1</v>
@@ -3608,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="AA4" s="47" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3616,19 +3633,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D5" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="F5" s="64" t="s">
         <v>188</v>
-      </c>
-      <c r="F5" s="64" t="s">
-        <v>193</v>
       </c>
       <c r="G5" s="66" t="s">
         <v>1</v>
@@ -3662,10 +3679,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Q5" s="47" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>1</v>
@@ -3699,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="AA5" s="47" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3707,19 +3724,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D6" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="63" t="s">
-        <v>188</v>
-      </c>
       <c r="F6" s="64" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G6" s="66" t="s">
         <v>1</v>
@@ -3753,10 +3770,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="Q6" s="47" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="R6" s="62" t="s">
         <v>1</v>
@@ -3790,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="AA6" s="47" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3801,16 +3818,16 @@
         <v>93</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G7" s="67" t="s">
         <v>1</v>
@@ -3828,11 +3845,11 @@
         <v>1</v>
       </c>
       <c r="L7" s="56" t="str">
-        <f t="shared" ref="L7:L20" si="4">_xlfn.CONCAT(C7)</f>
+        <f t="shared" ref="L7:L21" si="4">_xlfn.CONCAT(C7)</f>
         <v>Formal</v>
       </c>
       <c r="M7" s="56" t="str">
-        <f t="shared" ref="M7:O20" si="5">_xlfn.CONCAT("", D7)</f>
+        <f t="shared" ref="M7:O21" si="5">_xlfn.CONCAT("", D7)</f>
         <v>Elementos.TGB</v>
       </c>
       <c r="N7" s="56" t="str">
@@ -3844,7 +3861,7 @@
         <v>Valor.X</v>
       </c>
       <c r="P7" s="56" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Q7" s="56" t="str">
         <f t="shared" ref="Q7:Q15" si="6">_xlfn.TRANSLATE(P7,"pt","es")</f>
@@ -3854,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="57" t="str">
-        <f t="shared" ref="S7:U20" si="7">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U21" si="7">SUBSTITUTE(C7, "_", " ")</f>
         <v>Formal</v>
       </c>
       <c r="T7" s="57" t="str">
@@ -3882,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="AA7" s="47" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3893,16 +3910,16 @@
         <v>93</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="67" t="s">
         <v>1</v>
@@ -3936,7 +3953,7 @@
         <v>Valor.Y</v>
       </c>
       <c r="P8" s="56" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Q8" s="56" t="str">
         <f t="shared" si="6"/>
@@ -3961,7 +3978,7 @@
         <v>90</v>
       </c>
       <c r="W8" s="59" t="str">
-        <f t="shared" ref="W8:W20" si="8">CONCATENATE("Key.EGC",".",A8)</f>
+        <f t="shared" ref="W8:W21" si="8">CONCATENATE("Key.EGC",".",A8)</f>
         <v>Key.EGC.8</v>
       </c>
       <c r="X8" s="47" t="s">
@@ -3974,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="AA8" s="47" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3985,16 +4002,16 @@
         <v>93</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G9" s="67" t="s">
         <v>1</v>
@@ -4028,7 +4045,7 @@
         <v>Valor.Z</v>
       </c>
       <c r="P9" s="56" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="Q9" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4066,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="AA9" s="47" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4077,16 +4094,16 @@
         <v>93</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="G10" s="67" t="s">
         <v>1</v>
@@ -4117,10 +4134,10 @@
       </c>
       <c r="O10" s="56" t="str">
         <f t="shared" si="5"/>
-        <v>Valor.Deslocar</v>
+        <v>Valor.Distância</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Q10" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4158,7 +4175,7 @@
         <v>1</v>
       </c>
       <c r="AA10" s="47" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4169,16 +4186,16 @@
         <v>93</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G11" s="67" t="s">
         <v>1</v>
@@ -4212,7 +4229,7 @@
         <v>Valor.Angular</v>
       </c>
       <c r="P11" s="56" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q11" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4250,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="AA11" s="47" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4261,16 +4278,16 @@
         <v>93</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G12" s="67" t="s">
         <v>1</v>
@@ -4304,7 +4321,7 @@
         <v>Valor.Escalar</v>
       </c>
       <c r="P12" s="56" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q12" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4342,7 +4359,7 @@
         <v>1</v>
       </c>
       <c r="AA12" s="47" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4353,16 +4370,16 @@
         <v>93</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G13" s="67" t="s">
         <v>1</v>
@@ -4396,7 +4413,7 @@
         <v>Ponto.Eixo1</v>
       </c>
       <c r="P13" s="56" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Q13" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4434,7 +4451,7 @@
         <v>1</v>
       </c>
       <c r="AA13" s="47" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4445,16 +4462,16 @@
         <v>93</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G14" s="67" t="s">
         <v>1</v>
@@ -4488,7 +4505,7 @@
         <v>Ponto.Eixo2</v>
       </c>
       <c r="P14" s="56" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="Q14" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4526,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="AA14" s="47" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4537,16 +4554,16 @@
         <v>93</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G15" s="67" t="s">
         <v>1</v>
@@ -4580,7 +4597,7 @@
         <v>Ponto.Base</v>
       </c>
       <c r="P15" s="56" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q15" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4618,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="AA15" s="47" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4629,16 +4646,16 @@
         <v>93</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G16" s="67" t="s">
         <v>1</v>
@@ -4672,10 +4689,10 @@
         <v>Ponto.Destino</v>
       </c>
       <c r="P16" s="56" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q16" s="56" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="R16" s="62" t="s">
         <v>1</v>
@@ -4709,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="AA16" s="47" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4720,16 +4737,16 @@
         <v>93</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>117</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="G17" s="67" t="s">
         <v>1</v>
@@ -4744,50 +4761,50 @@
         <v>1</v>
       </c>
       <c r="K17" s="67" t="s">
-        <v>145</v>
+        <v>217</v>
       </c>
       <c r="L17" s="56" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="L17" si="9">_xlfn.CONCAT(C17)</f>
         <v>Formal</v>
       </c>
       <c r="M17" s="56" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="M17" si="10">_xlfn.CONCAT("", D17)</f>
         <v>Elementos.TGB</v>
       </c>
       <c r="N17" s="56" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="N17" si="11">_xlfn.CONCAT("", E17)</f>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="O17" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Translação</v>
+        <f t="shared" ref="O17" si="12">_xlfn.CONCAT("", F17)</f>
+        <v>Translação.XYZ</v>
       </c>
       <c r="P17" s="56" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="Q17" s="56" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="R17" s="62" t="s">
         <v>1</v>
       </c>
       <c r="S17" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S17" si="13">SUBSTITUTE(C17, "_", " ")</f>
         <v>Formal</v>
       </c>
       <c r="T17" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="T17" si="14">SUBSTITUTE(D17, "_", " ")</f>
         <v>Elementos.TGB</v>
       </c>
       <c r="U17" s="58" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="U17" si="15">SUBSTITUTE(E17, "_", " ")</f>
         <v>Movimento.Geométrico</v>
       </c>
       <c r="V17" s="47" t="s">
         <v>90</v>
       </c>
       <c r="W17" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="W17" si="16">CONCATENATE("Key.EGC",".",A17)</f>
         <v>Key.EGC.17</v>
       </c>
       <c r="X17" s="47" t="s">
@@ -4800,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="AA17" s="47" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4811,16 +4828,16 @@
         <v>93</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>117</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="G18" s="67" t="s">
         <v>1</v>
@@ -4835,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="67" t="s">
-        <v>138</v>
+        <v>219</v>
       </c>
       <c r="L18" s="56" t="str">
         <f t="shared" si="4"/>
@@ -4851,13 +4868,13 @@
       </c>
       <c r="O18" s="56" t="str">
         <f t="shared" si="5"/>
-        <v>Giro</v>
+        <v>Translação.Polar</v>
       </c>
       <c r="P18" s="56" t="s">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="Q18" s="56" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="R18" s="62" t="s">
         <v>1</v>
@@ -4891,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="AA18" s="47" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4902,16 +4919,16 @@
         <v>93</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>117</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G19" s="67" t="s">
         <v>1</v>
@@ -4942,13 +4959,13 @@
       </c>
       <c r="O19" s="56" t="str">
         <f t="shared" si="5"/>
-        <v>Escalar</v>
+        <v>Giro</v>
       </c>
       <c r="P19" s="56" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Q19" s="56" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="R19" s="62" t="s">
         <v>1</v>
@@ -4982,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="AA19" s="47" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4993,16 +5010,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>117</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G20" s="67" t="s">
         <v>1</v>
@@ -5017,7 +5034,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="67" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="L20" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5033,13 +5050,13 @@
       </c>
       <c r="O20" s="56" t="str">
         <f t="shared" si="5"/>
-        <v>Reflexão</v>
+        <v>Escalar</v>
       </c>
       <c r="P20" s="56" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="Q20" s="56" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="R20" s="62" t="s">
         <v>1</v>
@@ -5073,26 +5090,117 @@
         <v>1</v>
       </c>
       <c r="AA20" s="47" t="s">
-        <v>222</v>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="61">
+        <v>21</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="L21" s="56" t="str">
+        <f t="shared" si="4"/>
+        <v>Formal</v>
+      </c>
+      <c r="M21" s="56" t="str">
+        <f t="shared" si="5"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N21" s="56" t="str">
+        <f t="shared" si="5"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O21" s="56" t="str">
+        <f t="shared" si="5"/>
+        <v>Reflexão</v>
+      </c>
+      <c r="P21" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q21" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="R21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21" s="57" t="str">
+        <f t="shared" si="7"/>
+        <v>Formal</v>
+      </c>
+      <c r="T21" s="57" t="str">
+        <f t="shared" si="7"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U21" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V21" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="W21" s="59" t="str">
+        <f t="shared" si="8"/>
+        <v>Key.EGC.21</v>
+      </c>
+      <c r="X21" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="47" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:A21">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F7:F20">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+  <conditionalFormatting sqref="F1 F7:F21">
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5102,6 +5210,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
+  <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -5309,7 +5418,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5320,6 +5429,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
+  <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5352,7 +5462,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5362,6 +5472,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
+  <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5458,16 +5569,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F2" s="54" t="s">
         <v>1</v>
@@ -5494,28 +5605,28 @@
         <v>115</v>
       </c>
       <c r="N2" s="39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O2" s="70">
         <v>1.05</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="70">
         <v>1.05</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S2" s="70">
         <v>1.05</v>
       </c>
       <c r="T2" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="U2" s="52" t="s">
         <v>127</v>
-      </c>
-      <c r="U2" s="52" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5523,16 +5634,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F3" s="54" t="s">
         <v>1</v>
@@ -5559,28 +5670,28 @@
         <v>116</v>
       </c>
       <c r="N3" s="39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O3" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="P3" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="R3" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S3" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="T3" s="39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U3" s="52" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5588,16 +5699,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="54" t="s">
         <v>1</v>
@@ -5621,31 +5732,31 @@
         <v>96</v>
       </c>
       <c r="M4" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N4" s="39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O4" s="70">
         <v>3.05</v>
       </c>
       <c r="P4" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q4" s="70">
         <v>3.05</v>
       </c>
       <c r="R4" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S4" s="70">
         <v>3.05</v>
       </c>
       <c r="T4" s="39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U4" s="52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5653,10 +5764,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="54" t="s">
         <v>1</v>
@@ -5686,31 +5797,31 @@
         <v>96</v>
       </c>
       <c r="M5" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>127</v>
-      </c>
       <c r="U5" s="52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5718,10 +5829,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D6" s="54" t="s">
         <v>1</v>
@@ -5751,7 +5862,7 @@
         <v>96</v>
       </c>
       <c r="M6" s="41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N6" s="39" t="s">
         <v>1</v>
@@ -5783,10 +5894,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D7" s="54" t="s">
         <v>1</v>
@@ -5816,7 +5927,7 @@
         <v>96</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N7" s="39" t="s">
         <v>1</v>
@@ -5848,22 +5959,22 @@
         <v>8</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G8" s="55" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H8" s="44" t="s">
         <v>1</v>
@@ -5881,7 +5992,7 @@
         <v>96</v>
       </c>
       <c r="M8" s="41" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N8" s="39" t="s">
         <v>1</v>
@@ -5913,22 +6024,22 @@
         <v>9</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G9" s="55" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H9" s="44" t="s">
         <v>1</v>
@@ -5946,7 +6057,7 @@
         <v>96</v>
       </c>
       <c r="M9" s="41" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N9" s="39" t="s">
         <v>1</v>
@@ -5978,10 +6089,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="D10" s="54" t="s">
         <v>1</v>
@@ -6011,7 +6122,7 @@
         <v>96</v>
       </c>
       <c r="M10" s="41" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="N10" s="39" t="s">
         <v>1</v>
@@ -6043,10 +6154,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D11" s="54" t="s">
         <v>1</v>
@@ -6076,7 +6187,7 @@
         <v>96</v>
       </c>
       <c r="M11" s="41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>1</v>
@@ -6108,10 +6219,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" s="54" t="s">
         <v>1</v>
@@ -6141,7 +6252,7 @@
         <v>96</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N12" s="39" t="s">
         <v>1</v>
@@ -6170,12 +6281,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B12 H1:M12">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6183,6 +6294,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
+  <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4437DF90-3F2D-4BD7-A476-7D4FAB9825AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF670F38-DB41-4E5A-8AC3-40E76FA4ECA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="239">
   <si>
     <t>Key</t>
   </si>
@@ -1609,12 +1609,6 @@
     <t>Formalizar conceptos de las  Estructuras Genéticamente Construídas</t>
   </si>
   <si>
-    <t>"Uma translação"</t>
-  </si>
-  <si>
-    <t>"Uma rotação"</t>
-  </si>
-  <si>
     <t>Movimento.Geométrico</t>
   </si>
   <si>
@@ -1636,12 +1630,6 @@
     <t>Ponto.Destino</t>
   </si>
   <si>
-    <t>"Uma mudança escalar"</t>
-  </si>
-  <si>
-    <t>"Uma reflexão"</t>
-  </si>
-  <si>
     <t>código.ontogenético</t>
   </si>
   <si>
@@ -1660,18 +1648,6 @@
     <t>"O ponto base da transformação"</t>
   </si>
   <si>
-    <t>coordenada.x</t>
-  </si>
-  <si>
-    <t>coordenada.y</t>
-  </si>
-  <si>
-    <t>coordenada.z</t>
-  </si>
-  <si>
-    <t>"O valor de um ângulo absoluto"</t>
-  </si>
-  <si>
     <t>Ponto.Base and Valor.Escalar</t>
   </si>
   <si>
@@ -1696,15 +1672,6 @@
     <t>PB1</t>
   </si>
   <si>
-    <t>Vd1</t>
-  </si>
-  <si>
-    <t>Va1</t>
-  </si>
-  <si>
-    <t>Va2</t>
-  </si>
-  <si>
     <t>é.ponto.base</t>
   </si>
   <si>
@@ -1714,18 +1681,12 @@
     <t>"O Ponto Base do Projeto"</t>
   </si>
   <si>
-    <t>"A Translação principal dos módulos estruturais horizontais"</t>
-  </si>
-  <si>
     <t>TRA_Hor</t>
   </si>
   <si>
     <t>TRA_Ver</t>
   </si>
   <si>
-    <t>"A Translação principal dos módulos estruturais verticais"</t>
-  </si>
-  <si>
     <t>T1</t>
   </si>
   <si>
@@ -1924,9 +1885,6 @@
     <t>Valor.Distância and Valor.Angular</t>
   </si>
   <si>
-    <t>"Um valor de distância de deslocamento"</t>
-  </si>
-  <si>
     <t>Translação.XYZ</t>
   </si>
   <si>
@@ -1946,6 +1904,81 @@
   </si>
   <si>
     <t>Polar translation. The transformation that modifies the position of a point by means of a linear displacement. You need base point and target point.</t>
+  </si>
+  <si>
+    <t>valor.angular</t>
+  </si>
+  <si>
+    <t>valor.escalar</t>
+  </si>
+  <si>
+    <t>base.x</t>
+  </si>
+  <si>
+    <t>base.y</t>
+  </si>
+  <si>
+    <t>base.z</t>
+  </si>
+  <si>
+    <t>base.xx</t>
+  </si>
+  <si>
+    <t>base.zz</t>
+  </si>
+  <si>
+    <t>base.yy</t>
+  </si>
+  <si>
+    <t>"Uma translação absoluta definindo o deslocamento"</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>"Uma translação relativa definindo 2 pontos do vetor de translação"</t>
+  </si>
+  <si>
+    <t>"Uma rotação definindo centro de giro e ángulo"</t>
+  </si>
+  <si>
+    <t>"Uma mudança escalar definindo centro de homotetira e fator de escala"</t>
+  </si>
+  <si>
+    <t>"Uma reflexão definindo dois pontos do eixo de reflexão"</t>
+  </si>
+  <si>
+    <t>"A Translação principal dos módulos estruturais verticais usando uma transformação já definida"</t>
+  </si>
+  <si>
+    <t>"A Translação principal dos módulos estruturais horizontais usando uma transformação já definida"</t>
+  </si>
+  <si>
+    <t>"Definição de um valor de distância de deslocamento para usar em alguma transformação"</t>
+  </si>
+  <si>
+    <t>"Definição de um valor de ângulo absoluto para usar em alguma transformação"</t>
+  </si>
+  <si>
+    <t>A90</t>
+  </si>
+  <si>
+    <t>A60</t>
+  </si>
+  <si>
+    <t>DI1</t>
+  </si>
+  <si>
+    <t>DI-Ex1-Ex2</t>
+  </si>
+  <si>
+    <t>"Definição de um valor hipotético entre os Eixos 1 e 2 de um projeto hipotético"</t>
+  </si>
+  <si>
+    <t>valor.distância</t>
+  </si>
+  <si>
+    <t>5.45</t>
   </si>
 </sst>
 </file>
@@ -2302,7 +2335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2513,6 +2546,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2535,14 +2571,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2617,6 +2645,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2936,15 +2972,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -2955,7 +2991,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -2966,7 +3002,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -2977,7 +3013,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -2988,7 +3024,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3000,7 +3036,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3012,7 +3048,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3023,7 +3059,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3034,7 +3070,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3045,7 +3081,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3056,7 +3092,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3067,7 +3103,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3078,7 +3114,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3089,7 +3125,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3100,7 +3136,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3111,7 +3147,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3122,7 +3158,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3133,19 +3169,19 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46142.721239814811</v>
+        <v>46143.508998611112</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>109</v>
       </c>
@@ -3156,7 +3192,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>107</v>
       </c>
@@ -3168,7 +3204,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>108</v>
       </c>
@@ -3180,7 +3216,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3191,7 +3227,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3202,7 +3238,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3213,7 +3249,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3224,7 +3260,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>101</v>
       </c>
@@ -3245,34 +3281,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.69140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.84375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="65.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.15234375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="65.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="71.84375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="69.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.53515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.15234375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="69.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3355,24 +3391,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="61">
         <v>2</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E2" s="63" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G2" s="66" t="s">
         <v>1</v>
@@ -3406,10 +3442,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="47" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="Q2" s="47" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="R2" s="62" t="s">
         <v>1</v>
@@ -3443,27 +3479,27 @@
         <v>1</v>
       </c>
       <c r="AA2" s="47" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="61">
         <v>3</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G3" s="66" t="s">
         <v>1</v>
@@ -3497,10 +3533,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="47" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="Q3" s="47" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>1</v>
@@ -3534,27 +3570,27 @@
         <v>1</v>
       </c>
       <c r="AA3" s="47" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="61">
         <v>4</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E4" s="63" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G4" s="66" t="s">
         <v>1</v>
@@ -3588,10 +3624,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="47" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="Q4" s="47" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>1</v>
@@ -3625,27 +3661,27 @@
         <v>1</v>
       </c>
       <c r="AA4" s="47" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="61">
         <v>5</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E5" s="63" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G5" s="66" t="s">
         <v>1</v>
@@ -3679,10 +3715,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="Q5" s="47" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>1</v>
@@ -3716,27 +3752,27 @@
         <v>1</v>
       </c>
       <c r="AA5" s="47" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="61">
         <v>6</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C6" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="64" t="s">
         <v>177</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="64" t="s">
-        <v>190</v>
       </c>
       <c r="G6" s="66" t="s">
         <v>1</v>
@@ -3770,10 +3806,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="Q6" s="47" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="R6" s="62" t="s">
         <v>1</v>
@@ -3807,10 +3843,10 @@
         <v>1</v>
       </c>
       <c r="AA6" s="47" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="61">
         <v>7</v>
       </c>
@@ -3818,16 +3854,16 @@
         <v>93</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G7" s="67" t="s">
         <v>1</v>
@@ -3861,7 +3897,7 @@
         <v>Valor.X</v>
       </c>
       <c r="P7" s="56" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="Q7" s="56" t="str">
         <f t="shared" ref="Q7:Q15" si="6">_xlfn.TRANSLATE(P7,"pt","es")</f>
@@ -3899,10 +3935,10 @@
         <v>1</v>
       </c>
       <c r="AA7" s="47" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="61">
         <v>8</v>
       </c>
@@ -3910,16 +3946,16 @@
         <v>93</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G8" s="67" t="s">
         <v>1</v>
@@ -3953,7 +3989,7 @@
         <v>Valor.Y</v>
       </c>
       <c r="P8" s="56" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="Q8" s="56" t="str">
         <f t="shared" si="6"/>
@@ -3991,10 +4027,10 @@
         <v>1</v>
       </c>
       <c r="AA8" s="47" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="61">
         <v>9</v>
       </c>
@@ -4002,16 +4038,16 @@
         <v>93</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G9" s="67" t="s">
         <v>1</v>
@@ -4045,7 +4081,7 @@
         <v>Valor.Z</v>
       </c>
       <c r="P9" s="56" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="Q9" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4083,10 +4119,10 @@
         <v>1</v>
       </c>
       <c r="AA9" s="47" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="61">
         <v>10</v>
       </c>
@@ -4094,16 +4130,16 @@
         <v>93</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="G10" s="67" t="s">
         <v>1</v>
@@ -4137,7 +4173,7 @@
         <v>Valor.Distância</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="Q10" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4175,10 +4211,10 @@
         <v>1</v>
       </c>
       <c r="AA10" s="47" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="61">
         <v>11</v>
       </c>
@@ -4186,16 +4222,16 @@
         <v>93</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G11" s="67" t="s">
         <v>1</v>
@@ -4229,7 +4265,7 @@
         <v>Valor.Angular</v>
       </c>
       <c r="P11" s="56" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="Q11" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4267,10 +4303,10 @@
         <v>1</v>
       </c>
       <c r="AA11" s="47" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="61">
         <v>12</v>
       </c>
@@ -4278,16 +4314,16 @@
         <v>93</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G12" s="67" t="s">
         <v>1</v>
@@ -4321,7 +4357,7 @@
         <v>Valor.Escalar</v>
       </c>
       <c r="P12" s="56" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="Q12" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4359,10 +4395,10 @@
         <v>1</v>
       </c>
       <c r="AA12" s="47" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="61">
         <v>13</v>
       </c>
@@ -4370,16 +4406,16 @@
         <v>93</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="G13" s="67" t="s">
         <v>1</v>
@@ -4413,7 +4449,7 @@
         <v>Ponto.Eixo1</v>
       </c>
       <c r="P13" s="56" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="Q13" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4451,10 +4487,10 @@
         <v>1</v>
       </c>
       <c r="AA13" s="47" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="61">
         <v>14</v>
       </c>
@@ -4462,16 +4498,16 @@
         <v>93</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="G14" s="67" t="s">
         <v>1</v>
@@ -4505,7 +4541,7 @@
         <v>Ponto.Eixo2</v>
       </c>
       <c r="P14" s="56" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="Q14" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4543,10 +4579,10 @@
         <v>1</v>
       </c>
       <c r="AA14" s="47" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="61">
         <v>15</v>
       </c>
@@ -4554,16 +4590,16 @@
         <v>93</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G15" s="67" t="s">
         <v>1</v>
@@ -4597,7 +4633,7 @@
         <v>Ponto.Base</v>
       </c>
       <c r="P15" s="56" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="Q15" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4635,10 +4671,10 @@
         <v>1</v>
       </c>
       <c r="AA15" s="47" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="61">
         <v>16</v>
       </c>
@@ -4646,16 +4682,16 @@
         <v>93</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G16" s="67" t="s">
         <v>1</v>
@@ -4689,10 +4725,10 @@
         <v>Ponto.Destino</v>
       </c>
       <c r="P16" s="56" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="Q16" s="56" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="R16" s="62" t="s">
         <v>1</v>
@@ -4726,10 +4762,10 @@
         <v>1</v>
       </c>
       <c r="AA16" s="47" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="61">
         <v>17</v>
       </c>
@@ -4737,16 +4773,16 @@
         <v>93</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G17" s="67" t="s">
         <v>1</v>
@@ -4761,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="67" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="L17" s="56" t="str">
         <f t="shared" ref="L17" si="9">_xlfn.CONCAT(C17)</f>
@@ -4780,10 +4816,10 @@
         <v>Translação.XYZ</v>
       </c>
       <c r="P17" s="56" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="Q17" s="56" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="R17" s="62" t="s">
         <v>1</v>
@@ -4817,10 +4853,10 @@
         <v>1</v>
       </c>
       <c r="AA17" s="47" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="61">
         <v>18</v>
       </c>
@@ -4828,16 +4864,16 @@
         <v>93</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G18" s="67" t="s">
         <v>1</v>
@@ -4852,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="67" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="L18" s="56" t="str">
         <f t="shared" si="4"/>
@@ -4871,10 +4907,10 @@
         <v>Translação.Polar</v>
       </c>
       <c r="P18" s="56" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="Q18" s="56" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="R18" s="62" t="s">
         <v>1</v>
@@ -4908,10 +4944,10 @@
         <v>1</v>
       </c>
       <c r="AA18" s="47" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="61">
         <v>19</v>
       </c>
@@ -4919,16 +4955,16 @@
         <v>93</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G19" s="67" t="s">
         <v>1</v>
@@ -4943,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="67" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="L19" s="56" t="str">
         <f t="shared" si="4"/>
@@ -4962,10 +4998,10 @@
         <v>Giro</v>
       </c>
       <c r="P19" s="56" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="Q19" s="56" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="R19" s="62" t="s">
         <v>1</v>
@@ -4999,10 +5035,10 @@
         <v>1</v>
       </c>
       <c r="AA19" s="47" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="61">
         <v>20</v>
       </c>
@@ -5010,17 +5046,17 @@
         <v>93</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E20" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="51" t="s">
-        <v>119</v>
-      </c>
       <c r="G20" s="67" t="s">
         <v>1</v>
       </c>
@@ -5034,7 +5070,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="67" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="L20" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5053,10 +5089,10 @@
         <v>Escalar</v>
       </c>
       <c r="P20" s="56" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="Q20" s="56" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="R20" s="62" t="s">
         <v>1</v>
@@ -5090,10 +5126,10 @@
         <v>1</v>
       </c>
       <c r="AA20" s="47" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="61">
         <v>21</v>
       </c>
@@ -5101,16 +5137,16 @@
         <v>93</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G21" s="67" t="s">
         <v>1</v>
@@ -5125,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="67" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="L21" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5144,10 +5180,10 @@
         <v>Reflexão</v>
       </c>
       <c r="P21" s="56" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="Q21" s="56" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="R21" s="62" t="s">
         <v>1</v>
@@ -5181,26 +5217,26 @@
         <v>1</v>
       </c>
       <c r="AA21" s="47" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A21">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F7:F21">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5212,15 +5248,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
@@ -5285,7 +5321,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="35">
         <v>2</v>
       </c>
@@ -5350,7 +5386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35">
         <v>3</v>
       </c>
@@ -5418,7 +5454,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5431,14 +5467,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="32">
         <v>1</v>
       </c>
@@ -5449,7 +5485,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5462,7 +5498,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5473,33 +5509,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC14"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" customWidth="1"/>
-    <col min="13" max="13" width="28.140625" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
-    <col min="15" max="15" width="3.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" customWidth="1"/>
-    <col min="17" max="17" width="3.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.140625" customWidth="1"/>
-    <col min="19" max="19" width="4.5703125" style="71" customWidth="1"/>
-    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" customWidth="1"/>
+    <col min="3" max="3" width="7.53515625" customWidth="1"/>
+    <col min="4" max="4" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="3.53515625" customWidth="1"/>
+    <col min="12" max="12" width="5.15234375" customWidth="1"/>
+    <col min="13" max="13" width="38.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.23046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.15234375" customWidth="1"/>
+    <col min="17" max="17" width="4.23046875" style="71" customWidth="1"/>
+    <col min="18" max="18" width="5.15234375" customWidth="1"/>
+    <col min="19" max="19" width="4.23046875" style="71" customWidth="1"/>
+    <col min="20" max="20" width="5.15234375" customWidth="1"/>
+    <col min="21" max="21" width="4.23046875" style="71" customWidth="1"/>
+    <col min="22" max="22" width="5.15234375" style="72" customWidth="1"/>
+    <col min="23" max="23" width="4.23046875" style="71" customWidth="1"/>
+    <col min="24" max="24" width="5.15234375" style="72" customWidth="1"/>
+    <col min="25" max="25" width="4.23046875" style="71" customWidth="1"/>
+    <col min="26" max="26" width="5.15234375" style="72" customWidth="1"/>
+    <col min="27" max="27" width="4.23046875" style="71" customWidth="1"/>
+    <col min="28" max="28" width="5.921875" customWidth="1"/>
+    <col min="29" max="29" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -5542,10 +5583,10 @@
       <c r="N1" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="69" t="s">
+      <c r="O1" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="31" t="s">
         <v>48</v>
       </c>
       <c r="Q1" s="69" t="s">
@@ -5557,28 +5598,52 @@
       <c r="S1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="31" t="s">
+      <c r="T1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="U1" s="69" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V1" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="W1" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="X1" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z1" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB1" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC1" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="28">
         <v>2</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="D2" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>143</v>
+        <v>207</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>1</v>
       </c>
       <c r="F2" s="54" t="s">
         <v>1</v>
@@ -5602,48 +5667,72 @@
         <v>96</v>
       </c>
       <c r="M2" s="41" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="N2" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="O2" s="70">
-        <v>1.05</v>
+        <v>122</v>
+      </c>
+      <c r="O2" s="52" t="s">
+        <v>123</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="Q2" s="70">
         <v>1.05</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="S2" s="70">
         <v>1.05</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="U2" s="52" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="U2" s="70">
+        <v>0</v>
+      </c>
+      <c r="V2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="28">
         <v>3</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="55" t="s">
-        <v>143</v>
+        <v>207</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>1</v>
       </c>
       <c r="F3" s="54" t="s">
         <v>1</v>
@@ -5667,48 +5756,72 @@
         <v>96</v>
       </c>
       <c r="M3" s="41" t="s">
-        <v>116</v>
+        <v>224</v>
       </c>
       <c r="N3" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="O3" s="70">
-        <v>2.0499999999999998</v>
+        <v>122</v>
+      </c>
+      <c r="O3" s="52" t="s">
+        <v>123</v>
       </c>
       <c r="P3" s="39" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="Q3" s="70">
-        <v>2.0499999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="R3" s="39" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="S3" s="70">
-        <v>2.0499999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="T3" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="U3" s="52" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="U3" s="70">
+        <v>0</v>
+      </c>
+      <c r="V3" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="W3" s="70">
+        <v>5.2</v>
+      </c>
+      <c r="X3" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y3" s="70">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA3" s="70">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="28">
         <v>4</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>143</v>
+        <v>116</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>1</v>
       </c>
       <c r="F4" s="54" t="s">
         <v>1</v>
@@ -5732,42 +5845,66 @@
         <v>96</v>
       </c>
       <c r="M4" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="N4" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="O4" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="N4" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="O4" s="70">
-        <v>3.05</v>
-      </c>
       <c r="P4" s="39" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="Q4" s="70">
-        <v>3.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="R4" s="39" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="S4" s="70">
-        <v>3.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="T4" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="U4" s="52" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="U4" s="70">
+        <v>0</v>
+      </c>
+      <c r="V4" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC4" s="52">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="28">
         <v>5</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" s="54" t="s">
         <v>1</v>
@@ -5797,42 +5934,66 @@
         <v>96</v>
       </c>
       <c r="M5" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="O5" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" s="70" t="s">
-        <v>1</v>
-      </c>
       <c r="P5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="70" t="s">
-        <v>1</v>
+        <v>216</v>
+      </c>
+      <c r="Q5" s="70">
+        <v>3.05</v>
       </c>
       <c r="R5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="70" t="s">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="S5" s="70">
+        <v>3.05</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="U5" s="52" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="U5" s="70">
+        <v>0</v>
+      </c>
+      <c r="V5" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC5" s="52">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="28">
         <v>6</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D6" s="54" t="s">
         <v>1</v>
@@ -5862,42 +6023,66 @@
         <v>96</v>
       </c>
       <c r="M6" s="41" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="N6" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" s="70" t="s">
-        <v>1</v>
+        <v>122</v>
+      </c>
+      <c r="O6" s="52" t="s">
+        <v>126</v>
       </c>
       <c r="P6" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="70" t="s">
-        <v>1</v>
+        <v>216</v>
+      </c>
+      <c r="Q6" s="70">
+        <v>4.05</v>
       </c>
       <c r="R6" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="70" t="s">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="S6" s="70">
+        <v>4.05</v>
       </c>
       <c r="T6" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U6" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="U6" s="70">
+        <v>0</v>
+      </c>
+      <c r="V6" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="W6" s="70">
+        <v>14.05</v>
+      </c>
+      <c r="X6" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y6" s="70">
+        <v>14.05</v>
+      </c>
+      <c r="Z6" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA6" s="70">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="28">
         <v>7</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D7" s="54" t="s">
         <v>1</v>
@@ -5927,12 +6112,12 @@
         <v>96</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="N7" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O7" s="70" t="s">
+      <c r="O7" s="52" t="s">
         <v>1</v>
       </c>
       <c r="P7" s="39" t="s">
@@ -5950,31 +6135,55 @@
       <c r="T7" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U7" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="28">
         <v>8</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" s="55" t="s">
-        <v>154</v>
+        <v>120</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>1</v>
       </c>
       <c r="H8" s="44" t="s">
         <v>1</v>
@@ -5992,12 +6201,12 @@
         <v>96</v>
       </c>
       <c r="M8" s="41" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="N8" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O8" s="70" t="s">
+      <c r="O8" s="52" t="s">
         <v>1</v>
       </c>
       <c r="P8" s="39" t="s">
@@ -6015,31 +6224,55 @@
       <c r="T8" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U8" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="28">
         <v>9</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="G9" s="55" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="H9" s="44" t="s">
         <v>1</v>
@@ -6057,12 +6290,12 @@
         <v>96</v>
       </c>
       <c r="M9" s="41" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="N9" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O9" s="70" t="s">
+      <c r="O9" s="52" t="s">
         <v>1</v>
       </c>
       <c r="P9" s="39" t="s">
@@ -6080,31 +6313,55 @@
       <c r="T9" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U9" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="28">
         <v>10</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="D10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="60" t="s">
-        <v>1</v>
+        <v>207</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="G10" s="55" t="s">
+        <v>223</v>
       </c>
       <c r="H10" s="44" t="s">
         <v>1</v>
@@ -6122,12 +6379,12 @@
         <v>96</v>
       </c>
       <c r="M10" s="41" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="N10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O10" s="70" t="s">
+      <c r="O10" s="52" t="s">
         <v>1</v>
       </c>
       <c r="P10" s="39" t="s">
@@ -6145,19 +6402,43 @@
       <c r="T10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U10" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="28">
         <v>11</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="D11" s="54" t="s">
         <v>1</v>
@@ -6187,12 +6468,12 @@
         <v>96</v>
       </c>
       <c r="M11" s="41" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="70" t="s">
+      <c r="O11" s="52" t="s">
         <v>1</v>
       </c>
       <c r="P11" s="39" t="s">
@@ -6210,19 +6491,43 @@
       <c r="T11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U11" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="28">
         <v>12</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="D12" s="54" t="s">
         <v>1</v>
@@ -6252,12 +6557,12 @@
         <v>96</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="N12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O12" s="70" t="s">
+      <c r="O12" s="52" t="s">
         <v>1</v>
       </c>
       <c r="P12" s="39" t="s">
@@ -6275,17 +6580,220 @@
       <c r="T12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="U12" s="52" t="s">
-        <v>1</v>
+      <c r="U12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="AC12" s="52" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28">
+        <v>13</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="N13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V13" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC13" s="52">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28">
+        <v>14</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="N14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC14" s="52">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B12 H1:M12">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="H1:M14 A1:B14">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B12">
+  <conditionalFormatting sqref="B1:B14">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -6296,14 +6804,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6311,7 +6819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6319,7 +6827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6327,7 +6835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6335,7 +6843,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6343,7 +6851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6351,7 +6859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6359,7 +6867,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6367,7 +6875,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6375,7 +6883,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6383,7 +6891,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6391,7 +6899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6399,7 +6907,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6407,7 +6915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6415,7 +6923,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF670F38-DB41-4E5A-8AC3-40E76FA4ECA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E539C8C-632A-4254-8D20-B2929A92A279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="240">
   <si>
     <t>Key</t>
   </si>
@@ -1645,9 +1645,6 @@
     <t>"R"</t>
   </si>
   <si>
-    <t>"O ponto base da transformação"</t>
-  </si>
-  <si>
     <t>Ponto.Base and Valor.Escalar</t>
   </si>
   <si>
@@ -1678,9 +1675,6 @@
     <t>PBP</t>
   </si>
   <si>
-    <t>"O Ponto Base do Projeto"</t>
-  </si>
-  <si>
     <t>TRA_Hor</t>
   </si>
   <si>
@@ -1939,27 +1933,9 @@
     <t>"Uma translação relativa definindo 2 pontos do vetor de translação"</t>
   </si>
   <si>
-    <t>"Uma rotação definindo centro de giro e ángulo"</t>
-  </si>
-  <si>
-    <t>"Uma mudança escalar definindo centro de homotetira e fator de escala"</t>
-  </si>
-  <si>
-    <t>"Uma reflexão definindo dois pontos do eixo de reflexão"</t>
-  </si>
-  <si>
-    <t>"A Translação principal dos módulos estruturais verticais usando uma transformação já definida"</t>
-  </si>
-  <si>
-    <t>"A Translação principal dos módulos estruturais horizontais usando uma transformação já definida"</t>
-  </si>
-  <si>
     <t>"Definição de um valor de distância de deslocamento para usar em alguma transformação"</t>
   </si>
   <si>
-    <t>"Definição de um valor de ângulo absoluto para usar em alguma transformação"</t>
-  </si>
-  <si>
     <t>A90</t>
   </si>
   <si>
@@ -1972,13 +1948,40 @@
     <t>DI-Ex1-Ex2</t>
   </si>
   <si>
-    <t>"Definição de um valor hipotético entre os Eixos 1 e 2 de um projeto hipotético"</t>
-  </si>
-  <si>
     <t>valor.distância</t>
   </si>
   <si>
     <t>5.45</t>
+  </si>
+  <si>
+    <t>"Uma rotação definida pelo seu centro de giro e ángulo"</t>
+  </si>
+  <si>
+    <t>"Uma mudança escalar definida pelo seu centro de homotetia e o fator escalar"</t>
+  </si>
+  <si>
+    <t>"Uma reflexão definida por dois pontos do eixo de reflexão"</t>
+  </si>
+  <si>
+    <t>"O ponto base de uma transformação qualquer"</t>
+  </si>
+  <si>
+    <t>"O ponto base de implantação de um projeto qualquer"</t>
+  </si>
+  <si>
+    <t>"A Translação principal de módulos estruturais horizontais hipotéticos usando uma transformação já definida"</t>
+  </si>
+  <si>
+    <t>"A Translação principal dos módulos estruturais verticais hipotéticos usando uma transformação já definida"</t>
+  </si>
+  <si>
+    <t>"Definição de um valor de distância hipotético entre os Eixos 1 e 2 de um projeto qualquer"</t>
+  </si>
+  <si>
+    <t>"Definição de um valor de ângulo absoluto de 90 graus para usar em alguma transformação"</t>
+  </si>
+  <si>
+    <t>"Definição de um valor de ângulo absoluto de 60 graus para usar em alguma transformação"</t>
   </si>
 </sst>
 </file>
@@ -2556,14 +2559,6 @@
   <dxfs count="11">
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2571,6 +2566,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3175,7 +3178,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46143.508998611112</v>
+        <v>46143.51546678241</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>104</v>
@@ -3396,19 +3399,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="E2" s="63" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="F2" s="64" t="s">
         <v>165</v>
-      </c>
-      <c r="E2" s="63" t="s">
-        <v>166</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>167</v>
       </c>
       <c r="G2" s="66" t="s">
         <v>1</v>
@@ -3442,10 +3445,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Q2" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R2" s="62" t="s">
         <v>1</v>
@@ -3479,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="AA2" s="47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3487,19 +3490,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="C3" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>165</v>
-      </c>
       <c r="E3" s="63" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G3" s="66" t="s">
         <v>1</v>
@@ -3533,10 +3536,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q3" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>1</v>
@@ -3570,7 +3573,7 @@
         <v>1</v>
       </c>
       <c r="AA3" s="47" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3578,19 +3581,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>165</v>
-      </c>
       <c r="E4" s="63" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G4" s="66" t="s">
         <v>1</v>
@@ -3624,10 +3627,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q4" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>1</v>
@@ -3661,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="AA4" s="47" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3669,19 +3672,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>165</v>
-      </c>
       <c r="E5" s="63" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G5" s="66" t="s">
         <v>1</v>
@@ -3715,10 +3718,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q5" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>1</v>
@@ -3752,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="AA5" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3760,19 +3763,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="C6" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>165</v>
-      </c>
       <c r="E6" s="63" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G6" s="66" t="s">
         <v>1</v>
@@ -3806,10 +3809,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Q6" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R6" s="62" t="s">
         <v>1</v>
@@ -3843,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="AA6" s="47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3854,16 +3857,16 @@
         <v>93</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G7" s="67" t="s">
         <v>1</v>
@@ -3897,7 +3900,7 @@
         <v>Valor.X</v>
       </c>
       <c r="P7" s="56" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q7" s="56" t="str">
         <f t="shared" ref="Q7:Q15" si="6">_xlfn.TRANSLATE(P7,"pt","es")</f>
@@ -3935,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="AA7" s="47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3946,16 +3949,16 @@
         <v>93</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G8" s="67" t="s">
         <v>1</v>
@@ -3989,7 +3992,7 @@
         <v>Valor.Y</v>
       </c>
       <c r="P8" s="56" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q8" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4027,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="AA8" s="47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4038,16 +4041,16 @@
         <v>93</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G9" s="67" t="s">
         <v>1</v>
@@ -4081,7 +4084,7 @@
         <v>Valor.Z</v>
       </c>
       <c r="P9" s="56" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q9" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4119,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="AA9" s="47" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4130,16 +4133,16 @@
         <v>93</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G10" s="67" t="s">
         <v>1</v>
@@ -4173,7 +4176,7 @@
         <v>Valor.Distância</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q10" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4211,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="AA10" s="47" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4222,16 +4225,16 @@
         <v>93</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G11" s="67" t="s">
         <v>1</v>
@@ -4265,7 +4268,7 @@
         <v>Valor.Angular</v>
       </c>
       <c r="P11" s="56" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Q11" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4303,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="AA11" s="47" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4314,16 +4317,16 @@
         <v>93</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" s="67" t="s">
         <v>1</v>
@@ -4357,7 +4360,7 @@
         <v>Valor.Escalar</v>
       </c>
       <c r="P12" s="56" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q12" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4395,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="AA12" s="47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4406,16 +4409,16 @@
         <v>93</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G13" s="67" t="s">
         <v>1</v>
@@ -4449,7 +4452,7 @@
         <v>Ponto.Eixo1</v>
       </c>
       <c r="P13" s="56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q13" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4487,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="AA13" s="47" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4498,16 +4501,16 @@
         <v>93</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G14" s="67" t="s">
         <v>1</v>
@@ -4541,7 +4544,7 @@
         <v>Ponto.Eixo2</v>
       </c>
       <c r="P14" s="56" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q14" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4579,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="AA14" s="47" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4590,13 +4593,13 @@
         <v>93</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F15" s="51" t="s">
         <v>120</v>
@@ -4633,7 +4636,7 @@
         <v>Ponto.Base</v>
       </c>
       <c r="P15" s="56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q15" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4671,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="AA15" s="47" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4682,13 +4685,13 @@
         <v>93</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F16" s="51" t="s">
         <v>121</v>
@@ -4725,10 +4728,10 @@
         <v>Ponto.Destino</v>
       </c>
       <c r="P16" s="56" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q16" s="56" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R16" s="62" t="s">
         <v>1</v>
@@ -4762,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="AA16" s="47" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4773,16 +4776,16 @@
         <v>93</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>115</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G17" s="67" t="s">
         <v>1</v>
@@ -4797,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="67" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L17" s="56" t="str">
         <f t="shared" ref="L17" si="9">_xlfn.CONCAT(C17)</f>
@@ -4816,10 +4819,10 @@
         <v>Translação.XYZ</v>
       </c>
       <c r="P17" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q17" s="56" t="s">
         <v>209</v>
-      </c>
-      <c r="Q17" s="56" t="s">
-        <v>211</v>
       </c>
       <c r="R17" s="62" t="s">
         <v>1</v>
@@ -4853,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="AA17" s="47" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4864,16 +4867,16 @@
         <v>93</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>115</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G18" s="67" t="s">
         <v>1</v>
@@ -4888,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="67" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L18" s="56" t="str">
         <f t="shared" si="4"/>
@@ -4907,10 +4910,10 @@
         <v>Translação.Polar</v>
       </c>
       <c r="P18" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q18" s="56" t="s">
         <v>208</v>
-      </c>
-      <c r="Q18" s="56" t="s">
-        <v>210</v>
       </c>
       <c r="R18" s="62" t="s">
         <v>1</v>
@@ -4944,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="AA18" s="47" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -4955,10 +4958,10 @@
         <v>93</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>115</v>
@@ -4979,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="67" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L19" s="56" t="str">
         <f t="shared" si="4"/>
@@ -4998,10 +5001,10 @@
         <v>Giro</v>
       </c>
       <c r="P19" s="56" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q19" s="56" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R19" s="62" t="s">
         <v>1</v>
@@ -5035,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="AA19" s="47" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -5046,10 +5049,10 @@
         <v>93</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>115</v>
@@ -5070,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="67" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L20" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5089,10 +5092,10 @@
         <v>Escalar</v>
       </c>
       <c r="P20" s="56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q20" s="56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R20" s="62" t="s">
         <v>1</v>
@@ -5126,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="AA20" s="47" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -5137,10 +5140,10 @@
         <v>93</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>115</v>
@@ -5161,7 +5164,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L21" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5180,10 +5183,10 @@
         <v>Reflexão</v>
       </c>
       <c r="P21" s="56" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q21" s="56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="R21" s="62" t="s">
         <v>1</v>
@@ -5217,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="AA21" s="47" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -5521,7 +5524,7 @@
     <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="3.53515625" customWidth="1"/>
     <col min="12" max="12" width="5.15234375" customWidth="1"/>
-    <col min="13" max="13" width="38.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.84375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.23046875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="3.3828125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5.15234375" customWidth="1"/>
@@ -5634,10 +5637,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D2" s="54" t="s">
         <v>1</v>
@@ -5667,7 +5670,7 @@
         <v>96</v>
       </c>
       <c r="M2" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N2" s="39" t="s">
         <v>122</v>
@@ -5676,19 +5679,19 @@
         <v>123</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q2" s="70">
         <v>1.05</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S2" s="70">
         <v>1.05</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U2" s="70">
         <v>0</v>
@@ -5723,10 +5726,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D3" s="54" t="s">
         <v>1</v>
@@ -5756,7 +5759,7 @@
         <v>96</v>
       </c>
       <c r="M3" s="41" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N3" s="39" t="s">
         <v>122</v>
@@ -5765,37 +5768,37 @@
         <v>123</v>
       </c>
       <c r="P3" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q3" s="70">
         <v>1.05</v>
       </c>
       <c r="R3" s="39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S3" s="70">
         <v>1.05</v>
       </c>
       <c r="T3" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U3" s="70">
         <v>0</v>
       </c>
       <c r="V3" s="39" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="W3" s="70">
         <v>5.2</v>
       </c>
       <c r="X3" s="39" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y3" s="70">
         <v>0</v>
       </c>
       <c r="Z3" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AA3" s="70">
         <v>0</v>
@@ -5812,7 +5815,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C4" s="51" t="s">
         <v>116</v>
@@ -5845,7 +5848,7 @@
         <v>96</v>
       </c>
       <c r="M4" s="41" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="N4" s="39" t="s">
         <v>122</v>
@@ -5854,19 +5857,19 @@
         <v>124</v>
       </c>
       <c r="P4" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q4" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="R4" s="39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S4" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="T4" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U4" s="70">
         <v>0</v>
@@ -5890,7 +5893,7 @@
         <v>1</v>
       </c>
       <c r="AB4" s="39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AC4" s="52">
         <v>45</v>
@@ -5901,7 +5904,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>117</v>
@@ -5934,7 +5937,7 @@
         <v>96</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="N5" s="39" t="s">
         <v>122</v>
@@ -5943,19 +5946,19 @@
         <v>125</v>
       </c>
       <c r="P5" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q5" s="70">
         <v>3.05</v>
       </c>
       <c r="R5" s="39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S5" s="70">
         <v>3.05</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U5" s="70">
         <v>0</v>
@@ -5979,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="AB5" s="39" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AC5" s="52">
         <v>1.5</v>
@@ -5990,7 +5993,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C6" s="51" t="s">
         <v>118</v>
@@ -6023,7 +6026,7 @@
         <v>96</v>
       </c>
       <c r="M6" s="41" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="N6" s="39" t="s">
         <v>122</v>
@@ -6032,37 +6035,37 @@
         <v>126</v>
       </c>
       <c r="P6" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q6" s="70">
         <v>4.05</v>
       </c>
       <c r="R6" s="39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S6" s="70">
         <v>4.05</v>
       </c>
       <c r="T6" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U6" s="70">
         <v>0</v>
       </c>
       <c r="V6" s="38" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="W6" s="70">
         <v>14.05</v>
       </c>
       <c r="X6" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y6" s="70">
         <v>14.05</v>
       </c>
       <c r="Z6" s="38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AA6" s="70">
         <v>0</v>
@@ -6079,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>120</v>
@@ -6112,7 +6115,7 @@
         <v>96</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="N7" s="39" t="s">
         <v>1</v>
@@ -6168,7 +6171,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C8" s="51" t="s">
         <v>120</v>
@@ -6201,7 +6204,7 @@
         <v>96</v>
       </c>
       <c r="M8" s="41" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="N8" s="39" t="s">
         <v>1</v>
@@ -6257,22 +6260,22 @@
         <v>9</v>
       </c>
       <c r="B9" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="G9" s="55" t="s">
         <v>139</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="G9" s="55" t="s">
-        <v>141</v>
       </c>
       <c r="H9" s="44" t="s">
         <v>1</v>
@@ -6290,7 +6293,7 @@
         <v>96</v>
       </c>
       <c r="M9" s="41" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N9" s="39" t="s">
         <v>1</v>
@@ -6346,22 +6349,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D10" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="55" t="s">
-        <v>137</v>
-      </c>
       <c r="F10" s="53" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H10" s="44" t="s">
         <v>1</v>
@@ -6379,7 +6382,7 @@
         <v>96</v>
       </c>
       <c r="M10" s="41" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="N10" s="39" t="s">
         <v>1</v>
@@ -6435,10 +6438,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D11" s="54" t="s">
         <v>1</v>
@@ -6468,7 +6471,7 @@
         <v>96</v>
       </c>
       <c r="M11" s="41" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>1</v>
@@ -6524,10 +6527,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D12" s="54" t="s">
         <v>1</v>
@@ -6557,7 +6560,7 @@
         <v>96</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N12" s="39" t="s">
         <v>1</v>
@@ -6602,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="AB12" s="39" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AC12" s="52" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6613,10 +6616,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D13" s="54" t="s">
         <v>1</v>
@@ -6646,7 +6649,7 @@
         <v>96</v>
       </c>
       <c r="M13" s="41" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="N13" s="39" t="s">
         <v>1</v>
@@ -6691,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="AB13" s="39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AC13" s="52">
         <v>90</v>
@@ -6702,10 +6705,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D14" s="54" t="s">
         <v>1</v>
@@ -6735,7 +6738,7 @@
         <v>96</v>
       </c>
       <c r="M14" s="41" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="N14" s="39" t="s">
         <v>1</v>
@@ -6780,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="AB14" s="39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AC14" s="52">
         <v>60</v>
@@ -6788,13 +6791,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="H1:M14 A1:B14">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="A1:B14 H1:M14">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E539C8C-632A-4254-8D20-B2929A92A279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A73461D-2B9A-4B3B-B6CD-1BA66C518FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -1645,12 +1645,6 @@
     <t>"R"</t>
   </si>
   <si>
-    <t>Ponto.Base and Valor.Escalar</t>
-  </si>
-  <si>
-    <t>Ponto.Base and Valor.Angular</t>
-  </si>
-  <si>
     <t>Valor.Angular</t>
   </si>
   <si>
@@ -1696,9 +1690,6 @@
     <t>é.transformação.geométrica</t>
   </si>
   <si>
-    <t>Ponto.Eixo1 and Ponto.Eixo2</t>
-  </si>
-  <si>
     <t>Ponto.Eixo1</t>
   </si>
   <si>
@@ -1870,15 +1861,9 @@
     <t>Translação.Polar</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor.X and Valor.Y and Valor.Z </t>
-  </si>
-  <si>
     <t>Valor.Distância</t>
   </si>
   <si>
-    <t>Valor.Distância and Valor.Angular</t>
-  </si>
-  <si>
     <t>Translação.XYZ</t>
   </si>
   <si>
@@ -1982,6 +1967,21 @@
   </si>
   <si>
     <t>"Definição de um valor de ângulo absoluto de 60 graus para usar em alguma transformação"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> base.x exactly 1 ,    base.y exactly 1  ,  base.z exactly 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> base.x exactly 1  ,   base.y exactly 1  ,  base.z exactly 1  ,  valor.angular    exactly 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> base.x exactly 1  ,   base.y exactly 1  ,  base.z exactly 1 ,   valor.escalar     exactly 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> base.x exactly 1 ,    base.y exactly 1  ,  base.z exactly 1  ,  base.xx exactly 1  ,   base.yy exactly 1 ,   base.zz exactly 1  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> base.x exactly 1  ,   base.y exactly 1  ,  base.z exactly 1  ,  valor.distância  exactly 1  ,   valor.angular exactly 1 </t>
   </si>
 </sst>
 </file>
@@ -2677,9 +2677,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2717,7 +2717,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2823,7 +2823,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2965,7 +2965,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2975,15 +2975,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3172,19 +3172,19 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46143.51546678241</v>
+        <v>46156.691677893519</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>109</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>107</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>108</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>101</v>
       </c>
@@ -3284,34 +3284,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="8.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="76.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="65.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="71.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="65.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="71.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.53515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.15234375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="69.15234375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="69.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3394,24 +3394,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="61">
         <v>2</v>
       </c>
       <c r="B2" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="F2" s="64" t="s">
         <v>162</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="E2" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>165</v>
       </c>
       <c r="G2" s="66" t="s">
         <v>1</v>
@@ -3445,10 +3445,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="47" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q2" s="47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R2" s="62" t="s">
         <v>1</v>
@@ -3482,27 +3482,27 @@
         <v>1</v>
       </c>
       <c r="AA2" s="47" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="61">
         <v>3</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G3" s="66" t="s">
         <v>1</v>
@@ -3536,10 +3536,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="47" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q3" s="47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>1</v>
@@ -3573,27 +3573,27 @@
         <v>1</v>
       </c>
       <c r="AA3" s="47" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61">
         <v>4</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E4" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>171</v>
       </c>
       <c r="G4" s="66" t="s">
         <v>1</v>
@@ -3627,10 +3627,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q4" s="47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>1</v>
@@ -3664,27 +3664,27 @@
         <v>1</v>
       </c>
       <c r="AA4" s="47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="61">
         <v>5</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E5" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G5" s="66" t="s">
         <v>1</v>
@@ -3718,10 +3718,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q5" s="47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>1</v>
@@ -3755,27 +3755,27 @@
         <v>1</v>
       </c>
       <c r="AA5" s="47" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="61">
         <v>6</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E6" s="63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G6" s="66" t="s">
         <v>1</v>
@@ -3809,10 +3809,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q6" s="47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R6" s="62" t="s">
         <v>1</v>
@@ -3846,10 +3846,10 @@
         <v>1</v>
       </c>
       <c r="AA6" s="47" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="61">
         <v>7</v>
       </c>
@@ -3857,16 +3857,16 @@
         <v>93</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G7" s="67" t="s">
         <v>1</v>
@@ -3900,7 +3900,7 @@
         <v>Valor.X</v>
       </c>
       <c r="P7" s="56" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q7" s="56" t="str">
         <f t="shared" ref="Q7:Q15" si="6">_xlfn.TRANSLATE(P7,"pt","es")</f>
@@ -3938,10 +3938,10 @@
         <v>1</v>
       </c>
       <c r="AA7" s="47" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="61">
         <v>8</v>
       </c>
@@ -3949,16 +3949,16 @@
         <v>93</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G8" s="67" t="s">
         <v>1</v>
@@ -3992,7 +3992,7 @@
         <v>Valor.Y</v>
       </c>
       <c r="P8" s="56" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q8" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4030,10 +4030,10 @@
         <v>1</v>
       </c>
       <c r="AA8" s="47" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="61">
         <v>9</v>
       </c>
@@ -4041,16 +4041,16 @@
         <v>93</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G9" s="67" t="s">
         <v>1</v>
@@ -4084,7 +4084,7 @@
         <v>Valor.Z</v>
       </c>
       <c r="P9" s="56" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q9" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4122,10 +4122,10 @@
         <v>1</v>
       </c>
       <c r="AA9" s="47" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="61">
         <v>10</v>
       </c>
@@ -4133,16 +4133,16 @@
         <v>93</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G10" s="67" t="s">
         <v>1</v>
@@ -4176,7 +4176,7 @@
         <v>Valor.Distância</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q10" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4214,10 +4214,10 @@
         <v>1</v>
       </c>
       <c r="AA10" s="47" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="61">
         <v>11</v>
       </c>
@@ -4225,16 +4225,16 @@
         <v>93</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G11" s="67" t="s">
         <v>1</v>
@@ -4268,7 +4268,7 @@
         <v>Valor.Angular</v>
       </c>
       <c r="P11" s="56" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q11" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4306,10 +4306,10 @@
         <v>1</v>
       </c>
       <c r="AA11" s="47" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="61">
         <v>12</v>
       </c>
@@ -4317,16 +4317,16 @@
         <v>93</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>119</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G12" s="67" t="s">
         <v>1</v>
@@ -4360,7 +4360,7 @@
         <v>Valor.Escalar</v>
       </c>
       <c r="P12" s="56" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q12" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4398,10 +4398,10 @@
         <v>1</v>
       </c>
       <c r="AA12" s="47" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="61">
         <v>13</v>
       </c>
@@ -4409,16 +4409,16 @@
         <v>93</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G13" s="67" t="s">
         <v>1</v>
@@ -4452,7 +4452,7 @@
         <v>Ponto.Eixo1</v>
       </c>
       <c r="P13" s="56" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Q13" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4490,10 +4490,10 @@
         <v>1</v>
       </c>
       <c r="AA13" s="47" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="61">
         <v>14</v>
       </c>
@@ -4501,16 +4501,16 @@
         <v>93</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G14" s="67" t="s">
         <v>1</v>
@@ -4544,7 +4544,7 @@
         <v>Ponto.Eixo2</v>
       </c>
       <c r="P14" s="56" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Q14" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4582,10 +4582,10 @@
         <v>1</v>
       </c>
       <c r="AA14" s="47" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="61">
         <v>15</v>
       </c>
@@ -4593,13 +4593,13 @@
         <v>93</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F15" s="51" t="s">
         <v>120</v>
@@ -4636,7 +4636,7 @@
         <v>Ponto.Base</v>
       </c>
       <c r="P15" s="56" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q15" s="56" t="str">
         <f t="shared" si="6"/>
@@ -4674,10 +4674,10 @@
         <v>1</v>
       </c>
       <c r="AA15" s="47" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="61">
         <v>16</v>
       </c>
@@ -4685,13 +4685,13 @@
         <v>93</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F16" s="51" t="s">
         <v>121</v>
@@ -4728,10 +4728,10 @@
         <v>Ponto.Destino</v>
       </c>
       <c r="P16" s="56" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Q16" s="56" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R16" s="62" t="s">
         <v>1</v>
@@ -4765,10 +4765,10 @@
         <v>1</v>
       </c>
       <c r="AA16" s="47" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="61">
         <v>17</v>
       </c>
@@ -4776,16 +4776,16 @@
         <v>93</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>115</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G17" s="67" t="s">
         <v>1</v>
@@ -4800,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="67" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="L17" s="56" t="str">
         <f t="shared" ref="L17" si="9">_xlfn.CONCAT(C17)</f>
@@ -4819,10 +4819,10 @@
         <v>Translação.XYZ</v>
       </c>
       <c r="P17" s="56" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="Q17" s="56" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="R17" s="62" t="s">
         <v>1</v>
@@ -4856,10 +4856,10 @@
         <v>1</v>
       </c>
       <c r="AA17" s="47" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="61">
         <v>18</v>
       </c>
@@ -4867,16 +4867,16 @@
         <v>93</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>115</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G18" s="67" t="s">
         <v>1</v>
@@ -4891,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="67" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="L18" s="56" t="str">
         <f t="shared" si="4"/>
@@ -4910,10 +4910,10 @@
         <v>Translação.Polar</v>
       </c>
       <c r="P18" s="56" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="Q18" s="56" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="R18" s="62" t="s">
         <v>1</v>
@@ -4947,10 +4947,10 @@
         <v>1</v>
       </c>
       <c r="AA18" s="47" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="61">
         <v>19</v>
       </c>
@@ -4958,10 +4958,10 @@
         <v>93</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>115</v>
@@ -4982,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="67" t="s">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="L19" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5001,10 +5001,10 @@
         <v>Giro</v>
       </c>
       <c r="P19" s="56" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q19" s="56" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="R19" s="62" t="s">
         <v>1</v>
@@ -5038,10 +5038,10 @@
         <v>1</v>
       </c>
       <c r="AA19" s="47" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="61">
         <v>20</v>
       </c>
@@ -5049,10 +5049,10 @@
         <v>93</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>115</v>
@@ -5073,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="67" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="L20" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5092,10 +5092,10 @@
         <v>Escalar</v>
       </c>
       <c r="P20" s="56" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q20" s="56" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R20" s="62" t="s">
         <v>1</v>
@@ -5129,10 +5129,10 @@
         <v>1</v>
       </c>
       <c r="AA20" s="47" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="61">
         <v>21</v>
       </c>
@@ -5140,10 +5140,10 @@
         <v>93</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>115</v>
@@ -5164,7 +5164,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="67" t="s">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="L21" s="56" t="str">
         <f t="shared" si="4"/>
@@ -5183,10 +5183,10 @@
         <v>Reflexão</v>
       </c>
       <c r="P21" s="56" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q21" s="56" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="R21" s="62" t="s">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="AA21" s="47" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -5251,15 +5251,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="35">
         <v>2</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="35">
         <v>3</v>
       </c>
@@ -5470,14 +5470,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32">
         <v>1</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5513,37 +5513,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AC14"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" customWidth="1"/>
-    <col min="3" max="3" width="7.53515625" customWidth="1"/>
-    <col min="4" max="4" width="5.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="3.53515625" customWidth="1"/>
-    <col min="12" max="12" width="5.15234375" customWidth="1"/>
-    <col min="13" max="13" width="41.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.23046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.15234375" customWidth="1"/>
-    <col min="17" max="17" width="4.23046875" style="71" customWidth="1"/>
-    <col min="18" max="18" width="5.15234375" customWidth="1"/>
-    <col min="19" max="19" width="4.23046875" style="71" customWidth="1"/>
-    <col min="20" max="20" width="5.15234375" customWidth="1"/>
-    <col min="21" max="21" width="4.23046875" style="71" customWidth="1"/>
-    <col min="22" max="22" width="5.15234375" style="72" customWidth="1"/>
-    <col min="23" max="23" width="4.23046875" style="71" customWidth="1"/>
-    <col min="24" max="24" width="5.15234375" style="72" customWidth="1"/>
-    <col min="25" max="25" width="4.23046875" style="71" customWidth="1"/>
-    <col min="26" max="26" width="5.15234375" style="72" customWidth="1"/>
-    <col min="27" max="27" width="4.23046875" style="71" customWidth="1"/>
-    <col min="28" max="28" width="5.921875" customWidth="1"/>
-    <col min="29" max="29" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="3.5703125" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" customWidth="1"/>
+    <col min="13" max="13" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" customWidth="1"/>
+    <col min="17" max="17" width="4.28515625" style="71" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="71" customWidth="1"/>
+    <col min="20" max="20" width="5.140625" customWidth="1"/>
+    <col min="21" max="21" width="4.28515625" style="71" customWidth="1"/>
+    <col min="22" max="22" width="5.140625" style="72" customWidth="1"/>
+    <col min="23" max="23" width="4.28515625" style="71" customWidth="1"/>
+    <col min="24" max="24" width="5.140625" style="72" customWidth="1"/>
+    <col min="25" max="25" width="4.28515625" style="71" customWidth="1"/>
+    <col min="26" max="26" width="5.140625" style="72" customWidth="1"/>
+    <col min="27" max="27" width="4.28515625" style="71" customWidth="1"/>
+    <col min="28" max="28" width="5.85546875" customWidth="1"/>
+    <col min="29" max="29" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -5632,15 +5632,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28">
         <v>2</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D2" s="54" t="s">
         <v>1</v>
@@ -5670,7 +5670,7 @@
         <v>96</v>
       </c>
       <c r="M2" s="41" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N2" s="39" t="s">
         <v>122</v>
@@ -5679,19 +5679,19 @@
         <v>123</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Q2" s="70">
         <v>1.05</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="S2" s="70">
         <v>1.05</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="U2" s="70">
         <v>0</v>
@@ -5721,15 +5721,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>3</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D3" s="54" t="s">
         <v>1</v>
@@ -5759,7 +5759,7 @@
         <v>96</v>
       </c>
       <c r="M3" s="41" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N3" s="39" t="s">
         <v>122</v>
@@ -5768,37 +5768,37 @@
         <v>123</v>
       </c>
       <c r="P3" s="39" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="70">
         <v>1.05</v>
       </c>
       <c r="R3" s="39" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="S3" s="70">
         <v>1.05</v>
       </c>
       <c r="T3" s="39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="U3" s="70">
         <v>0</v>
       </c>
       <c r="V3" s="39" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="W3" s="70">
         <v>5.2</v>
       </c>
       <c r="X3" s="39" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Y3" s="70">
         <v>0</v>
       </c>
       <c r="Z3" s="39" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AA3" s="70">
         <v>0</v>
@@ -5810,12 +5810,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>4</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C4" s="51" t="s">
         <v>116</v>
@@ -5848,7 +5848,7 @@
         <v>96</v>
       </c>
       <c r="M4" s="41" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N4" s="39" t="s">
         <v>122</v>
@@ -5857,19 +5857,19 @@
         <v>124</v>
       </c>
       <c r="P4" s="39" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Q4" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="R4" s="39" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="S4" s="70">
         <v>2.0499999999999998</v>
       </c>
       <c r="T4" s="39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="U4" s="70">
         <v>0</v>
@@ -5893,18 +5893,18 @@
         <v>1</v>
       </c>
       <c r="AB4" s="39" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AC4" s="52">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>5</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>117</v>
@@ -5937,7 +5937,7 @@
         <v>96</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="N5" s="39" t="s">
         <v>122</v>
@@ -5946,19 +5946,19 @@
         <v>125</v>
       </c>
       <c r="P5" s="39" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Q5" s="70">
         <v>3.05</v>
       </c>
       <c r="R5" s="39" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="S5" s="70">
         <v>3.05</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="U5" s="70">
         <v>0</v>
@@ -5982,18 +5982,18 @@
         <v>1</v>
       </c>
       <c r="AB5" s="39" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AC5" s="52">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
         <v>6</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C6" s="51" t="s">
         <v>118</v>
@@ -6026,7 +6026,7 @@
         <v>96</v>
       </c>
       <c r="M6" s="41" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N6" s="39" t="s">
         <v>122</v>
@@ -6035,37 +6035,37 @@
         <v>126</v>
       </c>
       <c r="P6" s="39" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Q6" s="70">
         <v>4.05</v>
       </c>
       <c r="R6" s="39" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="S6" s="70">
         <v>4.05</v>
       </c>
       <c r="T6" s="39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="U6" s="70">
         <v>0</v>
       </c>
       <c r="V6" s="38" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="W6" s="70">
         <v>14.05</v>
       </c>
       <c r="X6" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Y6" s="70">
         <v>14.05</v>
       </c>
       <c r="Z6" s="38" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AA6" s="70">
         <v>0</v>
@@ -6077,12 +6077,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28">
         <v>7</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>120</v>
@@ -6115,7 +6115,7 @@
         <v>96</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N7" s="39" t="s">
         <v>1</v>
@@ -6166,12 +6166,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28">
         <v>8</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C8" s="51" t="s">
         <v>120</v>
@@ -6204,7 +6204,7 @@
         <v>96</v>
       </c>
       <c r="M8" s="41" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N8" s="39" t="s">
         <v>1</v>
@@ -6255,27 +6255,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>9</v>
       </c>
       <c r="B9" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="55" t="s">
         <v>137</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="55" t="s">
-        <v>136</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="G9" s="55" t="s">
-        <v>139</v>
       </c>
       <c r="H9" s="44" t="s">
         <v>1</v>
@@ -6293,7 +6293,7 @@
         <v>96</v>
       </c>
       <c r="M9" s="41" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="N9" s="39" t="s">
         <v>1</v>
@@ -6344,27 +6344,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>10</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H10" s="44" t="s">
         <v>1</v>
@@ -6382,7 +6382,7 @@
         <v>96</v>
       </c>
       <c r="M10" s="41" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="N10" s="39" t="s">
         <v>1</v>
@@ -6433,15 +6433,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>11</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D11" s="54" t="s">
         <v>1</v>
@@ -6471,7 +6471,7 @@
         <v>96</v>
       </c>
       <c r="M11" s="41" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>1</v>
@@ -6522,15 +6522,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
         <v>12</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D12" s="54" t="s">
         <v>1</v>
@@ -6560,7 +6560,7 @@
         <v>96</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="N12" s="39" t="s">
         <v>1</v>
@@ -6605,21 +6605,21 @@
         <v>1</v>
       </c>
       <c r="AB12" s="39" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AC12" s="52" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28">
         <v>13</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D13" s="54" t="s">
         <v>1</v>
@@ -6649,7 +6649,7 @@
         <v>96</v>
       </c>
       <c r="M13" s="41" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N13" s="39" t="s">
         <v>1</v>
@@ -6694,21 +6694,21 @@
         <v>1</v>
       </c>
       <c r="AB13" s="39" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AC13" s="52">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
         <v>14</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D14" s="54" t="s">
         <v>1</v>
@@ -6738,7 +6738,7 @@
         <v>96</v>
       </c>
       <c r="M14" s="41" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="N14" s="39" t="s">
         <v>1</v>
@@ -6783,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="AB14" s="39" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AC14" s="52">
         <v>60</v>
@@ -6807,14 +6807,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A73461D-2B9A-4B3B-B6CD-1BA66C518FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9352CC8-FAC3-489A-A9D8-1EBEAABF2E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -2677,9 +2677,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2717,7 +2717,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2823,7 +2823,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2965,7 +2965,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2975,15 +2975,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3172,19 +3172,19 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46156.691677893519</v>
+        <v>46214.377314120371</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>109</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>107</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="37" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>108</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>101</v>
       </c>
@@ -3284,34 +3284,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="76.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="65.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="69.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.4609375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="6.4609375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="54.3828125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.23046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.3828125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.07421875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.15234375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.53515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="62.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="61">
         <v>2</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="61">
         <v>3</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="61">
         <v>4</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="61">
         <v>5</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="61">
         <v>6</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="61">
         <v>7</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="61">
         <v>8</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="61">
         <v>9</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="61">
         <v>10</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="61">
         <v>11</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="61">
         <v>12</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="61">
         <v>13</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="61">
         <v>14</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="61">
         <v>15</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="61">
         <v>16</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="61">
         <v>17</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="61">
         <v>18</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="61">
         <v>19</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="61">
         <v>20</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="61">
         <v>21</v>
       </c>
@@ -5251,15 +5251,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="35">
         <v>2</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35">
         <v>3</v>
       </c>
@@ -5470,14 +5470,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="32">
         <v>1</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5513,37 +5513,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AC14"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="6.9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.53515625" customWidth="1"/>
+    <col min="4" max="4" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3828125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="3.5703125" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" customWidth="1"/>
-    <col min="13" max="13" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" customWidth="1"/>
-    <col min="17" max="17" width="4.28515625" style="71" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" customWidth="1"/>
-    <col min="19" max="19" width="4.28515625" style="71" customWidth="1"/>
-    <col min="20" max="20" width="5.140625" customWidth="1"/>
-    <col min="21" max="21" width="4.28515625" style="71" customWidth="1"/>
-    <col min="22" max="22" width="5.140625" style="72" customWidth="1"/>
-    <col min="23" max="23" width="4.28515625" style="71" customWidth="1"/>
-    <col min="24" max="24" width="5.140625" style="72" customWidth="1"/>
-    <col min="25" max="25" width="4.28515625" style="71" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="72" customWidth="1"/>
-    <col min="27" max="27" width="4.28515625" style="71" customWidth="1"/>
-    <col min="28" max="28" width="5.85546875" customWidth="1"/>
-    <col min="29" max="29" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="3.53515625" customWidth="1"/>
+    <col min="12" max="12" width="5.15234375" customWidth="1"/>
+    <col min="13" max="13" width="41.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.15234375" customWidth="1"/>
+    <col min="17" max="17" width="4.3046875" style="71" customWidth="1"/>
+    <col min="18" max="18" width="5.15234375" customWidth="1"/>
+    <col min="19" max="19" width="4.3046875" style="71" customWidth="1"/>
+    <col min="20" max="20" width="5.15234375" customWidth="1"/>
+    <col min="21" max="21" width="4.3046875" style="71" customWidth="1"/>
+    <col min="22" max="22" width="5.15234375" style="72" customWidth="1"/>
+    <col min="23" max="23" width="4.3046875" style="71" customWidth="1"/>
+    <col min="24" max="24" width="5.15234375" style="72" customWidth="1"/>
+    <col min="25" max="25" width="4.3046875" style="71" customWidth="1"/>
+    <col min="26" max="26" width="5.15234375" style="72" customWidth="1"/>
+    <col min="27" max="27" width="4.3046875" style="71" customWidth="1"/>
+    <col min="28" max="28" width="5.84375" customWidth="1"/>
+    <col min="29" max="29" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="28">
         <v>2</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="28">
         <v>3</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="28">
         <v>4</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="28">
         <v>5</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="28">
         <v>6</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="28">
         <v>7</v>
       </c>
@@ -6166,7 +6166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="28">
         <v>8</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="28">
         <v>9</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="28">
         <v>10</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="28">
         <v>11</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="28">
         <v>12</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="28">
         <v>13</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="28">
         <v>14</v>
       </c>
@@ -6807,14 +6807,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9352CC8-FAC3-489A-A9D8-1EBEAABF2E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8048C617-3A38-4AEF-81E6-F21C4C1F75BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="234">
   <si>
     <t>Key</t>
   </si>
@@ -1543,9 +1543,6 @@
     <t>Val</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Classe</t>
   </si>
   <si>
@@ -1747,21 +1744,12 @@
     <t>Informação</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
     <t>Requisito.Espacial</t>
   </si>
   <si>
@@ -1804,21 +1792,6 @@
     <t>La transformación que modifica la posición de un punto mediante un desplazamiento circular. Necesita punto base y ángulo de rotación.</t>
   </si>
   <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</t>
-  </si>
-  <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</t>
-  </si>
-  <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</t>
-  </si>
-  <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</t>
-  </si>
-  <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</t>
-  </si>
-  <si>
     <t>Value of X. Coordinate X.</t>
   </si>
   <si>
@@ -1982,6 +1955,15 @@
   </si>
   <si>
     <t xml:space="preserve"> base.x exactly 1  ,   base.y exactly 1  ,  base.z exactly 1  ,  valor.distância  exactly 1  ,   valor.angular exactly 1 </t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
   </si>
 </sst>
 </file>
@@ -2338,7 +2320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2402,14 +2384,8 @@
     <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2453,9 +2429,6 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2463,12 +2436,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2504,22 +2471,10 @@
     <xf numFmtId="0" fontId="18" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2537,9 +2492,6 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2552,11 +2504,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2589,6 +2550,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2641,6 +2610,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2648,14 +2625,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2975,59 +2944,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="42" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="39" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>110</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3035,11 +3004,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3047,232 +3016,232 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C9" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C12" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C13" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C14" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C15" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C16" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46214.377314120371</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>46216.382623726851</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="50" t="str">
+        <v>106</v>
+      </c>
+      <c r="B20" s="45" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="37" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C20" s="43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B21" s="50" t="str">
+        <v>107</v>
+      </c>
+      <c r="B21" s="45" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
-      <c r="C21" s="48" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C21" s="43" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C22" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>112</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>113</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize concepts of Genetically Constructed Structures</v>
       </c>
-      <c r="C26" s="48" t="s">
-        <v>106</v>
+      <c r="C26" s="43" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3284,34 +3253,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="6.4609375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.23046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="54.3828125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.23046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.07421875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="62.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="76" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="88.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" style="62" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="62" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6" style="62" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.28515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="87.42578125" style="62" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3330,19 +3300,19 @@
       <c r="F1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="65" t="s">
+      <c r="J1" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="K1" s="56" t="s">
         <v>43</v>
       </c>
       <c r="L1" s="22" t="s">
@@ -3363,7 +3333,7 @@
       <c r="Q1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="R1" s="22" t="s">
         <v>88</v>
       </c>
       <c r="S1" s="22" t="s">
@@ -3372,1874 +3342,1884 @@
       <c r="T1" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="U1" s="24" t="s">
+      <c r="U1" s="23" t="s">
         <v>80</v>
       </c>
       <c r="V1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="W1" s="23" t="s">
+      <c r="W1" s="65" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y1" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="Z1" s="68" t="s">
+      <c r="AA1" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="46" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="61">
+    </row>
+    <row r="2" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="63">
         <v>2</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="63" t="s">
-        <v>161</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="58" t="str">
+      <c r="G2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="52" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="M2" s="58" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M2" s="52" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N2" s="58" t="str">
+      <c r="N2" s="52" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
-      </c>
-      <c r="O2" s="58" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O2" s="52" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
-      </c>
-      <c r="P2" s="47" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="R2" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="57" t="str">
+        <v>Contêiner</v>
+      </c>
+      <c r="P2" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q2" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="R2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="42" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="T2" s="57" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T2" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="57" t="str">
+      <c r="U2" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
-      </c>
-      <c r="V2" s="47" t="s">
+        <v>Contêineres</v>
+      </c>
+      <c r="V2" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="59" t="str">
-        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.EGC",".",A2)</f>
-        <v>Key.EGC.2</v>
-      </c>
-      <c r="X2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="47" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="61">
+      <c r="W2" s="64" t="str">
+        <f>CONCATENATE("Key-EGC-",A2)</f>
+        <v>Key-EGC-2</v>
+      </c>
+      <c r="X2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA2" s="42" t="str">
+        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="63">
         <v>3</v>
       </c>
-      <c r="B3" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="64" t="s">
+      <c r="B3" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="G3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="58" t="str">
+      <c r="E3" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M3" s="58" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M3" s="52" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N3" s="58" t="str">
+      <c r="N3" s="52" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O3" s="58" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O3" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
-      <c r="P3" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q3" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="R3" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="57" t="str">
+      <c r="P3" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q3" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="R3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T3" s="57" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T3" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="57" t="str">
+      <c r="U3" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V3" s="47" t="s">
+        <v>Contêineres</v>
+      </c>
+      <c r="V3" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="59" t="str">
+      <c r="W3" s="64" t="str">
+        <f t="shared" ref="W3:W21" si="4">CONCATENATE("Key-EGC-",A3)</f>
+        <v>Key-EGC-3</v>
+      </c>
+      <c r="X3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="42" t="str">
         <f t="shared" si="3"/>
-        <v>Key.EGC.3</v>
-      </c>
-      <c r="X3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="47" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="61">
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="63">
         <v>4</v>
       </c>
-      <c r="B4" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="64" t="s">
+      <c r="B4" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="D4" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>168</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="58" t="str">
+      <c r="E4" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M4" s="58" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M4" s="52" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N4" s="58" t="str">
+      <c r="N4" s="52" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O4" s="58" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O4" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
-      <c r="P4" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q4" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="R4" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="57" t="str">
+      <c r="P4" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q4" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="57" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="57" t="str">
+      <c r="U4" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="47" t="s">
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W4" s="59" t="str">
+      <c r="W4" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-4</v>
+      </c>
+      <c r="X4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="42" t="str">
         <f t="shared" si="3"/>
-        <v>Key.EGC.4</v>
-      </c>
-      <c r="X4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="47" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="61">
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="63">
         <v>5</v>
       </c>
-      <c r="B5" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="64" t="s">
+      <c r="B5" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="F5" s="64" t="s">
-        <v>170</v>
-      </c>
-      <c r="G5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="58" t="str">
+      <c r="E5" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M5" s="58" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M5" s="52" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N5" s="58" t="str">
+      <c r="N5" s="52" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O5" s="58" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O5" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
-      <c r="P5" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q5" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="R5" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="57" t="str">
+      <c r="P5" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q5" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="R5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="57" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="57" t="str">
+      <c r="U5" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="47" t="s">
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W5" s="59" t="str">
+      <c r="W5" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-5</v>
+      </c>
+      <c r="X5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="42" t="str">
         <f t="shared" si="3"/>
-        <v>Key.EGC.5</v>
-      </c>
-      <c r="X5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="47" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="61">
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="63">
         <v>6</v>
       </c>
-      <c r="B6" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="64" t="s">
+      <c r="B6" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="G6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="58" t="str">
+      <c r="E6" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M6" s="58" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M6" s="52" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N6" s="58" t="str">
+      <c r="N6" s="52" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O6" s="58" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O6" s="52" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
-      <c r="P6" s="47" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q6" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="R6" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="57" t="str">
+      <c r="P6" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q6" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="R6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T6" s="57" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T6" s="42" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="57" t="str">
+      <c r="U6" s="42" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V6" s="47" t="s">
+        <v>Contêineres</v>
+      </c>
+      <c r="V6" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W6" s="59" t="str">
+      <c r="W6" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-6</v>
+      </c>
+      <c r="X6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="42" t="str">
         <f t="shared" si="3"/>
-        <v>Key.EGC.6</v>
-      </c>
-      <c r="X6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="47" t="s">
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="63">
+        <v>7</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="51" t="str">
+        <f t="shared" ref="L7:L21" si="5">_xlfn.CONCAT(C7)</f>
+        <v>Formal</v>
+      </c>
+      <c r="M7" s="51" t="str">
+        <f t="shared" ref="M7:O21" si="6">_xlfn.CONCAT("", D7)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N7" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O7" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Valor.X</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q7" s="51" t="str">
+        <f t="shared" ref="Q7:Q15" si="7">_xlfn.TRANSLATE(P7,"pt","es")</f>
+        <v>Valor de X. Coordenada X.</v>
+      </c>
+      <c r="R7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="42" t="str">
+        <f t="shared" ref="S7:U21" si="8">SUBSTITUTE(C7, "_", " ")</f>
+        <v>Formal</v>
+      </c>
+      <c r="T7" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U7" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V7" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W7" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-7</v>
+      </c>
+      <c r="X7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="42" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="63">
+        <v>8</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M8" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N8" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O8" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Valor.Y</v>
+      </c>
+      <c r="P8" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q8" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor de Y. Coordenada Y.</v>
+      </c>
+      <c r="R8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T8" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U8" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V8" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W8" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-8</v>
+      </c>
+      <c r="X8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="42" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="63">
+        <v>9</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M9" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N9" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O9" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Valor.Z</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q9" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor Z. Coordenada Z.</v>
+      </c>
+      <c r="R9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T9" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U9" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V9" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W9" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-9</v>
+      </c>
+      <c r="X9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="42" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="63">
+        <v>10</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M10" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N10" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O10" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Valor.Distância</v>
+      </c>
+      <c r="P10" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q10" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor desplazado. Valor de distancia de una traslación</v>
+      </c>
+      <c r="R10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T10" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U10" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V10" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W10" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-10</v>
+      </c>
+      <c r="X10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="42" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="63">
+        <v>11</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M11" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N11" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O11" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Valor.Angular</v>
+      </c>
+      <c r="P11" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q11" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor angular de una transformada de espín o rotación</v>
+      </c>
+      <c r="R11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T11" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U11" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V11" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W11" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-11</v>
+      </c>
+      <c r="X11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="42" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="63">
+        <v>12</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M12" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N12" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O12" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Valor.Escalar</v>
+      </c>
+      <c r="P12" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q12" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Valor escalar de una transformación que cambia la escala</v>
+      </c>
+      <c r="R12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T12" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U12" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="V12" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W12" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-12</v>
+      </c>
+      <c r="X12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="42" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="63">
+        <v>13</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M13" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N13" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O13" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Ponto.Eixo1</v>
+      </c>
+      <c r="P13" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q13" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Punto 1 que define un eje de simetría</v>
+      </c>
+      <c r="R13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T13" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U13" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V13" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W13" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-13</v>
+      </c>
+      <c r="X13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="63">
+        <v>14</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M14" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N14" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O14" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Ponto.Eixo2</v>
+      </c>
+      <c r="P14" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q14" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Punto 2 que define un eje de simetría</v>
+      </c>
+      <c r="R14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T14" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U14" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V14" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W14" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-14</v>
+      </c>
+      <c r="X14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="63">
+        <v>15</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M15" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N15" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O15" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Ponto.Base</v>
+      </c>
+      <c r="P15" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q15" s="51" t="str">
+        <f t="shared" si="7"/>
+        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
+      </c>
+      <c r="R15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T15" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U15" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V15" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W15" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-15</v>
+      </c>
+      <c r="X15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="42" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="61">
-        <v>7</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="G7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="56" t="str">
-        <f t="shared" ref="L7:L21" si="4">_xlfn.CONCAT(C7)</f>
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="63">
+        <v>16</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="51" t="str">
+        <f t="shared" si="5"/>
         <v>Formal</v>
       </c>
-      <c r="M7" s="56" t="str">
-        <f t="shared" ref="M7:O21" si="5">_xlfn.CONCAT("", D7)</f>
+      <c r="M16" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Elementos.TGB</v>
       </c>
-      <c r="N7" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O7" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Valor.X</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q7" s="56" t="str">
-        <f t="shared" ref="Q7:Q15" si="6">_xlfn.TRANSLATE(P7,"pt","es")</f>
-        <v>Valor de X. Coordenada X.</v>
-      </c>
-      <c r="R7" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="57" t="str">
-        <f t="shared" ref="S7:U21" si="7">SUBSTITUTE(C7, "_", " ")</f>
+      <c r="N16" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="O16" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Ponto.Destino</v>
+      </c>
+      <c r="P16" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q16" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="R16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="42" t="str">
+        <f t="shared" si="8"/>
         <v>Formal</v>
       </c>
-      <c r="T7" s="57" t="str">
-        <f t="shared" si="7"/>
+      <c r="T16" s="42" t="str">
+        <f t="shared" si="8"/>
         <v>Elementos.TGB</v>
       </c>
-      <c r="U7" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V7" s="47" t="s">
+      <c r="U16" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Bases.Geométricas</v>
+      </c>
+      <c r="V16" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W7" s="59" t="str">
-        <f>CONCATENATE("Key.EGC",".",A7)</f>
-        <v>Key.EGC.7</v>
-      </c>
-      <c r="X7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="47" t="s">
+      <c r="W16" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-16</v>
+      </c>
+      <c r="X16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="42" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="61">
-        <v>8</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="G8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M8" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N8" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O8" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Valor.Y</v>
-      </c>
-      <c r="P8" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q8" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor de Y. Coordenada Y.</v>
-      </c>
-      <c r="R8" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T8" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U8" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V8" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W8" s="59" t="str">
-        <f t="shared" ref="W8:W21" si="8">CONCATENATE("Key.EGC",".",A8)</f>
-        <v>Key.EGC.8</v>
-      </c>
-      <c r="X8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="47" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="61">
-        <v>9</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M9" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N9" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O9" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Valor.Z</v>
-      </c>
-      <c r="P9" s="56" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q9" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor Z. Coordenada Z.</v>
-      </c>
-      <c r="R9" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T9" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U9" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V9" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W9" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.9</v>
-      </c>
-      <c r="X9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="47" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="61">
-        <v>10</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M10" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N10" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O10" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Valor.Distância</v>
-      </c>
-      <c r="P10" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q10" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor desplazado. Valor de distancia de una traslación</v>
-      </c>
-      <c r="R10" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T10" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U10" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V10" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W10" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.10</v>
-      </c>
-      <c r="X10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="47" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="61">
-        <v>11</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M11" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N11" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O11" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Valor.Angular</v>
-      </c>
-      <c r="P11" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q11" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor angular de una transformada de espín o rotación</v>
-      </c>
-      <c r="R11" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T11" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U11" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V11" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W11" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.11</v>
-      </c>
-      <c r="X11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="47" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="61">
-        <v>12</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="G12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M12" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N12" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O12" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Valor.Escalar</v>
-      </c>
-      <c r="P12" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q12" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor escalar de una transformación que cambia la escala</v>
-      </c>
-      <c r="R12" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T12" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U12" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="V12" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W12" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.12</v>
-      </c>
-      <c r="X12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="47" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="61">
-        <v>13</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="G13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M13" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N13" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="O13" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Ponto.Eixo1</v>
-      </c>
-      <c r="P13" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q13" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Punto 1 que define un eje de simetría</v>
-      </c>
-      <c r="R13" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T13" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U13" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V13" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W13" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.13</v>
-      </c>
-      <c r="X13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="47" t="s">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="63">
+        <v>17</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="46" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="61">
-        <v>14</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="F14" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="G14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M14" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N14" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="O14" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Ponto.Eixo2</v>
-      </c>
-      <c r="P14" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q14" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Punto 2 que define un eje de simetría</v>
-      </c>
-      <c r="R14" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T14" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U14" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V14" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W14" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.14</v>
-      </c>
-      <c r="X14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="47" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="61">
-        <v>15</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="F15" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="G15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M15" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N15" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="O15" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Ponto.Base</v>
-      </c>
-      <c r="P15" s="56" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q15" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
-      </c>
-      <c r="R15" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T15" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U15" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V15" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W15" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.15</v>
-      </c>
-      <c r="X15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="47" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="61">
-        <v>16</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="F16" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="G16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M16" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N16" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="O16" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Ponto.Destino</v>
-      </c>
-      <c r="P16" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q16" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="R16" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T16" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U16" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="V16" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W16" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.16</v>
-      </c>
-      <c r="X16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="47" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="61">
-        <v>17</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="G17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="67" t="s">
-        <v>235</v>
-      </c>
-      <c r="L17" s="56" t="str">
+      <c r="G17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L17" s="51" t="str">
         <f t="shared" ref="L17" si="9">_xlfn.CONCAT(C17)</f>
         <v>Formal</v>
       </c>
-      <c r="M17" s="56" t="str">
+      <c r="M17" s="51" t="str">
         <f t="shared" ref="M17" si="10">_xlfn.CONCAT("", D17)</f>
         <v>Elementos.TGB</v>
       </c>
-      <c r="N17" s="56" t="str">
+      <c r="N17" s="51" t="str">
         <f t="shared" ref="N17" si="11">_xlfn.CONCAT("", E17)</f>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O17" s="56" t="str">
+      <c r="O17" s="51" t="str">
         <f t="shared" ref="O17" si="12">_xlfn.CONCAT("", F17)</f>
         <v>Translação.XYZ</v>
       </c>
-      <c r="P17" s="56" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q17" s="56" t="s">
-        <v>204</v>
-      </c>
-      <c r="R17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="57" t="str">
+      <c r="P17" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q17" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="R17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="42" t="str">
         <f t="shared" ref="S17" si="13">SUBSTITUTE(C17, "_", " ")</f>
         <v>Formal</v>
       </c>
-      <c r="T17" s="57" t="str">
+      <c r="T17" s="42" t="str">
         <f t="shared" ref="T17" si="14">SUBSTITUTE(D17, "_", " ")</f>
         <v>Elementos.TGB</v>
       </c>
-      <c r="U17" s="58" t="str">
+      <c r="U17" s="52" t="str">
         <f t="shared" ref="U17" si="15">SUBSTITUTE(E17, "_", " ")</f>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="V17" s="47" t="s">
+      <c r="V17" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W17" s="59" t="str">
-        <f t="shared" ref="W17" si="16">CONCATENATE("Key.EGC",".",A17)</f>
-        <v>Key.EGC.17</v>
-      </c>
-      <c r="X17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="47" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="61">
+      <c r="W17" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-17</v>
+      </c>
+      <c r="X17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="42" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="63">
         <v>18</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="26" t="s">
+      <c r="B18" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="L18" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M18" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N18" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O18" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Translação.Polar</v>
+      </c>
+      <c r="P18" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q18" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="R18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T18" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U18" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V18" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W18" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-18</v>
+      </c>
+      <c r="X18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="42" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="63">
+        <v>19</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="L19" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M19" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N19" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O19" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Giro</v>
+      </c>
+      <c r="P19" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q19" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="R19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T19" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U19" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V19" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W19" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-EGC-19</v>
+      </c>
+      <c r="X19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="42" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="63">
+        <v>20</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="L20" s="51" t="str">
+        <f t="shared" si="5"/>
+        <v>Formal</v>
+      </c>
+      <c r="M20" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N20" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O20" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Escalar</v>
+      </c>
+      <c r="P20" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q20" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="G18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="L18" s="56" t="str">
+      <c r="R20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Formal</v>
+      </c>
+      <c r="T20" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U20" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="V20" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="W20" s="64" t="str">
         <f t="shared" si="4"/>
+        <v>Key-EGC-20</v>
+      </c>
+      <c r="X20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="63">
+        <v>21</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="58" t="s">
+        <v>229</v>
+      </c>
+      <c r="L21" s="51" t="str">
+        <f t="shared" si="5"/>
         <v>Formal</v>
       </c>
-      <c r="M18" s="56" t="str">
-        <f t="shared" si="5"/>
+      <c r="M21" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Elementos.TGB</v>
       </c>
-      <c r="N18" s="56" t="str">
-        <f t="shared" si="5"/>
+      <c r="N21" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="O18" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Translação.Polar</v>
-      </c>
-      <c r="P18" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q18" s="56" t="s">
-        <v>203</v>
-      </c>
-      <c r="R18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="57" t="str">
-        <f t="shared" si="7"/>
+      <c r="O21" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Reflexão</v>
+      </c>
+      <c r="P21" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q21" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="R21" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21" s="42" t="str">
+        <f t="shared" si="8"/>
         <v>Formal</v>
       </c>
-      <c r="T18" s="57" t="str">
-        <f t="shared" si="7"/>
+      <c r="T21" s="42" t="str">
+        <f t="shared" si="8"/>
         <v>Elementos.TGB</v>
       </c>
-      <c r="U18" s="58" t="str">
-        <f t="shared" si="7"/>
+      <c r="U21" s="52" t="str">
+        <f t="shared" si="8"/>
         <v>Movimento.Geométrico</v>
       </c>
-      <c r="V18" s="47" t="s">
+      <c r="V21" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W18" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.18</v>
-      </c>
-      <c r="X18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="47" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="61">
-        <v>19</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="67" t="s">
-        <v>236</v>
-      </c>
-      <c r="L19" s="56" t="str">
+      <c r="W21" s="64" t="str">
         <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M19" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N19" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O19" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Giro</v>
-      </c>
-      <c r="P19" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q19" s="56" t="s">
-        <v>179</v>
-      </c>
-      <c r="R19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T19" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U19" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V19" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W19" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.19</v>
-      </c>
-      <c r="X19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="47" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="61">
-        <v>20</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="67" t="s">
-        <v>237</v>
-      </c>
-      <c r="L20" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M20" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N20" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O20" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Escalar</v>
-      </c>
-      <c r="P20" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q20" s="56" t="s">
-        <v>178</v>
-      </c>
-      <c r="R20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T20" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U20" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V20" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W20" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.20</v>
-      </c>
-      <c r="X20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="47" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="61">
-        <v>21</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="L21" s="56" t="str">
-        <f t="shared" si="4"/>
-        <v>Formal</v>
-      </c>
-      <c r="M21" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N21" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O21" s="56" t="str">
-        <f t="shared" si="5"/>
-        <v>Reflexão</v>
-      </c>
-      <c r="P21" s="56" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q21" s="56" t="s">
-        <v>177</v>
-      </c>
-      <c r="R21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Formal</v>
-      </c>
-      <c r="T21" s="57" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U21" s="58" t="str">
-        <f t="shared" si="7"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V21" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="W21" s="59" t="str">
-        <f t="shared" si="8"/>
-        <v>Key.EGC.21</v>
-      </c>
-      <c r="X21" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="47" t="s">
-        <v>197</v>
+        <v>Key-EGC-21</v>
+      </c>
+      <c r="X21" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="42" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="F1 F7:F21">
+    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B21">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F7:F21">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
     <cfRule type="duplicateValues" dxfId="7" priority="3"/>
     <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V6">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5251,81 +5231,81 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="L1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="M1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="N1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="36" t="s">
+      <c r="O1" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="36" t="s">
+      <c r="P1" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="36" t="s">
+      <c r="Q1" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="36" t="s">
+      <c r="R1" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="36" t="s">
+      <c r="S1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="36" t="s">
+      <c r="T1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="36" t="s">
+      <c r="U1" s="34" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="35">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="33">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5389,8 +5369,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="33">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -5470,32 +5450,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="32">
-        <v>1</v>
-      </c>
-      <c r="B1" s="33" t="s">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30">
+        <v>1</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
-      <c r="B2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="34" t="s">
+      <c r="B2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5512,1286 +5492,1117 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:AC14"/>
-  <sheetFormatPr defaultRowHeight="6.9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Y14"/>
+  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.53515625" customWidth="1"/>
-    <col min="4" max="4" width="5.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="3.53515625" customWidth="1"/>
-    <col min="12" max="12" width="5.15234375" customWidth="1"/>
-    <col min="13" max="13" width="41.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.15234375" customWidth="1"/>
-    <col min="17" max="17" width="4.3046875" style="71" customWidth="1"/>
-    <col min="18" max="18" width="5.15234375" customWidth="1"/>
-    <col min="19" max="19" width="4.3046875" style="71" customWidth="1"/>
-    <col min="20" max="20" width="5.15234375" customWidth="1"/>
-    <col min="21" max="21" width="4.3046875" style="71" customWidth="1"/>
-    <col min="22" max="22" width="5.15234375" style="72" customWidth="1"/>
-    <col min="23" max="23" width="4.3046875" style="71" customWidth="1"/>
-    <col min="24" max="24" width="5.15234375" style="72" customWidth="1"/>
-    <col min="25" max="25" width="4.3046875" style="71" customWidth="1"/>
-    <col min="26" max="26" width="5.15234375" style="72" customWidth="1"/>
-    <col min="27" max="27" width="4.3046875" style="71" customWidth="1"/>
-    <col min="28" max="28" width="5.84375" customWidth="1"/>
-    <col min="29" max="29" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="59" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="61" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="62" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="62" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="62" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.42578125" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="43" t="s">
+      <c r="J1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="K1" s="40" t="s">
         <v>92</v>
       </c>
       <c r="L1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="O1" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="69" t="s">
+      <c r="Q1" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="69" t="s">
+      <c r="S1" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="T1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="69" t="s">
+      <c r="U1" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="V1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="69" t="s">
+      <c r="W1" s="59" t="s">
         <v>92</v>
       </c>
       <c r="X1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="Y1" s="69" t="s">
+      <c r="Y1" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="Z1" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA1" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB1" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC1" s="43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="28">
+    </row>
+    <row r="2" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="26">
         <v>2</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="M2" s="60">
+        <v>1.05</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="O2" s="60">
+        <v>1.05</v>
+      </c>
+      <c r="P2" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q2" s="60">
+        <v>0</v>
+      </c>
+      <c r="R2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26">
+        <v>3</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="M3" s="60">
+        <v>1.05</v>
+      </c>
+      <c r="N3" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="O3" s="60">
+        <v>1.05</v>
+      </c>
+      <c r="P3" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q3" s="60">
+        <v>0</v>
+      </c>
+      <c r="R3" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="S3" s="60">
+        <v>5.2</v>
+      </c>
+      <c r="T3" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="U3" s="60">
+        <v>0</v>
+      </c>
+      <c r="V3" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="W3" s="60">
+        <v>0</v>
+      </c>
+      <c r="X3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26">
+        <v>4</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C4" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="L4" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" s="41" t="s">
+      <c r="M4" s="60">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="O4" s="60">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q4" s="60">
+        <v>0</v>
+      </c>
+      <c r="R4" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V4" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y4" s="47">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="26">
+        <v>5</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="K5" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="M5" s="60">
+        <v>3.05</v>
+      </c>
+      <c r="N5" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="O5" s="60">
+        <v>3.05</v>
+      </c>
+      <c r="P5" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q5" s="60">
+        <v>0</v>
+      </c>
+      <c r="R5" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y5" s="47">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
+        <v>6</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="K6" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="M6" s="60">
+        <v>4.05</v>
+      </c>
+      <c r="N6" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="O6" s="60">
+        <v>4.05</v>
+      </c>
+      <c r="P6" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q6" s="60">
+        <v>0</v>
+      </c>
+      <c r="R6" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="S6" s="60">
+        <v>14.05</v>
+      </c>
+      <c r="T6" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="U6" s="60">
+        <v>14.05</v>
+      </c>
+      <c r="V6" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="W6" s="60">
+        <v>0</v>
+      </c>
+      <c r="X6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
+        <v>7</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26">
+        <v>8</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>9</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>10</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>11</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
+        <v>12</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y12" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="N2" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="O2" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="P2" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q2" s="70">
-        <v>1.05</v>
-      </c>
-      <c r="R2" s="39" t="s">
+    </row>
+    <row r="13" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>13</v>
+      </c>
+      <c r="B13" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="S2" s="70">
-        <v>1.05</v>
-      </c>
-      <c r="T2" s="39" t="s">
+      <c r="C13" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y13" s="47">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26">
+        <v>14</v>
+      </c>
+      <c r="B14" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="U2" s="70">
-        <v>0</v>
-      </c>
-      <c r="V2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28">
-        <v>3</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M3" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="N3" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q3" s="70">
-        <v>1.05</v>
-      </c>
-      <c r="R3" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="S3" s="70">
-        <v>1.05</v>
-      </c>
-      <c r="T3" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="U3" s="70">
-        <v>0</v>
-      </c>
-      <c r="V3" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="W3" s="70">
-        <v>5.2</v>
-      </c>
-      <c r="X3" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y3" s="70">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA3" s="70">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="28">
-        <v>4</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M4" s="41" t="s">
+      <c r="C14" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="N4" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="O4" s="52" t="s">
-        <v>124</v>
-      </c>
-      <c r="P4" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q4" s="70">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="R4" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="S4" s="70">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="T4" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="U4" s="70">
-        <v>0</v>
-      </c>
-      <c r="V4" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X4" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC4" s="52">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="28">
-        <v>5</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M5" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="N5" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="O5" s="52" t="s">
-        <v>125</v>
-      </c>
-      <c r="P5" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q5" s="70">
-        <v>3.05</v>
-      </c>
-      <c r="R5" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="S5" s="70">
-        <v>3.05</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="U5" s="70">
-        <v>0</v>
-      </c>
-      <c r="V5" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X5" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="AC5" s="52">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="28">
-        <v>6</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M6" s="41" t="s">
-        <v>227</v>
-      </c>
-      <c r="N6" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="O6" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="P6" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q6" s="70">
-        <v>4.05</v>
-      </c>
-      <c r="R6" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="S6" s="70">
-        <v>4.05</v>
-      </c>
-      <c r="T6" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="U6" s="70">
-        <v>0</v>
-      </c>
-      <c r="V6" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="W6" s="70">
-        <v>14.05</v>
-      </c>
-      <c r="X6" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y6" s="70">
-        <v>14.05</v>
-      </c>
-      <c r="Z6" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA6" s="70">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="28">
-        <v>7</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>228</v>
-      </c>
-      <c r="N7" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P7" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T7" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X7" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="28">
-        <v>8</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="N8" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W8" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X8" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="28">
-        <v>9</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="N9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U9" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W9" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X9" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="28">
-        <v>10</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="G10" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M10" s="41" t="s">
-        <v>231</v>
-      </c>
-      <c r="N10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="28">
-        <v>11</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="N11" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T11" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U11" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W11" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="28">
-        <v>12</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M12" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="N12" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U12" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W12" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC12" s="52" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="28">
-        <v>13</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M13" s="41" t="s">
-        <v>233</v>
-      </c>
-      <c r="N13" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O13" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T13" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U13" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W13" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC13" s="52">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" ht="6.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="28">
-        <v>14</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L14" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="M14" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="N14" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O14" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="P14" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="R14" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="U14" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="V14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="W14" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC14" s="52">
+      <c r="J14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y14" s="47">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B14 H1:M14">
+  <conditionalFormatting sqref="A1:B14 H1:I14">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -6807,14 +6618,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6822,7 +6633,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6830,7 +6641,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6838,7 +6649,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6846,7 +6657,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6854,7 +6665,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6862,7 +6673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6870,7 +6681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6878,7 +6689,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6886,7 +6697,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6894,7 +6705,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6902,7 +6713,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6910,7 +6721,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6918,7 +6729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6926,7 +6737,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8048C617-3A38-4AEF-81E6-F21C4C1F75BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71E2808-3C2B-41EF-8607-6E2CE4F5D649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -1774,9 +1774,6 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Formal</t>
-  </si>
-  <si>
     <t>Elementos.TGB</t>
   </si>
   <si>
@@ -1957,13 +1954,16 @@
     <t xml:space="preserve"> base.x exactly 1  ,   base.y exactly 1  ,  base.z exactly 1  ,  valor.distância  exactly 1  ,   valor.angular exactly 1 </t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Formantes</t>
   </si>
 </sst>
 </file>
@@ -2610,14 +2610,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2625,6 +2617,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2944,15 +2944,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3141,19 +3141,19 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46216.382623726851</v>
+        <v>46243.521928240742</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>108</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>106</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>107</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>100</v>
       </c>
@@ -3253,35 +3253,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.69140625" customWidth="1"/>
+    <col min="4" max="4" width="8.07421875" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.15234375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.69140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.15234375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="76" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="88.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="62" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="88.3046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.69140625" style="62" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="62" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" style="62" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="62" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.3046875" style="62" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.53515625" style="62" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69140625" style="62" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="62" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.42578125" style="62" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.28515625" style="62" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="87.42578125" style="62" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.3046875" style="62" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="87.3828125" style="62" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3364,12 +3364,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="63">
         <v>2</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>157</v>
@@ -3378,7 +3378,7 @@
         <v>159</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F2" s="55" t="s">
         <v>158</v>
@@ -3449,19 +3449,19 @@
         <v>1</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AA2" s="42" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="63">
         <v>3</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C3" s="54" t="s">
         <v>157</v>
@@ -3470,7 +3470,7 @@
         <v>159</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F3" s="55" t="s">
         <v>162</v>
@@ -3548,12 +3548,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="63">
         <v>4</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>157</v>
@@ -3562,7 +3562,7 @@
         <v>159</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F4" s="55" t="s">
         <v>164</v>
@@ -3640,12 +3640,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="63">
         <v>5</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C5" s="54" t="s">
         <v>157</v>
@@ -3654,7 +3654,7 @@
         <v>159</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F5" s="55" t="s">
         <v>166</v>
@@ -3732,12 +3732,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="63">
         <v>6</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C6" s="54" t="s">
         <v>157</v>
@@ -3746,7 +3746,7 @@
         <v>159</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F6" s="55" t="s">
         <v>168</v>
@@ -3824,18 +3824,18 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="63">
         <v>7</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C7" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>118</v>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L7" s="51" t="str">
         <f t="shared" ref="L7:L21" si="5">_xlfn.CONCAT(C7)</f>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M7" s="51" t="str">
         <f t="shared" ref="M7:O21" si="6">_xlfn.CONCAT("", D7)</f>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="S7" s="42" t="str">
         <f t="shared" ref="S7:U21" si="8">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T7" s="42" t="str">
         <f t="shared" si="8"/>
@@ -3913,21 +3913,21 @@
         <v>1</v>
       </c>
       <c r="AA7" s="42" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="63">
         <v>8</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C8" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>118</v>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="L8" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M8" s="51" t="str">
         <f t="shared" si="6"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="S8" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T8" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4005,21 +4005,21 @@
         <v>1</v>
       </c>
       <c r="AA8" s="42" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="63">
         <v>9</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C9" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>118</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="L9" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M9" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="S9" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T9" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4097,27 +4097,27 @@
         <v>1</v>
       </c>
       <c r="AA9" s="42" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="63">
         <v>10</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C10" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>118</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G10" s="58" t="s">
         <v>1</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L10" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M10" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="S10" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T10" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4189,21 +4189,21 @@
         <v>1</v>
       </c>
       <c r="AA10" s="42" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="63">
         <v>11</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C11" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>118</v>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="L11" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M11" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="S11" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T11" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4281,21 +4281,21 @@
         <v>1</v>
       </c>
       <c r="AA11" s="42" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="63">
         <v>12</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C12" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>118</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="L12" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M12" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S12" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T12" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4373,21 +4373,21 @@
         <v>1</v>
       </c>
       <c r="AA12" s="42" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="63">
         <v>13</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C13" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>156</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="L13" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M13" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="S13" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T13" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4465,21 +4465,21 @@
         <v>1</v>
       </c>
       <c r="AA13" s="42" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="63">
         <v>14</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C14" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>156</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L14" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M14" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="S14" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T14" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4557,21 +4557,21 @@
         <v>1</v>
       </c>
       <c r="AA14" s="42" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="63">
         <v>15</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C15" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>156</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="L15" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M15" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="S15" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T15" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4649,21 +4649,21 @@
         <v>1</v>
       </c>
       <c r="AA15" s="42" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="63">
         <v>16</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C16" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>156</v>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="L16" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M16" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4706,14 +4706,14 @@
         <v>146</v>
       </c>
       <c r="Q16" s="51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R16" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T16" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4740,27 +4740,27 @@
         <v>1</v>
       </c>
       <c r="AA16" s="42" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="63">
         <v>17</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C17" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>114</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>1</v>
@@ -4775,11 +4775,11 @@
         <v>1</v>
       </c>
       <c r="K17" s="58" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L17" s="51" t="str">
         <f t="shared" ref="L17" si="9">_xlfn.CONCAT(C17)</f>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M17" s="51" t="str">
         <f t="shared" ref="M17" si="10">_xlfn.CONCAT("", D17)</f>
@@ -4794,17 +4794,17 @@
         <v>Translação.XYZ</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q17" s="51" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R17" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S17" s="42" t="str">
         <f t="shared" ref="S17" si="13">SUBSTITUTE(C17, "_", " ")</f>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T17" s="42" t="str">
         <f t="shared" ref="T17" si="14">SUBSTITUTE(D17, "_", " ")</f>
@@ -4831,27 +4831,27 @@
         <v>1</v>
       </c>
       <c r="AA17" s="42" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="63">
         <v>18</v>
       </c>
       <c r="B18" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C18" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>1</v>
@@ -4866,11 +4866,11 @@
         <v>1</v>
       </c>
       <c r="K18" s="58" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L18" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M18" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4885,17 +4885,17 @@
         <v>Translação.Polar</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q18" s="51" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R18" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S18" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T18" s="42" t="str">
         <f t="shared" si="8"/>
@@ -4922,21 +4922,21 @@
         <v>1</v>
       </c>
       <c r="AA18" s="42" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="63">
         <v>19</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C19" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>114</v>
@@ -4957,11 +4957,11 @@
         <v>1</v>
       </c>
       <c r="K19" s="58" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L19" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M19" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4979,14 +4979,14 @@
         <v>153</v>
       </c>
       <c r="Q19" s="51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R19" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T19" s="42" t="str">
         <f t="shared" si="8"/>
@@ -5013,21 +5013,21 @@
         <v>1</v>
       </c>
       <c r="AA19" s="42" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="63">
         <v>20</v>
       </c>
       <c r="B20" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C20" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>114</v>
@@ -5048,11 +5048,11 @@
         <v>1</v>
       </c>
       <c r="K20" s="58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L20" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M20" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5070,14 +5070,14 @@
         <v>154</v>
       </c>
       <c r="Q20" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R20" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S20" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T20" s="42" t="str">
         <f t="shared" si="8"/>
@@ -5104,21 +5104,21 @@
         <v>1</v>
       </c>
       <c r="AA20" s="42" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="63">
         <v>21</v>
       </c>
       <c r="B21" s="54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>114</v>
@@ -5139,11 +5139,11 @@
         <v>1</v>
       </c>
       <c r="K21" s="58" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L21" s="51" t="str">
         <f t="shared" si="5"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="M21" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5161,14 +5161,14 @@
         <v>155</v>
       </c>
       <c r="Q21" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R21" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S21" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>Formal</v>
+        <v>Formantes</v>
       </c>
       <c r="T21" s="42" t="str">
         <f t="shared" si="8"/>
@@ -5195,17 +5195,17 @@
         <v>1</v>
       </c>
       <c r="AA21" s="42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F1 F7:F21">
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:B21">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F7:F21">
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
     <cfRule type="duplicateValues" dxfId="9" priority="1"/>
@@ -5231,15 +5231,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>22</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -5450,14 +5450,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="3" max="3" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5493,36 +5493,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.69140625" customWidth="1"/>
+    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="59" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="62" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="62" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.5703125" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="62" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.84375" style="61" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.3828125" style="61" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.84375" style="62" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.84375" style="62" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.53515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.84375" style="62" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.3828125" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="39" t="s">
         <v>91</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -5607,7 +5607,7 @@
         <v>136</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>1</v>
@@ -5625,7 +5625,7 @@
         <v>95</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J2" s="37" t="s">
         <v>121</v>
@@ -5634,19 +5634,19 @@
         <v>122</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M2" s="60">
         <v>1.05</v>
       </c>
       <c r="N2" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O2" s="60">
         <v>1.05</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q2" s="60">
         <v>0</v>
@@ -5676,15 +5676,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="26">
         <v>3</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>1</v>
@@ -5702,7 +5702,7 @@
         <v>95</v>
       </c>
       <c r="I3" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J3" s="37" t="s">
         <v>121</v>
@@ -5711,37 +5711,37 @@
         <v>122</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M3" s="60">
         <v>1.05</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O3" s="60">
         <v>1.05</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q3" s="60">
         <v>0</v>
       </c>
       <c r="R3" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S3" s="60">
         <v>5.2</v>
       </c>
       <c r="T3" s="37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="U3" s="60">
         <v>0</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W3" s="60">
         <v>0</v>
@@ -5753,7 +5753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="26">
         <v>4</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>95</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J4" s="37" t="s">
         <v>121</v>
@@ -5788,19 +5788,19 @@
         <v>123</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M4" s="60">
         <v>2.0499999999999998</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O4" s="60">
         <v>2.0499999999999998</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q4" s="60">
         <v>0</v>
@@ -5824,13 +5824,13 @@
         <v>1</v>
       </c>
       <c r="X4" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y4" s="47">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="26">
         <v>5</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>95</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J5" s="37" t="s">
         <v>121</v>
@@ -5865,19 +5865,19 @@
         <v>124</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M5" s="60">
         <v>3.05</v>
       </c>
       <c r="N5" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O5" s="60">
         <v>3.05</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q5" s="60">
         <v>0</v>
@@ -5901,13 +5901,13 @@
         <v>1</v>
       </c>
       <c r="X5" s="37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y5" s="47">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="26">
         <v>6</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>95</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J6" s="37" t="s">
         <v>121</v>
@@ -5942,37 +5942,37 @@
         <v>125</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M6" s="60">
         <v>4.05</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O6" s="60">
         <v>4.05</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q6" s="60">
         <v>0</v>
       </c>
       <c r="R6" s="36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S6" s="60">
         <v>14.05</v>
       </c>
       <c r="T6" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="U6" s="60">
         <v>14.05</v>
       </c>
       <c r="V6" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W6" s="60">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="26">
         <v>7</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>95</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J7" s="37" t="s">
         <v>1</v>
@@ -6061,7 +6061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="26">
         <v>8</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>95</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J8" s="37" t="s">
         <v>1</v>
@@ -6138,7 +6138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="26">
         <v>9</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>134</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>132</v>
@@ -6164,7 +6164,7 @@
         <v>95</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J9" s="37" t="s">
         <v>1</v>
@@ -6215,7 +6215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="26">
         <v>10</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>135</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" s="48" t="s">
         <v>132</v>
@@ -6235,13 +6235,13 @@
         <v>140</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>95</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>1</v>
@@ -6292,15 +6292,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="26">
         <v>11</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>1</v>
@@ -6318,7 +6318,7 @@
         <v>95</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J11" s="37" t="s">
         <v>1</v>
@@ -6369,15 +6369,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="26">
         <v>12</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>1</v>
@@ -6395,7 +6395,7 @@
         <v>95</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J12" s="37" t="s">
         <v>1</v>
@@ -6440,18 +6440,18 @@
         <v>1</v>
       </c>
       <c r="X12" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y12" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="Y12" s="47" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="26">
         <v>13</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C13" s="46" t="s">
         <v>126</v>
@@ -6472,7 +6472,7 @@
         <v>95</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J13" s="37" t="s">
         <v>1</v>
@@ -6517,18 +6517,18 @@
         <v>1</v>
       </c>
       <c r="X13" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y13" s="47">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="26">
         <v>14</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C14" s="46" t="s">
         <v>126</v>
@@ -6549,7 +6549,7 @@
         <v>95</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>1</v>
@@ -6594,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y14" s="47">
         <v>60</v>
@@ -6618,14 +6618,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/GENE/Ontologia_Genetica.xlsx
+++ b/Versão5/GENE/Ontologia_Genetica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GENE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71E2808-3C2B-41EF-8607-6E2CE4F5D649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E5EDCF-A8A7-4217-9C25-70535EB12308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="219">
   <si>
     <t>Key</t>
   </si>
@@ -1735,45 +1735,6 @@
     <t>Bases.Geométricas</t>
   </si>
   <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Contêiner</t>
-  </si>
-  <si>
-    <t>Informação</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Requisito.Espacial</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Mobiliário</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Equipamento</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
-    <t>Requisito.Sistemas</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>Elementos.TGB</t>
   </si>
   <si>
@@ -1952,12 +1913,6 @@
   </si>
   <si>
     <t xml:space="preserve"> base.x exactly 1  ,   base.y exactly 1  ,  base.z exactly 1  ,  valor.distância  exactly 1  ,   valor.angular exactly 1 </t>
-  </si>
-  <si>
-    <t>Contêineres</t>
-  </si>
-  <si>
-    <t>[ 5I ]</t>
   </si>
   <si>
     <t>Conceitos</t>
@@ -2320,7 +2275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2480,14 +2435,8 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2517,7 +2466,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2554,22 +2511,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2577,54 +2518,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2944,15 +2837,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>51</v>
       </c>
@@ -2963,7 +2856,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>60</v>
       </c>
@@ -2974,7 +2867,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -2985,7 +2878,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>52</v>
       </c>
@@ -2996,7 +2889,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>53</v>
       </c>
@@ -3008,7 +2901,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
@@ -3020,7 +2913,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>55</v>
       </c>
@@ -3031,7 +2924,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>56</v>
       </c>
@@ -3042,7 +2935,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>64</v>
       </c>
@@ -3053,7 +2946,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -3064,7 +2957,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -3075,7 +2968,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -3086,7 +2979,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>67</v>
       </c>
@@ -3097,7 +2990,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>68</v>
       </c>
@@ -3108,7 +3001,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
@@ -3119,7 +3012,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>70</v>
       </c>
@@ -3130,7 +3023,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
@@ -3141,19 +3034,19 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46243.521928240742</v>
+        <v>46244.67327013889</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>108</v>
       </c>
@@ -3164,7 +3057,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>106</v>
       </c>
@@ -3176,7 +3069,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="35" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="35" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>107</v>
       </c>
@@ -3188,7 +3081,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3199,7 +3092,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3210,7 +3103,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>74</v>
       </c>
@@ -3221,7 +3114,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
@@ -3232,7 +3125,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>100</v>
       </c>
@@ -3252,36 +3145,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD6176F-27DE-4341-8BCF-4E468F3B43BE}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AA16"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.69140625" customWidth="1"/>
-    <col min="4" max="4" width="8.07421875" customWidth="1"/>
-    <col min="5" max="5" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.53515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.15234375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.15234375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="76" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="88.3046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.69140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9" style="62" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.3046875" style="62" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.53515625" style="62" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.69140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6" style="62" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.3828125" style="62" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.3046875" style="62" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="87.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="88.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.42578125" style="60" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="87.42578125" style="60" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
@@ -3300,19 +3193,19 @@
       <c r="F1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="J1" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="55" t="s">
         <v>43</v>
       </c>
       <c r="L1" s="22" t="s">
@@ -3348,7 +3241,7 @@
       <c r="V1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="W1" s="65" t="s">
+      <c r="W1" s="63" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="22" t="s">
@@ -3364,82 +3257,83 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="63">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="61">
         <v>2</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>230</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="G2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="52" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
-      </c>
-      <c r="M2" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N2" s="52" t="str">
-        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Contêineres</v>
-      </c>
-      <c r="O2" s="52" t="str">
+      <c r="E2" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="51" t="str">
+        <f t="shared" ref="L2:L16" si="0">_xlfn.CONCAT(C2)</f>
+        <v>Formantes</v>
+      </c>
+      <c r="M2" s="51" t="str">
+        <f t="shared" ref="M2:O16" si="1">_xlfn.CONCAT("", D2)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N2" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q2" s="42" t="s">
-        <v>161</v>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O2" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Valor.X</v>
+      </c>
+      <c r="P2" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q2" s="51" t="str">
+        <f t="shared" ref="Q2:Q10" si="2">_xlfn.TRANSLATE(P2,"pt","es")</f>
+        <v>Valor de X. Coordenada X.</v>
       </c>
       <c r="R2" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S2" s="42" t="str">
-        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Gestão</v>
+        <f t="shared" ref="S2:U16" si="3">SUBSTITUTE(C2, "_", " ")</f>
+        <v>Formantes</v>
       </c>
       <c r="T2" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U2" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U2" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V2" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="64" t="str">
-        <f>CONCATENATE("Key-EGC-",A2)</f>
+      <c r="W2" s="62" t="str">
+        <f t="shared" ref="W2:W16" si="4">CONCATENATE("Key-EGC-",A2)</f>
         <v>Key-EGC-2</v>
       </c>
       <c r="X2" s="42" t="s">
@@ -3449,89 +3343,89 @@
         <v>1</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="AA2" s="42" t="str">
-        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="63">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="42" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="61">
         <v>3</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D3" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" s="55" t="s">
-        <v>230</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="52" t="str">
+      <c r="E3" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="51" t="str">
         <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M3" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N3" s="52" t="str">
+        <v>Formantes</v>
+      </c>
+      <c r="M3" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O3" s="52" t="str">
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N3" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>Requisito Espacial</v>
-      </c>
-      <c r="P3" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q3" s="42" t="s">
-        <v>161</v>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O3" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Valor.Y</v>
+      </c>
+      <c r="P3" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q3" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>Valor de Y. Coordenada Y.</v>
       </c>
       <c r="R3" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S3" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <f t="shared" si="3"/>
+        <v>Formantes</v>
       </c>
       <c r="T3" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U3" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U3" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V3" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="64" t="str">
-        <f t="shared" ref="W3:W21" si="4">CONCATENATE("Key-EGC-",A3)</f>
+      <c r="W3" s="62" t="str">
+        <f t="shared" si="4"/>
         <v>Key-EGC-3</v>
       </c>
       <c r="X3" s="42" t="s">
@@ -3543,86 +3437,86 @@
       <c r="Z3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AA3" s="42" t="str">
+      <c r="AA3" s="42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="61">
+        <v>4</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>Formantes</v>
+      </c>
+      <c r="M4" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N4" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O4" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Valor.Z</v>
+      </c>
+      <c r="P4" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q4" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>Valor Z. Coordenada Z.</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="42" t="str">
         <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="63">
-        <v>4</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>230</v>
-      </c>
-      <c r="F4" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M4" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N4" s="52" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O4" s="52" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Mobiliário</v>
-      </c>
-      <c r="P4" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q4" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="R4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <v>Formantes</v>
       </c>
       <c r="T4" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U4" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U4" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V4" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W4" s="64" t="str">
+      <c r="W4" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-4</v>
       </c>
@@ -3635,86 +3529,86 @@
       <c r="Z4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AA4" s="42" t="str">
+      <c r="AA4" s="42" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="61">
+        <v>5</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>Formantes</v>
+      </c>
+      <c r="M5" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N5" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O5" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Valor.Distância</v>
+      </c>
+      <c r="P5" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q5" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>Valor desplazado. Valor de distancia de una traslación</v>
+      </c>
+      <c r="R5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="42" t="str">
         <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="63">
-        <v>5</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>157</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="55" t="s">
-        <v>230</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="G5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M5" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N5" s="52" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O5" s="52" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Equipamento</v>
-      </c>
-      <c r="P5" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q5" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="R5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <v>Formantes</v>
       </c>
       <c r="T5" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U5" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U5" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V5" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W5" s="64" t="str">
+      <c r="W5" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-5</v>
       </c>
@@ -3727,86 +3621,86 @@
       <c r="Z5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AA5" s="42" t="str">
+      <c r="AA5" s="42" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="61">
+        <v>6</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>Formantes</v>
+      </c>
+      <c r="M6" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N6" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Parâmetro.Geométrico</v>
+      </c>
+      <c r="O6" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Valor.Angular</v>
+      </c>
+      <c r="P6" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q6" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>Valor angular de una transformada de espín o rotación</v>
+      </c>
+      <c r="R6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="42" t="str">
         <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" s="62" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="63">
-        <v>6</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="55" t="s">
-        <v>230</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="G6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M6" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N6" s="52" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O6" s="52" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Sistemas</v>
-      </c>
-      <c r="P6" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q6" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="R6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
+        <v>Formantes</v>
       </c>
       <c r="T6" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U6" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
+        <f t="shared" si="3"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="U6" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V6" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W6" s="64" t="str">
+      <c r="W6" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-6</v>
       </c>
@@ -3819,87 +3713,86 @@
       <c r="Z6" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AA6" s="42" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="63">
+      <c r="AA6" s="42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="61">
         <v>7</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>118</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="56" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="51" t="str">
-        <f t="shared" ref="L7:L21" si="5">_xlfn.CONCAT(C7)</f>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M7" s="51" t="str">
-        <f t="shared" ref="M7:O21" si="6">_xlfn.CONCAT("", D7)</f>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N7" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="O7" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor.X</v>
+        <f t="shared" si="1"/>
+        <v>Valor.Escalar</v>
       </c>
       <c r="P7" s="51" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="Q7" s="51" t="str">
-        <f t="shared" ref="Q7:Q15" si="7">_xlfn.TRANSLATE(P7,"pt","es")</f>
-        <v>Valor de X. Coordenada X.</v>
+        <f t="shared" si="2"/>
+        <v>Valor escalar de una transformación que cambia la escala</v>
       </c>
       <c r="R7" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S7" s="42" t="str">
-        <f t="shared" ref="S7:U21" si="8">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T7" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U7" s="52" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Parâmetro.Geométrico</v>
       </c>
       <c r="V7" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W7" s="64" t="str">
+      <c r="W7" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-7</v>
       </c>
@@ -3913,85 +3806,85 @@
         <v>1</v>
       </c>
       <c r="AA7" s="42" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="63">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="61">
         <v>8</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="56" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M8" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N8" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="1"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="O8" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor.Y</v>
+        <f t="shared" si="1"/>
+        <v>Ponto.Eixo1</v>
       </c>
       <c r="P8" s="51" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="Q8" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Valor de Y. Coordenada Y.</v>
+        <f t="shared" si="2"/>
+        <v>Punto 1 que define un eje de simetría</v>
       </c>
       <c r="R8" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T8" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U8" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="3"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="V8" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W8" s="64" t="str">
+      <c r="W8" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-8</v>
       </c>
@@ -4005,85 +3898,85 @@
         <v>1</v>
       </c>
       <c r="AA8" s="42" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="63">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="61">
         <v>9</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="56" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M9" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N9" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="1"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="O9" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor.Z</v>
+        <f t="shared" si="1"/>
+        <v>Ponto.Eixo2</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="Q9" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Valor Z. Coordenada Z.</v>
+        <f t="shared" si="2"/>
+        <v>Punto 2 que define un eje de simetría</v>
       </c>
       <c r="R9" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T9" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U9" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="3"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="V9" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W9" s="64" t="str">
+      <c r="W9" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-9</v>
       </c>
@@ -4097,85 +3990,85 @@
         <v>1</v>
       </c>
       <c r="AA9" s="42" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="63">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="61">
         <v>10</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="G10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="56" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M10" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N10" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="1"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="O10" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor.Distância</v>
+        <f t="shared" si="1"/>
+        <v>Ponto.Base</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="Q10" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Valor desplazado. Valor de distancia de una traslación</v>
+        <f t="shared" si="2"/>
+        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
       </c>
       <c r="R10" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T10" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U10" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="3"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="V10" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W10" s="64" t="str">
+      <c r="W10" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-10</v>
       </c>
@@ -4189,85 +4082,84 @@
         <v>1</v>
       </c>
       <c r="AA10" s="42" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="63">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="61">
         <v>11</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="56" t="s">
         <v>1</v>
       </c>
       <c r="L11" s="51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M11" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N11" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="1"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="O11" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor.Angular</v>
+        <f t="shared" si="1"/>
+        <v>Ponto.Destino</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q11" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Valor angular de una transformada de espín o rotación</v>
+        <v>146</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>158</v>
       </c>
       <c r="R11" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T11" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U11" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" si="3"/>
+        <v>Bases.Geométricas</v>
       </c>
       <c r="V11" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W11" s="64" t="str">
+      <c r="W11" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-11</v>
       </c>
@@ -4281,85 +4173,84 @@
         <v>1</v>
       </c>
       <c r="AA11" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="61">
+        <v>12</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="56" t="s">
+        <v>212</v>
+      </c>
+      <c r="L12" s="51" t="str">
+        <f t="shared" ref="L12" si="5">_xlfn.CONCAT(C12)</f>
+        <v>Formantes</v>
+      </c>
+      <c r="M12" s="51" t="str">
+        <f t="shared" ref="M12" si="6">_xlfn.CONCAT("", D12)</f>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N12" s="51" t="str">
+        <f t="shared" ref="N12" si="7">_xlfn.CONCAT("", E12)</f>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O12" s="51" t="str">
+        <f t="shared" ref="O12" si="8">_xlfn.CONCAT("", F12)</f>
+        <v>Translação.XYZ</v>
+      </c>
+      <c r="P12" s="51" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="63">
-        <v>12</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="51" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q12" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="R12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12" s="42" t="str">
+        <f t="shared" ref="S12" si="9">SUBSTITUTE(C12, "_", " ")</f>
         <v>Formantes</v>
       </c>
-      <c r="M12" s="51" t="str">
-        <f t="shared" si="6"/>
+      <c r="T12" s="42" t="str">
+        <f t="shared" ref="T12" si="10">SUBSTITUTE(D12, "_", " ")</f>
         <v>Elementos.TGB</v>
       </c>
-      <c r="N12" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Parâmetro.Geométrico</v>
-      </c>
-      <c r="O12" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Valor.Escalar</v>
-      </c>
-      <c r="P12" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q12" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Valor escalar de una transformación que cambia la escala</v>
-      </c>
-      <c r="R12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T12" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.TGB</v>
-      </c>
       <c r="U12" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Parâmetro.Geométrico</v>
+        <f t="shared" ref="U12" si="11">SUBSTITUTE(E12, "_", " ")</f>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="V12" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W12" s="64" t="str">
+      <c r="W12" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-12</v>
       </c>
@@ -4373,85 +4264,84 @@
         <v>1</v>
       </c>
       <c r="AA12" s="42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="61">
+        <v>13</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="L13" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>Formantes</v>
+      </c>
+      <c r="M13" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Elementos.TGB</v>
+      </c>
+      <c r="N13" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Movimento.Geométrico</v>
+      </c>
+      <c r="O13" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Translação.Polar</v>
+      </c>
+      <c r="P13" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q13" s="51" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="63">
-        <v>13</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="G13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="51" t="str">
-        <f t="shared" si="5"/>
+      <c r="R13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="42" t="str">
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
-      <c r="M13" s="51" t="str">
-        <f t="shared" si="6"/>
+      <c r="T13" s="42" t="str">
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
-      <c r="N13" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Bases.Geométricas</v>
-      </c>
-      <c r="O13" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Ponto.Eixo1</v>
-      </c>
-      <c r="P13" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q13" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Punto 1 que define un eje de simetría</v>
-      </c>
-      <c r="R13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T13" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.TGB</v>
-      </c>
       <c r="U13" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Bases.Geométricas</v>
+        <f t="shared" si="3"/>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="V13" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W13" s="64" t="str">
+      <c r="W13" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-13</v>
       </c>
@@ -4465,85 +4355,84 @@
         <v>1</v>
       </c>
       <c r="AA13" s="42" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="63">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="61">
         <v>14</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="G14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="58" t="s">
-        <v>1</v>
+        <v>115</v>
+      </c>
+      <c r="G14" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="56" t="s">
+        <v>213</v>
       </c>
       <c r="L14" s="51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M14" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N14" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Bases.Geométricas</v>
+        <f t="shared" si="1"/>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="O14" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Ponto.Eixo2</v>
+        <f t="shared" si="1"/>
+        <v>Giro</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q14" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Punto 2 que define un eje de simetría</v>
+        <v>153</v>
+      </c>
+      <c r="Q14" s="51" t="s">
+        <v>161</v>
       </c>
       <c r="R14" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S14" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T14" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U14" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Bases.Geométricas</v>
+        <f t="shared" si="3"/>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="V14" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W14" s="64" t="str">
+      <c r="W14" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-14</v>
       </c>
@@ -4557,85 +4446,84 @@
         <v>1</v>
       </c>
       <c r="AA14" s="42" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="63">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="61">
         <v>15</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="G15" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="58" t="s">
-        <v>1</v>
+        <v>116</v>
+      </c>
+      <c r="G15" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="56" t="s">
+        <v>214</v>
       </c>
       <c r="L15" s="51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M15" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N15" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Bases.Geométricas</v>
+        <f t="shared" si="1"/>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="O15" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Ponto.Base</v>
+        <f t="shared" si="1"/>
+        <v>Escalar</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q15" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Punto base que puede servir como primer punto base de un vector de traslación o para referenciar un proyecto</v>
+        <v>154</v>
+      </c>
+      <c r="Q15" s="51" t="s">
+        <v>160</v>
       </c>
       <c r="R15" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T15" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U15" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Bases.Geométricas</v>
+        <f t="shared" si="3"/>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="V15" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W15" s="64" t="str">
+      <c r="W15" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-15</v>
       </c>
@@ -4649,84 +4537,84 @@
         <v>1</v>
       </c>
       <c r="AA15" s="42" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="63">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="61">
         <v>16</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="G16" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="58" t="s">
-        <v>1</v>
+        <v>117</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="56" t="s">
+        <v>215</v>
       </c>
       <c r="L16" s="51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>Formantes</v>
       </c>
       <c r="M16" s="51" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="N16" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Bases.Geométricas</v>
+        <f t="shared" si="1"/>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="O16" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Ponto.Destino</v>
+        <f t="shared" si="1"/>
+        <v>Reflexão</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="Q16" s="51" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="R16" s="42" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Formantes</v>
       </c>
       <c r="T16" s="42" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>Elementos.TGB</v>
       </c>
       <c r="U16" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Bases.Geométricas</v>
+        <f t="shared" si="3"/>
+        <v>Movimento.Geométrico</v>
       </c>
       <c r="V16" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="W16" s="64" t="str">
+      <c r="W16" s="62" t="str">
         <f t="shared" si="4"/>
         <v>Key-EGC-16</v>
       </c>
@@ -4740,488 +4628,17 @@
         <v>1</v>
       </c>
       <c r="AA16" s="42" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="63">
-        <v>17</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="G17" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L17" s="51" t="str">
-        <f t="shared" ref="L17" si="9">_xlfn.CONCAT(C17)</f>
-        <v>Formantes</v>
-      </c>
-      <c r="M17" s="51" t="str">
-        <f t="shared" ref="M17" si="10">_xlfn.CONCAT("", D17)</f>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N17" s="51" t="str">
-        <f t="shared" ref="N17" si="11">_xlfn.CONCAT("", E17)</f>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O17" s="51" t="str">
-        <f t="shared" ref="O17" si="12">_xlfn.CONCAT("", F17)</f>
-        <v>Translação.XYZ</v>
-      </c>
-      <c r="P17" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q17" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="R17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="42" t="str">
-        <f t="shared" ref="S17" si="13">SUBSTITUTE(C17, "_", " ")</f>
-        <v>Formantes</v>
-      </c>
-      <c r="T17" s="42" t="str">
-        <f t="shared" ref="T17" si="14">SUBSTITUTE(D17, "_", " ")</f>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U17" s="52" t="str">
-        <f t="shared" ref="U17" si="15">SUBSTITUTE(E17, "_", " ")</f>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V17" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W17" s="64" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-EGC-17</v>
-      </c>
-      <c r="X17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="42" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="63">
-        <v>18</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="G18" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="L18" s="51" t="str">
-        <f t="shared" si="5"/>
-        <v>Formantes</v>
-      </c>
-      <c r="M18" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N18" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O18" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Translação.Polar</v>
-      </c>
-      <c r="P18" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q18" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="R18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T18" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U18" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V18" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W18" s="64" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-EGC-18</v>
-      </c>
-      <c r="X18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="42" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="63">
-        <v>19</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="G19" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="58" t="s">
-        <v>226</v>
-      </c>
-      <c r="L19" s="51" t="str">
-        <f t="shared" si="5"/>
-        <v>Formantes</v>
-      </c>
-      <c r="M19" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N19" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O19" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Giro</v>
-      </c>
-      <c r="P19" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q19" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="R19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T19" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U19" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V19" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W19" s="64" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-EGC-19</v>
-      </c>
-      <c r="X19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="42" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="63">
-        <v>20</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="58" t="s">
-        <v>227</v>
-      </c>
-      <c r="L20" s="51" t="str">
-        <f t="shared" si="5"/>
-        <v>Formantes</v>
-      </c>
-      <c r="M20" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N20" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O20" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Escalar</v>
-      </c>
-      <c r="P20" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q20" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="R20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T20" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U20" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V20" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W20" s="64" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-EGC-20</v>
-      </c>
-      <c r="X20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="42" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="63">
-        <v>21</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="58" t="s">
-        <v>228</v>
-      </c>
-      <c r="L21" s="51" t="str">
-        <f t="shared" si="5"/>
-        <v>Formantes</v>
-      </c>
-      <c r="M21" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="N21" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="O21" s="51" t="str">
-        <f t="shared" si="6"/>
-        <v>Reflexão</v>
-      </c>
-      <c r="P21" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q21" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="R21" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Formantes</v>
-      </c>
-      <c r="T21" s="42" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.TGB</v>
-      </c>
-      <c r="U21" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Movimento.Geométrico</v>
-      </c>
-      <c r="V21" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="W21" s="64" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-EGC-21</v>
-      </c>
-      <c r="X21" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="42" t="s">
-        <v>187</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B21">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B16">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F7:F21">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V6">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F1:F16">
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5231,15 +4648,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="33" t="s">
         <v>22</v>
       </c>
@@ -5304,7 +4721,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -5369,7 +4786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -5437,7 +4854,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5450,14 +4867,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
-    <col min="3" max="3" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -5468,7 +4885,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5481,7 +4898,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5493,36 +4910,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E710AC9-81F8-4DDA-B9A5-638130FB9FB8}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.69140625" customWidth="1"/>
-    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="59" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.84375" style="61" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.3828125" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.84375" style="62" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.84375" style="62" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.53515625" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.84375" style="62" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.3828125" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
         <v>91</v>
       </c>
@@ -5559,37 +4976,37 @@
       <c r="L1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="57" t="s">
         <v>92</v>
       </c>
       <c r="N1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="59" t="s">
+      <c r="O1" s="57" t="s">
         <v>92</v>
       </c>
       <c r="P1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="59" t="s">
+      <c r="Q1" s="57" t="s">
         <v>92</v>
       </c>
       <c r="R1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="59" t="s">
+      <c r="S1" s="57" t="s">
         <v>92</v>
       </c>
       <c r="T1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="U1" s="59" t="s">
+      <c r="U1" s="57" t="s">
         <v>92</v>
       </c>
       <c r="V1" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="59" t="s">
+      <c r="W1" s="57" t="s">
         <v>92</v>
       </c>
       <c r="X1" s="29" t="s">
@@ -5599,7 +5016,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -5607,7 +5024,7 @@
         <v>136</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>1</v>
@@ -5625,7 +5042,7 @@
         <v>95</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="J2" s="37" t="s">
         <v>121</v>
@@ -5634,39 +5051,39 @@
         <v>122</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="M2" s="60">
+        <v>186</v>
+      </c>
+      <c r="M2" s="58">
         <v>1.05</v>
       </c>
       <c r="N2" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="O2" s="60">
+        <v>187</v>
+      </c>
+      <c r="O2" s="58">
         <v>1.05</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q2" s="60">
+        <v>188</v>
+      </c>
+      <c r="Q2" s="58">
         <v>0</v>
       </c>
       <c r="R2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="60" t="s">
+      <c r="S2" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="60" t="s">
+      <c r="U2" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W2" s="60" t="s">
+      <c r="W2" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X2" s="37" t="s">
@@ -5676,15 +5093,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
         <v>3</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>1</v>
@@ -5702,7 +5119,7 @@
         <v>95</v>
       </c>
       <c r="I3" s="38" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="J3" s="37" t="s">
         <v>121</v>
@@ -5711,39 +5128,39 @@
         <v>122</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="M3" s="60">
+        <v>186</v>
+      </c>
+      <c r="M3" s="58">
         <v>1.05</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="O3" s="60">
+        <v>187</v>
+      </c>
+      <c r="O3" s="58">
         <v>1.05</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q3" s="60">
+        <v>188</v>
+      </c>
+      <c r="Q3" s="58">
         <v>0</v>
       </c>
       <c r="R3" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="S3" s="60">
+        <v>189</v>
+      </c>
+      <c r="S3" s="58">
         <v>5.2</v>
       </c>
       <c r="T3" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="U3" s="60">
+        <v>191</v>
+      </c>
+      <c r="U3" s="58">
         <v>0</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="W3" s="60">
+        <v>190</v>
+      </c>
+      <c r="W3" s="58">
         <v>0</v>
       </c>
       <c r="X3" s="37" t="s">
@@ -5753,7 +5170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>4</v>
       </c>
@@ -5779,7 +5196,7 @@
         <v>95</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="J4" s="37" t="s">
         <v>121</v>
@@ -5788,49 +5205,49 @@
         <v>123</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="M4" s="60">
+        <v>186</v>
+      </c>
+      <c r="M4" s="58">
         <v>2.0499999999999998</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="O4" s="60">
+        <v>187</v>
+      </c>
+      <c r="O4" s="58">
         <v>2.0499999999999998</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q4" s="60">
+        <v>188</v>
+      </c>
+      <c r="Q4" s="58">
         <v>0</v>
       </c>
       <c r="R4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S4" s="60" t="s">
+      <c r="S4" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U4" s="60" t="s">
+      <c r="U4" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W4" s="60" t="s">
+      <c r="W4" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X4" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="Y4" s="47">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>5</v>
       </c>
@@ -5856,7 +5273,7 @@
         <v>95</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="J5" s="37" t="s">
         <v>121</v>
@@ -5865,49 +5282,49 @@
         <v>124</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="M5" s="60">
+        <v>186</v>
+      </c>
+      <c r="M5" s="58">
         <v>3.05</v>
       </c>
       <c r="N5" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="O5" s="60">
+        <v>187</v>
+      </c>
+      <c r="O5" s="58">
         <v>3.05</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q5" s="60">
+        <v>188</v>
+      </c>
+      <c r="Q5" s="58">
         <v>0</v>
       </c>
       <c r="R5" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S5" s="60" t="s">
+      <c r="S5" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U5" s="60" t="s">
+      <c r="U5" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V5" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W5" s="60" t="s">
+      <c r="W5" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X5" s="37" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="Y5" s="47">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>6</v>
       </c>
@@ -5933,7 +5350,7 @@
         <v>95</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="J6" s="37" t="s">
         <v>121</v>
@@ -5942,39 +5359,39 @@
         <v>125</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="M6" s="60">
+        <v>186</v>
+      </c>
+      <c r="M6" s="58">
         <v>4.05</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="O6" s="60">
+        <v>187</v>
+      </c>
+      <c r="O6" s="58">
         <v>4.05</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q6" s="60">
+        <v>188</v>
+      </c>
+      <c r="Q6" s="58">
         <v>0</v>
       </c>
       <c r="R6" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="S6" s="60">
+        <v>189</v>
+      </c>
+      <c r="S6" s="58">
         <v>14.05</v>
       </c>
       <c r="T6" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="U6" s="60">
+        <v>191</v>
+      </c>
+      <c r="U6" s="58">
         <v>14.05</v>
       </c>
       <c r="V6" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="W6" s="60">
+        <v>190</v>
+      </c>
+      <c r="W6" s="58">
         <v>0</v>
       </c>
       <c r="X6" s="37" t="s">
@@ -5984,7 +5401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>7</v>
       </c>
@@ -6010,7 +5427,7 @@
         <v>95</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="J7" s="37" t="s">
         <v>1</v>
@@ -6021,37 +5438,37 @@
       <c r="L7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M7" s="60" t="s">
+      <c r="M7" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O7" s="60" t="s">
+      <c r="O7" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="60" t="s">
+      <c r="Q7" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R7" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S7" s="60" t="s">
+      <c r="S7" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T7" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U7" s="60" t="s">
+      <c r="U7" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V7" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W7" s="60" t="s">
+      <c r="W7" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X7" s="37" t="s">
@@ -6061,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>8</v>
       </c>
@@ -6087,7 +5504,7 @@
         <v>95</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="J8" s="37" t="s">
         <v>1</v>
@@ -6098,37 +5515,37 @@
       <c r="L8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M8" s="60" t="s">
+      <c r="M8" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O8" s="60" t="s">
+      <c r="O8" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q8" s="60" t="s">
+      <c r="Q8" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R8" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S8" s="60" t="s">
+      <c r="S8" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T8" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U8" s="60" t="s">
+      <c r="U8" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V8" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W8" s="60" t="s">
+      <c r="W8" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X8" s="37" t="s">
@@ -6138,7 +5555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>9</v>
       </c>
@@ -6146,7 +5563,7 @@
         <v>134</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>132</v>
@@ -6164,7 +5581,7 @@
         <v>95</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="J9" s="37" t="s">
         <v>1</v>
@@ -6175,37 +5592,37 @@
       <c r="L9" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M9" s="60" t="s">
+      <c r="M9" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N9" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O9" s="60" t="s">
+      <c r="O9" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P9" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q9" s="60" t="s">
+      <c r="Q9" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R9" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S9" s="60" t="s">
+      <c r="S9" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T9" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U9" s="60" t="s">
+      <c r="U9" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V9" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W9" s="60" t="s">
+      <c r="W9" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X9" s="37" t="s">
@@ -6215,7 +5632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>10</v>
       </c>
@@ -6223,7 +5640,7 @@
         <v>135</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D10" s="48" t="s">
         <v>132</v>
@@ -6235,13 +5652,13 @@
         <v>140</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>95</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>1</v>
@@ -6252,37 +5669,37 @@
       <c r="L10" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="60" t="s">
+      <c r="M10" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N10" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O10" s="60" t="s">
+      <c r="O10" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P10" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q10" s="60" t="s">
+      <c r="Q10" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R10" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S10" s="60" t="s">
+      <c r="S10" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U10" s="60" t="s">
+      <c r="U10" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V10" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W10" s="60" t="s">
+      <c r="W10" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X10" s="37" t="s">
@@ -6292,15 +5709,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>11</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>1</v>
@@ -6318,7 +5735,7 @@
         <v>95</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="J11" s="37" t="s">
         <v>1</v>
@@ -6329,37 +5746,37 @@
       <c r="L11" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M11" s="60" t="s">
+      <c r="M11" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N11" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="60" t="s">
+      <c r="O11" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P11" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q11" s="60" t="s">
+      <c r="Q11" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R11" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S11" s="60" t="s">
+      <c r="S11" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T11" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U11" s="60" t="s">
+      <c r="U11" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V11" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W11" s="60" t="s">
+      <c r="W11" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X11" s="37" t="s">
@@ -6369,15 +5786,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>12</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>1</v>
@@ -6395,7 +5812,7 @@
         <v>95</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="J12" s="37" t="s">
         <v>1</v>
@@ -6406,52 +5823,52 @@
       <c r="L12" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M12" s="60" t="s">
+      <c r="M12" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N12" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O12" s="60" t="s">
+      <c r="O12" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P12" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q12" s="60" t="s">
+      <c r="Q12" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R12" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S12" s="60" t="s">
+      <c r="S12" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T12" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U12" s="60" t="s">
+      <c r="U12" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V12" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W12" s="60" t="s">
+      <c r="W12" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X12" s="37" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="Y12" s="47" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>13</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C13" s="46" t="s">
         <v>126</v>
@@ -6472,7 +5889,7 @@
         <v>95</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="J13" s="37" t="s">
         <v>1</v>
@@ -6483,52 +5900,52 @@
       <c r="L13" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="60" t="s">
+      <c r="M13" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N13" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O13" s="60" t="s">
+      <c r="O13" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P13" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q13" s="60" t="s">
+      <c r="Q13" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R13" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S13" s="60" t="s">
+      <c r="S13" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T13" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U13" s="60" t="s">
+      <c r="U13" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V13" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W13" s="60" t="s">
+      <c r="W13" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X13" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="Y13" s="47">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:25" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
         <v>14</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C14" s="46" t="s">
         <v>126</v>
@@ -6549,7 +5966,7 @@
         <v>95</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>1</v>
@@ -6560,41 +5977,41 @@
       <c r="L14" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="M14" s="60" t="s">
+      <c r="M14" s="58" t="s">
         <v>1</v>
       </c>
       <c r="N14" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="60" t="s">
+      <c r="O14" s="58" t="s">
         <v>1</v>
       </c>
       <c r="P14" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="Q14" s="60" t="s">
+      <c r="Q14" s="58" t="s">
         <v>1</v>
       </c>
       <c r="R14" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="S14" s="60" t="s">
+      <c r="S14" s="58" t="s">
         <v>1</v>
       </c>
       <c r="T14" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U14" s="60" t="s">
+      <c r="U14" s="58" t="s">
         <v>1</v>
       </c>
       <c r="V14" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="W14" s="60" t="s">
+      <c r="W14" s="58" t="s">
         <v>1</v>
       </c>
       <c r="X14" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="Y14" s="47">
         <v>60</v>
@@ -6603,12 +6020,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B14 H1:I14">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -6618,14 +6035,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -6633,7 +6050,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -6641,7 +6058,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -6649,7 +6066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -6657,7 +6074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -6665,7 +6082,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -6673,7 +6090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -6681,7 +6098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -6689,7 +6106,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -6697,7 +6114,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -6705,7 +6122,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -6713,7 +6130,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -6721,7 +6138,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -6729,7 +6146,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -6737,7 +6154,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>
